--- a/public/templates/SALES_EBAY_TEMPLATE.xlsx
+++ b/public/templates/SALES_EBAY_TEMPLATE.xlsx
@@ -116,22 +116,22 @@
     <t>Colour</t>
   </si>
   <si>
-    <t>EBAY-EXAMPLE</t>
+    <t>EB-3310</t>
   </si>
   <si>
-    <t>SG-XC5-64-BK</t>
+    <t>IP13P-256-GRA</t>
   </si>
   <si>
-    <t>350100000000001</t>
+    <t>350100000023757</t>
   </si>
   <si>
-    <t>EXAMPLE SUPPLIER</t>
+    <t>CELLHUB TRADING</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Samsung Galaxy XC5 64GB</t>
+    <t>Apple iPhone 13P 256GB</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -803,10 +803,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3">
-        <v>30</v>
+        <v>520</v>
       </c>
       <c r="H2" s="3">
-        <v>55.99</v>
+        <v>679</v>
       </c>
       <c r="I2" s="3">
         <f>IF($H2="","",H2-G2)</f>
@@ -830,7 +830,7 @@
         <f>IF($H2="","",K2+L2+M2+N2)</f>
       </c>
       <c r="P2" s="3">
-        <v>4.65</v>
+        <v>8</v>
       </c>
       <c r="Q2" s="3">
         <v>0</v>

--- a/public/templates/SALES_EBAY_TEMPLATE.xlsx
+++ b/public/templates/SALES_EBAY_TEMPLATE.xlsx
@@ -809,25 +809,25 @@
         <v>679</v>
       </c>
       <c r="I2" s="3">
-        <f>IF($H2="","",H2-G2)</f>
+        <f>H2-G2</f>
       </c>
       <c r="J2" s="3">
-        <f>IF($H2="","",I2*16.67%)</f>
+        <f>I2*16.67%</f>
       </c>
       <c r="K2" s="3">
-        <f>IF($H2="","",(H2*6.9%)-(H2*6.9%)*10%)</f>
+        <f>(H2*6.9%)-(H2*6.9%)*10%</f>
       </c>
       <c r="L2" s="3">
-        <f>IF($H2="","",H2*0.35%)</f>
+        <f>H2*0.35%</f>
       </c>
       <c r="M2" s="3">
         <v>0.4</v>
       </c>
       <c r="N2" s="3">
-        <f>IF($H2="","",(K2+L2+M2)*20%)</f>
+        <f>(K2+L2+M2)*20%</f>
       </c>
       <c r="O2" s="3">
-        <f>IF($H2="","",K2+L2+M2+N2)</f>
+        <f>K2+L2+M2+N2</f>
       </c>
       <c r="P2" s="3">
         <v>8</v>
@@ -839,22 +839,22 @@
         <v>0</v>
       </c>
       <c r="S2" s="3">
-        <f>IF($H2="","",R2*20%)</f>
+        <f>R2*20%</f>
       </c>
       <c r="T2" s="3">
         <v>1</v>
       </c>
       <c r="U2" s="3">
-        <f>IF($H2="","",N2+Q2+S2)</f>
+        <f>N2+Q2+S2</f>
       </c>
       <c r="V2" s="3">
-        <f>IF($H2="","",I2-J2-O2-P2-Q2-R2-S2-T2)</f>
+        <f>I2-J2-O2-P2-Q2-R2-S2-T2</f>
       </c>
       <c r="W2" s="3">
-        <f>IF($H2="","",(V2-AE2)/H2*100)</f>
+        <f>(V2-AE2)/H2*100</f>
       </c>
       <c r="X2" s="3">
-        <f>IF($H2="","",J2-U2)</f>
+        <f>J2-U2</f>
       </c>
       <c r="Y2" t="s">
         <v>38</v>
@@ -863,7 +863,7 @@
         <v>39</v>
       </c>
       <c r="AF2" s="3">
-        <f>IF($H2="","",V2-AE2)</f>
+        <f>V2-AE2</f>
       </c>
       <c r="AG2" t="s">
         <v>38</v>
@@ -872,7 +872,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="G3" s="3"/>
@@ -923,7 +923,7 @@
         <f>IF($H3="","",V3-AE3)</f>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="G4" s="3"/>
@@ -974,7 +974,7 @@
         <f>IF($H4="","",V4-AE4)</f>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="G5" s="3"/>
@@ -1025,7 +1025,7 @@
         <f>IF($H5="","",V5-AE5)</f>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="G6" s="3"/>
@@ -1076,7 +1076,7 @@
         <f>IF($H6="","",V6-AE6)</f>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="G7" s="3"/>
@@ -1127,7 +1127,7 @@
         <f>IF($H7="","",V7-AE7)</f>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="G8" s="3"/>
@@ -1178,7 +1178,7 @@
         <f>IF($H8="","",V8-AE8)</f>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="G9" s="3"/>
@@ -1229,7 +1229,7 @@
         <f>IF($H9="","",V9-AE9)</f>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="G10" s="3"/>
@@ -1280,7 +1280,7 @@
         <f>IF($H10="","",V10-AE10)</f>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="G11" s="3"/>
@@ -1331,7 +1331,7 @@
         <f>IF($H11="","",V11-AE11)</f>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="G12" s="3"/>
@@ -1382,7 +1382,7 @@
         <f>IF($H12="","",V12-AE12)</f>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="G13" s="3"/>
@@ -1433,7 +1433,7 @@
         <f>IF($H13="","",V13-AE13)</f>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="G14" s="3"/>
@@ -1484,7 +1484,7 @@
         <f>IF($H14="","",V14-AE14)</f>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="G15" s="3"/>
@@ -1535,7 +1535,7 @@
         <f>IF($H15="","",V15-AE15)</f>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="G16" s="3"/>
@@ -1586,7 +1586,7 @@
         <f>IF($H16="","",V16-AE16)</f>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="G17" s="3"/>
@@ -1637,7 +1637,7 @@
         <f>IF($H17="","",V17-AE17)</f>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="G18" s="3"/>
@@ -1688,7 +1688,7 @@
         <f>IF($H18="","",V18-AE18)</f>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="G19" s="3"/>
@@ -1739,7 +1739,7 @@
         <f>IF($H19="","",V19-AE19)</f>
       </c>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="G20" s="3"/>
@@ -1790,7 +1790,7 @@
         <f>IF($H20="","",V20-AE20)</f>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="G21" s="3"/>
@@ -1841,7 +1841,7 @@
         <f>IF($H21="","",V21-AE21)</f>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="G22" s="3"/>
@@ -1892,7 +1892,7 @@
         <f>IF($H22="","",V22-AE22)</f>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="G23" s="3"/>
@@ -1943,7 +1943,7 @@
         <f>IF($H23="","",V23-AE23)</f>
       </c>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="G24" s="3"/>
@@ -1994,7 +1994,7 @@
         <f>IF($H24="","",V24-AE24)</f>
       </c>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="G25" s="3"/>
@@ -2045,7 +2045,7 @@
         <f>IF($H25="","",V25-AE25)</f>
       </c>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="G26" s="3"/>
@@ -2096,7 +2096,7 @@
         <f>IF($H26="","",V26-AE26)</f>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="G27" s="3"/>
@@ -2147,7 +2147,7 @@
         <f>IF($H27="","",V27-AE27)</f>
       </c>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="G28" s="3"/>
@@ -2198,7 +2198,7 @@
         <f>IF($H28="","",V28-AE28)</f>
       </c>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="G29" s="3"/>
@@ -2249,7 +2249,7 @@
         <f>IF($H29="","",V29-AE29)</f>
       </c>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="G30" s="3"/>
@@ -2300,7 +2300,7 @@
         <f>IF($H30="","",V30-AE30)</f>
       </c>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="G31" s="3"/>
@@ -2351,7 +2351,7 @@
         <f>IF($H31="","",V31-AE31)</f>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="G32" s="3"/>
@@ -2402,7 +2402,7 @@
         <f>IF($H32="","",V32-AE32)</f>
       </c>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="G33" s="3"/>
@@ -2453,7 +2453,7 @@
         <f>IF($H33="","",V33-AE33)</f>
       </c>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="G34" s="3"/>
@@ -2504,7 +2504,7 @@
         <f>IF($H34="","",V34-AE34)</f>
       </c>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="G35" s="3"/>
@@ -2555,7 +2555,7 @@
         <f>IF($H35="","",V35-AE35)</f>
       </c>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="G36" s="3"/>
@@ -2606,7 +2606,7 @@
         <f>IF($H36="","",V36-AE36)</f>
       </c>
     </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="G37" s="3"/>
@@ -2657,7 +2657,7 @@
         <f>IF($H37="","",V37-AE37)</f>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="G38" s="3"/>
@@ -2708,7 +2708,7 @@
         <f>IF($H38="","",V38-AE38)</f>
       </c>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="G39" s="3"/>
@@ -2759,7 +2759,7 @@
         <f>IF($H39="","",V39-AE39)</f>
       </c>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="G40" s="3"/>
@@ -2810,7 +2810,7 @@
         <f>IF($H40="","",V40-AE40)</f>
       </c>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="G41" s="3"/>
@@ -2861,7 +2861,7 @@
         <f>IF($H41="","",V41-AE41)</f>
       </c>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="G42" s="3"/>
@@ -2912,7 +2912,7 @@
         <f>IF($H42="","",V42-AE42)</f>
       </c>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="G43" s="3"/>
@@ -2963,7 +2963,7 @@
         <f>IF($H43="","",V43-AE43)</f>
       </c>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="G44" s="3"/>
@@ -3014,7 +3014,7 @@
         <f>IF($H44="","",V44-AE44)</f>
       </c>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="G45" s="3"/>
@@ -3065,7 +3065,7 @@
         <f>IF($H45="","",V45-AE45)</f>
       </c>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="G46" s="3"/>
@@ -3116,7 +3116,7 @@
         <f>IF($H46="","",V46-AE46)</f>
       </c>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="G47" s="3"/>
@@ -3167,7 +3167,7 @@
         <f>IF($H47="","",V47-AE47)</f>
       </c>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="G48" s="3"/>
@@ -3218,7 +3218,7 @@
         <f>IF($H48="","",V48-AE48)</f>
       </c>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="G49" s="3"/>
@@ -3269,7 +3269,7 @@
         <f>IF($H49="","",V49-AE49)</f>
       </c>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="G50" s="3"/>
@@ -3320,7 +3320,7 @@
         <f>IF($H50="","",V50-AE50)</f>
       </c>
     </row>
-    <row r="51" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="G51" s="3"/>
@@ -3371,7 +3371,7 @@
         <f>IF($H51="","",V51-AE51)</f>
       </c>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="G52" s="3"/>
@@ -3422,7 +3422,7 @@
         <f>IF($H52="","",V52-AE52)</f>
       </c>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="G53" s="3"/>
@@ -3473,7 +3473,7 @@
         <f>IF($H53="","",V53-AE53)</f>
       </c>
     </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="G54" s="3"/>
@@ -3524,7 +3524,7 @@
         <f>IF($H54="","",V54-AE54)</f>
       </c>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="G55" s="3"/>
@@ -3575,7 +3575,7 @@
         <f>IF($H55="","",V55-AE55)</f>
       </c>
     </row>
-    <row r="56" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="G56" s="3"/>
@@ -3626,7 +3626,7 @@
         <f>IF($H56="","",V56-AE56)</f>
       </c>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="G57" s="3"/>
@@ -3677,7 +3677,7 @@
         <f>IF($H57="","",V57-AE57)</f>
       </c>
     </row>
-    <row r="58" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="G58" s="3"/>
@@ -3728,7 +3728,7 @@
         <f>IF($H58="","",V58-AE58)</f>
       </c>
     </row>
-    <row r="59" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="G59" s="3"/>
@@ -3779,7 +3779,7 @@
         <f>IF($H59="","",V59-AE59)</f>
       </c>
     </row>
-    <row r="60" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="G60" s="3"/>
@@ -3830,7 +3830,7 @@
         <f>IF($H60="","",V60-AE60)</f>
       </c>
     </row>
-    <row r="61" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="G61" s="3"/>
@@ -3881,7 +3881,7 @@
         <f>IF($H61="","",V61-AE61)</f>
       </c>
     </row>
-    <row r="62" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="G62" s="3"/>
@@ -3932,7 +3932,7 @@
         <f>IF($H62="","",V62-AE62)</f>
       </c>
     </row>
-    <row r="63" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="G63" s="3"/>
@@ -3983,7 +3983,7 @@
         <f>IF($H63="","",V63-AE63)</f>
       </c>
     </row>
-    <row r="64" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="G64" s="3"/>
@@ -4034,7 +4034,7 @@
         <f>IF($H64="","",V64-AE64)</f>
       </c>
     </row>
-    <row r="65" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="G65" s="3"/>
@@ -4085,7 +4085,7 @@
         <f>IF($H65="","",V65-AE65)</f>
       </c>
     </row>
-    <row r="66" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="G66" s="3"/>
@@ -4136,7 +4136,7 @@
         <f>IF($H66="","",V66-AE66)</f>
       </c>
     </row>
-    <row r="67" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="G67" s="3"/>
@@ -4187,7 +4187,7 @@
         <f>IF($H67="","",V67-AE67)</f>
       </c>
     </row>
-    <row r="68" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="G68" s="3"/>
@@ -4238,7 +4238,7 @@
         <f>IF($H68="","",V68-AE68)</f>
       </c>
     </row>
-    <row r="69" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="G69" s="3"/>
@@ -4289,7 +4289,7 @@
         <f>IF($H69="","",V69-AE69)</f>
       </c>
     </row>
-    <row r="70" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="G70" s="3"/>
@@ -4340,7 +4340,7 @@
         <f>IF($H70="","",V70-AE70)</f>
       </c>
     </row>
-    <row r="71" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="G71" s="3"/>
@@ -4391,7 +4391,7 @@
         <f>IF($H71="","",V71-AE71)</f>
       </c>
     </row>
-    <row r="72" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="G72" s="3"/>
@@ -4442,7 +4442,7 @@
         <f>IF($H72="","",V72-AE72)</f>
       </c>
     </row>
-    <row r="73" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="G73" s="3"/>
@@ -4493,7 +4493,7 @@
         <f>IF($H73="","",V73-AE73)</f>
       </c>
     </row>
-    <row r="74" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="G74" s="3"/>
@@ -4544,7 +4544,7 @@
         <f>IF($H74="","",V74-AE74)</f>
       </c>
     </row>
-    <row r="75" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="G75" s="3"/>
@@ -4595,7 +4595,7 @@
         <f>IF($H75="","",V75-AE75)</f>
       </c>
     </row>
-    <row r="76" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="G76" s="3"/>
@@ -4646,7 +4646,7 @@
         <f>IF($H76="","",V76-AE76)</f>
       </c>
     </row>
-    <row r="77" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="G77" s="3"/>
@@ -4697,7 +4697,7 @@
         <f>IF($H77="","",V77-AE77)</f>
       </c>
     </row>
-    <row r="78" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="G78" s="3"/>
@@ -4748,7 +4748,7 @@
         <f>IF($H78="","",V78-AE78)</f>
       </c>
     </row>
-    <row r="79" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="G79" s="3"/>
@@ -4799,7 +4799,7 @@
         <f>IF($H79="","",V79-AE79)</f>
       </c>
     </row>
-    <row r="80" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="G80" s="3"/>
@@ -4850,7 +4850,7 @@
         <f>IF($H80="","",V80-AE80)</f>
       </c>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="G81" s="3"/>
@@ -4901,7 +4901,7 @@
         <f>IF($H81="","",V81-AE81)</f>
       </c>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="G82" s="3"/>
@@ -4952,7 +4952,7 @@
         <f>IF($H82="","",V82-AE82)</f>
       </c>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="G83" s="3"/>
@@ -5003,7 +5003,7 @@
         <f>IF($H83="","",V83-AE83)</f>
       </c>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="G84" s="3"/>
@@ -5054,7 +5054,7 @@
         <f>IF($H84="","",V84-AE84)</f>
       </c>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="G85" s="3"/>
@@ -5105,7 +5105,7 @@
         <f>IF($H85="","",V85-AE85)</f>
       </c>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="G86" s="3"/>
@@ -5156,7 +5156,7 @@
         <f>IF($H86="","",V86-AE86)</f>
       </c>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="G87" s="3"/>
@@ -5207,7 +5207,7 @@
         <f>IF($H87="","",V87-AE87)</f>
       </c>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="G88" s="3"/>
@@ -5258,7 +5258,7 @@
         <f>IF($H88="","",V88-AE88)</f>
       </c>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="G89" s="3"/>
@@ -5309,7 +5309,7 @@
         <f>IF($H89="","",V89-AE89)</f>
       </c>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="G90" s="3"/>
@@ -5360,7 +5360,7 @@
         <f>IF($H90="","",V90-AE90)</f>
       </c>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="G91" s="3"/>
@@ -5411,7 +5411,7 @@
         <f>IF($H91="","",V91-AE91)</f>
       </c>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="G92" s="3"/>
@@ -5462,7 +5462,7 @@
         <f>IF($H92="","",V92-AE92)</f>
       </c>
     </row>
-    <row r="93" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="G93" s="3"/>
@@ -5513,7 +5513,7 @@
         <f>IF($H93="","",V93-AE93)</f>
       </c>
     </row>
-    <row r="94" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="G94" s="3"/>
@@ -5564,7 +5564,7 @@
         <f>IF($H94="","",V94-AE94)</f>
       </c>
     </row>
-    <row r="95" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="G95" s="3"/>
@@ -5615,7 +5615,7 @@
         <f>IF($H95="","",V95-AE95)</f>
       </c>
     </row>
-    <row r="96" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="G96" s="3"/>
@@ -5666,7 +5666,7 @@
         <f>IF($H96="","",V96-AE96)</f>
       </c>
     </row>
-    <row r="97" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="G97" s="3"/>
@@ -5717,7 +5717,7 @@
         <f>IF($H97="","",V97-AE97)</f>
       </c>
     </row>
-    <row r="98" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="G98" s="3"/>
@@ -5768,7 +5768,7 @@
         <f>IF($H98="","",V98-AE98)</f>
       </c>
     </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="G99" s="3"/>
@@ -5819,7 +5819,7 @@
         <f>IF($H99="","",V99-AE99)</f>
       </c>
     </row>
-    <row r="100" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="G100" s="3"/>
@@ -5870,7 +5870,7 @@
         <f>IF($H100="","",V100-AE100)</f>
       </c>
     </row>
-    <row r="101" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="G101" s="3"/>
@@ -5921,7 +5921,7 @@
         <f>IF($H101="","",V101-AE101)</f>
       </c>
     </row>
-    <row r="102" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="G102" s="3"/>
@@ -5972,7 +5972,7 @@
         <f>IF($H102="","",V102-AE102)</f>
       </c>
     </row>
-    <row r="103" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="G103" s="3"/>
@@ -6023,7 +6023,7 @@
         <f>IF($H103="","",V103-AE103)</f>
       </c>
     </row>
-    <row r="104" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="G104" s="3"/>
@@ -6074,7 +6074,7 @@
         <f>IF($H104="","",V104-AE104)</f>
       </c>
     </row>
-    <row r="105" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="G105" s="3"/>
@@ -6125,7 +6125,7 @@
         <f>IF($H105="","",V105-AE105)</f>
       </c>
     </row>
-    <row r="106" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="G106" s="3"/>
@@ -6176,7 +6176,7 @@
         <f>IF($H106="","",V106-AE106)</f>
       </c>
     </row>
-    <row r="107" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="G107" s="3"/>
@@ -6227,7 +6227,7 @@
         <f>IF($H107="","",V107-AE107)</f>
       </c>
     </row>
-    <row r="108" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="G108" s="3"/>
@@ -6278,7 +6278,7 @@
         <f>IF($H108="","",V108-AE108)</f>
       </c>
     </row>
-    <row r="109" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="G109" s="3"/>
@@ -6329,7 +6329,7 @@
         <f>IF($H109="","",V109-AE109)</f>
       </c>
     </row>
-    <row r="110" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="G110" s="3"/>
@@ -6380,7 +6380,7 @@
         <f>IF($H110="","",V110-AE110)</f>
       </c>
     </row>
-    <row r="111" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="G111" s="3"/>
@@ -6431,7 +6431,7 @@
         <f>IF($H111="","",V111-AE111)</f>
       </c>
     </row>
-    <row r="112" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="G112" s="3"/>
@@ -6482,7 +6482,7 @@
         <f>IF($H112="","",V112-AE112)</f>
       </c>
     </row>
-    <row r="113" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="G113" s="3"/>
@@ -6533,7 +6533,7 @@
         <f>IF($H113="","",V113-AE113)</f>
       </c>
     </row>
-    <row r="114" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="G114" s="3"/>
@@ -6584,7 +6584,7 @@
         <f>IF($H114="","",V114-AE114)</f>
       </c>
     </row>
-    <row r="115" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="G115" s="3"/>
@@ -6635,7 +6635,7 @@
         <f>IF($H115="","",V115-AE115)</f>
       </c>
     </row>
-    <row r="116" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="G116" s="3"/>
@@ -6686,7 +6686,7 @@
         <f>IF($H116="","",V116-AE116)</f>
       </c>
     </row>
-    <row r="117" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="G117" s="3"/>
@@ -6737,7 +6737,7 @@
         <f>IF($H117="","",V117-AE117)</f>
       </c>
     </row>
-    <row r="118" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="G118" s="3"/>
@@ -6788,7 +6788,7 @@
         <f>IF($H118="","",V118-AE118)</f>
       </c>
     </row>
-    <row r="119" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="G119" s="3"/>
@@ -6839,7 +6839,7 @@
         <f>IF($H119="","",V119-AE119)</f>
       </c>
     </row>
-    <row r="120" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="G120" s="3"/>
@@ -6890,7 +6890,7 @@
         <f>IF($H120="","",V120-AE120)</f>
       </c>
     </row>
-    <row r="121" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="G121" s="3"/>
@@ -6941,7 +6941,7 @@
         <f>IF($H121="","",V121-AE121)</f>
       </c>
     </row>
-    <row r="122" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="G122" s="3"/>
@@ -6992,7 +6992,7 @@
         <f>IF($H122="","",V122-AE122)</f>
       </c>
     </row>
-    <row r="123" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="G123" s="3"/>
@@ -7043,7 +7043,7 @@
         <f>IF($H123="","",V123-AE123)</f>
       </c>
     </row>
-    <row r="124" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="G124" s="3"/>
@@ -7094,7 +7094,7 @@
         <f>IF($H124="","",V124-AE124)</f>
       </c>
     </row>
-    <row r="125" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="G125" s="3"/>
@@ -7145,7 +7145,7 @@
         <f>IF($H125="","",V125-AE125)</f>
       </c>
     </row>
-    <row r="126" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="G126" s="3"/>
@@ -7196,7 +7196,7 @@
         <f>IF($H126="","",V126-AE126)</f>
       </c>
     </row>
-    <row r="127" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="G127" s="3"/>
@@ -7247,7 +7247,7 @@
         <f>IF($H127="","",V127-AE127)</f>
       </c>
     </row>
-    <row r="128" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="G128" s="3"/>
@@ -7298,7 +7298,7 @@
         <f>IF($H128="","",V128-AE128)</f>
       </c>
     </row>
-    <row r="129" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="G129" s="3"/>
@@ -7349,7 +7349,7 @@
         <f>IF($H129="","",V129-AE129)</f>
       </c>
     </row>
-    <row r="130" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="G130" s="3"/>
@@ -7400,7 +7400,7 @@
         <f>IF($H130="","",V130-AE130)</f>
       </c>
     </row>
-    <row r="131" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="G131" s="3"/>
@@ -7451,7 +7451,7 @@
         <f>IF($H131="","",V131-AE131)</f>
       </c>
     </row>
-    <row r="132" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="G132" s="3"/>
@@ -7502,7 +7502,7 @@
         <f>IF($H132="","",V132-AE132)</f>
       </c>
     </row>
-    <row r="133" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="G133" s="3"/>
@@ -7553,7 +7553,7 @@
         <f>IF($H133="","",V133-AE133)</f>
       </c>
     </row>
-    <row r="134" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="G134" s="3"/>
@@ -7604,7 +7604,7 @@
         <f>IF($H134="","",V134-AE134)</f>
       </c>
     </row>
-    <row r="135" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="G135" s="3"/>
@@ -7655,7 +7655,7 @@
         <f>IF($H135="","",V135-AE135)</f>
       </c>
     </row>
-    <row r="136" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="G136" s="3"/>
@@ -7706,7 +7706,7 @@
         <f>IF($H136="","",V136-AE136)</f>
       </c>
     </row>
-    <row r="137" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="G137" s="3"/>
@@ -7757,7 +7757,7 @@
         <f>IF($H137="","",V137-AE137)</f>
       </c>
     </row>
-    <row r="138" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="G138" s="3"/>
@@ -7808,7 +7808,7 @@
         <f>IF($H138="","",V138-AE138)</f>
       </c>
     </row>
-    <row r="139" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="G139" s="3"/>
@@ -7859,7 +7859,7 @@
         <f>IF($H139="","",V139-AE139)</f>
       </c>
     </row>
-    <row r="140" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="G140" s="3"/>
@@ -7910,7 +7910,7 @@
         <f>IF($H140="","",V140-AE140)</f>
       </c>
     </row>
-    <row r="141" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="G141" s="3"/>
@@ -7961,7 +7961,7 @@
         <f>IF($H141="","",V141-AE141)</f>
       </c>
     </row>
-    <row r="142" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="G142" s="3"/>
@@ -8012,7 +8012,7 @@
         <f>IF($H142="","",V142-AE142)</f>
       </c>
     </row>
-    <row r="143" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="G143" s="3"/>
@@ -8063,7 +8063,7 @@
         <f>IF($H143="","",V143-AE143)</f>
       </c>
     </row>
-    <row r="144" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="G144" s="3"/>
@@ -8114,7 +8114,7 @@
         <f>IF($H144="","",V144-AE144)</f>
       </c>
     </row>
-    <row r="145" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="G145" s="3"/>
@@ -8165,7 +8165,7 @@
         <f>IF($H145="","",V145-AE145)</f>
       </c>
     </row>
-    <row r="146" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="G146" s="3"/>
@@ -8216,7 +8216,7 @@
         <f>IF($H146="","",V146-AE146)</f>
       </c>
     </row>
-    <row r="147" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="G147" s="3"/>
@@ -8267,7 +8267,7 @@
         <f>IF($H147="","",V147-AE147)</f>
       </c>
     </row>
-    <row r="148" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="G148" s="3"/>
@@ -8318,7 +8318,7 @@
         <f>IF($H148="","",V148-AE148)</f>
       </c>
     </row>
-    <row r="149" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="G149" s="3"/>
@@ -8369,7 +8369,7 @@
         <f>IF($H149="","",V149-AE149)</f>
       </c>
     </row>
-    <row r="150" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="G150" s="3"/>
@@ -8420,7 +8420,7 @@
         <f>IF($H150="","",V150-AE150)</f>
       </c>
     </row>
-    <row r="151" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="G151" s="3"/>
@@ -8471,7 +8471,7 @@
         <f>IF($H151="","",V151-AE151)</f>
       </c>
     </row>
-    <row r="152" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="G152" s="3"/>
@@ -8522,7 +8522,7 @@
         <f>IF($H152="","",V152-AE152)</f>
       </c>
     </row>
-    <row r="153" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="G153" s="3"/>
@@ -8573,7 +8573,7 @@
         <f>IF($H153="","",V153-AE153)</f>
       </c>
     </row>
-    <row r="154" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="G154" s="3"/>
@@ -8624,7 +8624,7 @@
         <f>IF($H154="","",V154-AE154)</f>
       </c>
     </row>
-    <row r="155" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="G155" s="3"/>
@@ -8675,7 +8675,7 @@
         <f>IF($H155="","",V155-AE155)</f>
       </c>
     </row>
-    <row r="156" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="G156" s="3"/>
@@ -8726,7 +8726,7 @@
         <f>IF($H156="","",V156-AE156)</f>
       </c>
     </row>
-    <row r="157" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="G157" s="3"/>
@@ -8777,7 +8777,7 @@
         <f>IF($H157="","",V157-AE157)</f>
       </c>
     </row>
-    <row r="158" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="G158" s="3"/>
@@ -8828,7 +8828,7 @@
         <f>IF($H158="","",V158-AE158)</f>
       </c>
     </row>
-    <row r="159" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="G159" s="3"/>
@@ -8879,7 +8879,7 @@
         <f>IF($H159="","",V159-AE159)</f>
       </c>
     </row>
-    <row r="160" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="G160" s="3"/>
@@ -8930,7 +8930,7 @@
         <f>IF($H160="","",V160-AE160)</f>
       </c>
     </row>
-    <row r="161" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="G161" s="3"/>
@@ -8981,7 +8981,7 @@
         <f>IF($H161="","",V161-AE161)</f>
       </c>
     </row>
-    <row r="162" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="G162" s="3"/>
@@ -9032,7 +9032,7 @@
         <f>IF($H162="","",V162-AE162)</f>
       </c>
     </row>
-    <row r="163" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="G163" s="3"/>
@@ -9083,7 +9083,7 @@
         <f>IF($H163="","",V163-AE163)</f>
       </c>
     </row>
-    <row r="164" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="G164" s="3"/>
@@ -9134,7 +9134,7 @@
         <f>IF($H164="","",V164-AE164)</f>
       </c>
     </row>
-    <row r="165" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="G165" s="3"/>
@@ -9185,7 +9185,7 @@
         <f>IF($H165="","",V165-AE165)</f>
       </c>
     </row>
-    <row r="166" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="G166" s="3"/>
@@ -9236,7 +9236,7 @@
         <f>IF($H166="","",V166-AE166)</f>
       </c>
     </row>
-    <row r="167" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="G167" s="3"/>
@@ -9287,7 +9287,7 @@
         <f>IF($H167="","",V167-AE167)</f>
       </c>
     </row>
-    <row r="168" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="G168" s="3"/>
@@ -9338,7 +9338,7 @@
         <f>IF($H168="","",V168-AE168)</f>
       </c>
     </row>
-    <row r="169" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="G169" s="3"/>
@@ -9389,7 +9389,7 @@
         <f>IF($H169="","",V169-AE169)</f>
       </c>
     </row>
-    <row r="170" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="G170" s="3"/>
@@ -9440,7 +9440,7 @@
         <f>IF($H170="","",V170-AE170)</f>
       </c>
     </row>
-    <row r="171" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="G171" s="3"/>
@@ -9491,7 +9491,7 @@
         <f>IF($H171="","",V171-AE171)</f>
       </c>
     </row>
-    <row r="172" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="G172" s="3"/>
@@ -9542,7 +9542,7 @@
         <f>IF($H172="","",V172-AE172)</f>
       </c>
     </row>
-    <row r="173" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="G173" s="3"/>
@@ -9593,7 +9593,7 @@
         <f>IF($H173="","",V173-AE173)</f>
       </c>
     </row>
-    <row r="174" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="G174" s="3"/>
@@ -9644,7 +9644,7 @@
         <f>IF($H174="","",V174-AE174)</f>
       </c>
     </row>
-    <row r="175" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="G175" s="3"/>
@@ -9695,7 +9695,7 @@
         <f>IF($H175="","",V175-AE175)</f>
       </c>
     </row>
-    <row r="176" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="G176" s="3"/>
@@ -9746,7 +9746,7 @@
         <f>IF($H176="","",V176-AE176)</f>
       </c>
     </row>
-    <row r="177" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="G177" s="3"/>
@@ -9797,7 +9797,7 @@
         <f>IF($H177="","",V177-AE177)</f>
       </c>
     </row>
-    <row r="178" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="G178" s="3"/>
@@ -9848,7 +9848,7 @@
         <f>IF($H178="","",V178-AE178)</f>
       </c>
     </row>
-    <row r="179" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="G179" s="3"/>
@@ -9899,7 +9899,7 @@
         <f>IF($H179="","",V179-AE179)</f>
       </c>
     </row>
-    <row r="180" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="G180" s="3"/>
@@ -9950,7 +9950,7 @@
         <f>IF($H180="","",V180-AE180)</f>
       </c>
     </row>
-    <row r="181" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="G181" s="3"/>
@@ -10001,7 +10001,7 @@
         <f>IF($H181="","",V181-AE181)</f>
       </c>
     </row>
-    <row r="182" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="G182" s="3"/>
@@ -10052,7 +10052,7 @@
         <f>IF($H182="","",V182-AE182)</f>
       </c>
     </row>
-    <row r="183" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="G183" s="3"/>
@@ -10103,7 +10103,7 @@
         <f>IF($H183="","",V183-AE183)</f>
       </c>
     </row>
-    <row r="184" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="G184" s="3"/>
@@ -10154,7 +10154,7 @@
         <f>IF($H184="","",V184-AE184)</f>
       </c>
     </row>
-    <row r="185" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="G185" s="3"/>
@@ -10205,7 +10205,7 @@
         <f>IF($H185="","",V185-AE185)</f>
       </c>
     </row>
-    <row r="186" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="G186" s="3"/>
@@ -10256,7 +10256,7 @@
         <f>IF($H186="","",V186-AE186)</f>
       </c>
     </row>
-    <row r="187" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="G187" s="3"/>
@@ -10307,7 +10307,7 @@
         <f>IF($H187="","",V187-AE187)</f>
       </c>
     </row>
-    <row r="188" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="G188" s="3"/>
@@ -10358,7 +10358,7 @@
         <f>IF($H188="","",V188-AE188)</f>
       </c>
     </row>
-    <row r="189" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="G189" s="3"/>
@@ -10409,7 +10409,7 @@
         <f>IF($H189="","",V189-AE189)</f>
       </c>
     </row>
-    <row r="190" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="G190" s="3"/>
@@ -10460,7 +10460,7 @@
         <f>IF($H190="","",V190-AE190)</f>
       </c>
     </row>
-    <row r="191" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="G191" s="3"/>
@@ -10511,7 +10511,7 @@
         <f>IF($H191="","",V191-AE191)</f>
       </c>
     </row>
-    <row r="192" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="G192" s="3"/>
@@ -10562,7 +10562,7 @@
         <f>IF($H192="","",V192-AE192)</f>
       </c>
     </row>
-    <row r="193" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="G193" s="3"/>
@@ -10613,7 +10613,7 @@
         <f>IF($H193="","",V193-AE193)</f>
       </c>
     </row>
-    <row r="194" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="G194" s="3"/>
@@ -10664,7 +10664,7 @@
         <f>IF($H194="","",V194-AE194)</f>
       </c>
     </row>
-    <row r="195" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="G195" s="3"/>
@@ -10715,7 +10715,7 @@
         <f>IF($H195="","",V195-AE195)</f>
       </c>
     </row>
-    <row r="196" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="G196" s="3"/>
@@ -10766,7 +10766,7 @@
         <f>IF($H196="","",V196-AE196)</f>
       </c>
     </row>
-    <row r="197" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="G197" s="3"/>
@@ -10817,7 +10817,7 @@
         <f>IF($H197="","",V197-AE197)</f>
       </c>
     </row>
-    <row r="198" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="G198" s="3"/>
@@ -10868,7 +10868,7 @@
         <f>IF($H198="","",V198-AE198)</f>
       </c>
     </row>
-    <row r="199" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="G199" s="3"/>
@@ -10919,7 +10919,7 @@
         <f>IF($H199="","",V199-AE199)</f>
       </c>
     </row>
-    <row r="200" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="G200" s="3"/>
@@ -10970,7 +10970,7 @@
         <f>IF($H200="","",V200-AE200)</f>
       </c>
     </row>
-    <row r="201" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="G201" s="3"/>
@@ -11021,7 +11021,7 @@
         <f>IF($H201="","",V201-AE201)</f>
       </c>
     </row>
-    <row r="202" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="G202" s="3"/>

--- a/public/templates/SALES_EBAY_TEMPLATE.xlsx
+++ b/public/templates/SALES_EBAY_TEMPLATE.xlsx
@@ -860,7 +860,7 @@
         <f>L2-M2-R2-S2-T2-U2-V2-W2</f>
       </c>
       <c r="Z2" s="3">
-        <f>(Y2-AB2)/K2*100</f>
+        <f>(Y2-AB2)/J2*100</f>
       </c>
       <c r="AA2" s="3">
         <f>M2-X2</f>
@@ -914,7 +914,7 @@
         <f>IF($K3="","",L3-M3-R3-S3-T3-U3-V3-W3)</f>
       </c>
       <c r="Z3" s="3">
-        <f>IF($K3="","",(Y3-AB3)/K3*100)</f>
+        <f>IF($K3="","",(Y3-AB3)/J3*100)</f>
       </c>
       <c r="AA3" s="3">
         <f>IF($K3="","",M3-X3)</f>
@@ -965,7 +965,7 @@
         <f>IF($K4="","",L4-M4-R4-S4-T4-U4-V4-W4)</f>
       </c>
       <c r="Z4" s="3">
-        <f>IF($K4="","",(Y4-AB4)/K4*100)</f>
+        <f>IF($K4="","",(Y4-AB4)/J4*100)</f>
       </c>
       <c r="AA4" s="3">
         <f>IF($K4="","",M4-X4)</f>
@@ -1016,7 +1016,7 @@
         <f>IF($K5="","",L5-M5-R5-S5-T5-U5-V5-W5)</f>
       </c>
       <c r="Z5" s="3">
-        <f>IF($K5="","",(Y5-AB5)/K5*100)</f>
+        <f>IF($K5="","",(Y5-AB5)/J5*100)</f>
       </c>
       <c r="AA5" s="3">
         <f>IF($K5="","",M5-X5)</f>
@@ -1067,7 +1067,7 @@
         <f>IF($K6="","",L6-M6-R6-S6-T6-U6-V6-W6)</f>
       </c>
       <c r="Z6" s="3">
-        <f>IF($K6="","",(Y6-AB6)/K6*100)</f>
+        <f>IF($K6="","",(Y6-AB6)/J6*100)</f>
       </c>
       <c r="AA6" s="3">
         <f>IF($K6="","",M6-X6)</f>
@@ -1118,7 +1118,7 @@
         <f>IF($K7="","",L7-M7-R7-S7-T7-U7-V7-W7)</f>
       </c>
       <c r="Z7" s="3">
-        <f>IF($K7="","",(Y7-AB7)/K7*100)</f>
+        <f>IF($K7="","",(Y7-AB7)/J7*100)</f>
       </c>
       <c r="AA7" s="3">
         <f>IF($K7="","",M7-X7)</f>
@@ -1169,7 +1169,7 @@
         <f>IF($K8="","",L8-M8-R8-S8-T8-U8-V8-W8)</f>
       </c>
       <c r="Z8" s="3">
-        <f>IF($K8="","",(Y8-AB8)/K8*100)</f>
+        <f>IF($K8="","",(Y8-AB8)/J8*100)</f>
       </c>
       <c r="AA8" s="3">
         <f>IF($K8="","",M8-X8)</f>
@@ -1220,7 +1220,7 @@
         <f>IF($K9="","",L9-M9-R9-S9-T9-U9-V9-W9)</f>
       </c>
       <c r="Z9" s="3">
-        <f>IF($K9="","",(Y9-AB9)/K9*100)</f>
+        <f>IF($K9="","",(Y9-AB9)/J9*100)</f>
       </c>
       <c r="AA9" s="3">
         <f>IF($K9="","",M9-X9)</f>
@@ -1271,7 +1271,7 @@
         <f>IF($K10="","",L10-M10-R10-S10-T10-U10-V10-W10)</f>
       </c>
       <c r="Z10" s="3">
-        <f>IF($K10="","",(Y10-AB10)/K10*100)</f>
+        <f>IF($K10="","",(Y10-AB10)/J10*100)</f>
       </c>
       <c r="AA10" s="3">
         <f>IF($K10="","",M10-X10)</f>
@@ -1322,7 +1322,7 @@
         <f>IF($K11="","",L11-M11-R11-S11-T11-U11-V11-W11)</f>
       </c>
       <c r="Z11" s="3">
-        <f>IF($K11="","",(Y11-AB11)/K11*100)</f>
+        <f>IF($K11="","",(Y11-AB11)/J11*100)</f>
       </c>
       <c r="AA11" s="3">
         <f>IF($K11="","",M11-X11)</f>
@@ -1373,7 +1373,7 @@
         <f>IF($K12="","",L12-M12-R12-S12-T12-U12-V12-W12)</f>
       </c>
       <c r="Z12" s="3">
-        <f>IF($K12="","",(Y12-AB12)/K12*100)</f>
+        <f>IF($K12="","",(Y12-AB12)/J12*100)</f>
       </c>
       <c r="AA12" s="3">
         <f>IF($K12="","",M12-X12)</f>
@@ -1424,7 +1424,7 @@
         <f>IF($K13="","",L13-M13-R13-S13-T13-U13-V13-W13)</f>
       </c>
       <c r="Z13" s="3">
-        <f>IF($K13="","",(Y13-AB13)/K13*100)</f>
+        <f>IF($K13="","",(Y13-AB13)/J13*100)</f>
       </c>
       <c r="AA13" s="3">
         <f>IF($K13="","",M13-X13)</f>
@@ -1475,7 +1475,7 @@
         <f>IF($K14="","",L14-M14-R14-S14-T14-U14-V14-W14)</f>
       </c>
       <c r="Z14" s="3">
-        <f>IF($K14="","",(Y14-AB14)/K14*100)</f>
+        <f>IF($K14="","",(Y14-AB14)/J14*100)</f>
       </c>
       <c r="AA14" s="3">
         <f>IF($K14="","",M14-X14)</f>
@@ -1526,7 +1526,7 @@
         <f>IF($K15="","",L15-M15-R15-S15-T15-U15-V15-W15)</f>
       </c>
       <c r="Z15" s="3">
-        <f>IF($K15="","",(Y15-AB15)/K15*100)</f>
+        <f>IF($K15="","",(Y15-AB15)/J15*100)</f>
       </c>
       <c r="AA15" s="3">
         <f>IF($K15="","",M15-X15)</f>
@@ -1577,7 +1577,7 @@
         <f>IF($K16="","",L16-M16-R16-S16-T16-U16-V16-W16)</f>
       </c>
       <c r="Z16" s="3">
-        <f>IF($K16="","",(Y16-AB16)/K16*100)</f>
+        <f>IF($K16="","",(Y16-AB16)/J16*100)</f>
       </c>
       <c r="AA16" s="3">
         <f>IF($K16="","",M16-X16)</f>
@@ -1628,7 +1628,7 @@
         <f>IF($K17="","",L17-M17-R17-S17-T17-U17-V17-W17)</f>
       </c>
       <c r="Z17" s="3">
-        <f>IF($K17="","",(Y17-AB17)/K17*100)</f>
+        <f>IF($K17="","",(Y17-AB17)/J17*100)</f>
       </c>
       <c r="AA17" s="3">
         <f>IF($K17="","",M17-X17)</f>
@@ -1679,7 +1679,7 @@
         <f>IF($K18="","",L18-M18-R18-S18-T18-U18-V18-W18)</f>
       </c>
       <c r="Z18" s="3">
-        <f>IF($K18="","",(Y18-AB18)/K18*100)</f>
+        <f>IF($K18="","",(Y18-AB18)/J18*100)</f>
       </c>
       <c r="AA18" s="3">
         <f>IF($K18="","",M18-X18)</f>
@@ -1730,7 +1730,7 @@
         <f>IF($K19="","",L19-M19-R19-S19-T19-U19-V19-W19)</f>
       </c>
       <c r="Z19" s="3">
-        <f>IF($K19="","",(Y19-AB19)/K19*100)</f>
+        <f>IF($K19="","",(Y19-AB19)/J19*100)</f>
       </c>
       <c r="AA19" s="3">
         <f>IF($K19="","",M19-X19)</f>
@@ -1781,7 +1781,7 @@
         <f>IF($K20="","",L20-M20-R20-S20-T20-U20-V20-W20)</f>
       </c>
       <c r="Z20" s="3">
-        <f>IF($K20="","",(Y20-AB20)/K20*100)</f>
+        <f>IF($K20="","",(Y20-AB20)/J20*100)</f>
       </c>
       <c r="AA20" s="3">
         <f>IF($K20="","",M20-X20)</f>
@@ -1832,7 +1832,7 @@
         <f>IF($K21="","",L21-M21-R21-S21-T21-U21-V21-W21)</f>
       </c>
       <c r="Z21" s="3">
-        <f>IF($K21="","",(Y21-AB21)/K21*100)</f>
+        <f>IF($K21="","",(Y21-AB21)/J21*100)</f>
       </c>
       <c r="AA21" s="3">
         <f>IF($K21="","",M21-X21)</f>
@@ -1883,7 +1883,7 @@
         <f>IF($K22="","",L22-M22-R22-S22-T22-U22-V22-W22)</f>
       </c>
       <c r="Z22" s="3">
-        <f>IF($K22="","",(Y22-AB22)/K22*100)</f>
+        <f>IF($K22="","",(Y22-AB22)/J22*100)</f>
       </c>
       <c r="AA22" s="3">
         <f>IF($K22="","",M22-X22)</f>
@@ -1934,7 +1934,7 @@
         <f>IF($K23="","",L23-M23-R23-S23-T23-U23-V23-W23)</f>
       </c>
       <c r="Z23" s="3">
-        <f>IF($K23="","",(Y23-AB23)/K23*100)</f>
+        <f>IF($K23="","",(Y23-AB23)/J23*100)</f>
       </c>
       <c r="AA23" s="3">
         <f>IF($K23="","",M23-X23)</f>
@@ -1985,7 +1985,7 @@
         <f>IF($K24="","",L24-M24-R24-S24-T24-U24-V24-W24)</f>
       </c>
       <c r="Z24" s="3">
-        <f>IF($K24="","",(Y24-AB24)/K24*100)</f>
+        <f>IF($K24="","",(Y24-AB24)/J24*100)</f>
       </c>
       <c r="AA24" s="3">
         <f>IF($K24="","",M24-X24)</f>
@@ -2036,7 +2036,7 @@
         <f>IF($K25="","",L25-M25-R25-S25-T25-U25-V25-W25)</f>
       </c>
       <c r="Z25" s="3">
-        <f>IF($K25="","",(Y25-AB25)/K25*100)</f>
+        <f>IF($K25="","",(Y25-AB25)/J25*100)</f>
       </c>
       <c r="AA25" s="3">
         <f>IF($K25="","",M25-X25)</f>
@@ -2087,7 +2087,7 @@
         <f>IF($K26="","",L26-M26-R26-S26-T26-U26-V26-W26)</f>
       </c>
       <c r="Z26" s="3">
-        <f>IF($K26="","",(Y26-AB26)/K26*100)</f>
+        <f>IF($K26="","",(Y26-AB26)/J26*100)</f>
       </c>
       <c r="AA26" s="3">
         <f>IF($K26="","",M26-X26)</f>
@@ -2138,7 +2138,7 @@
         <f>IF($K27="","",L27-M27-R27-S27-T27-U27-V27-W27)</f>
       </c>
       <c r="Z27" s="3">
-        <f>IF($K27="","",(Y27-AB27)/K27*100)</f>
+        <f>IF($K27="","",(Y27-AB27)/J27*100)</f>
       </c>
       <c r="AA27" s="3">
         <f>IF($K27="","",M27-X27)</f>
@@ -2189,7 +2189,7 @@
         <f>IF($K28="","",L28-M28-R28-S28-T28-U28-V28-W28)</f>
       </c>
       <c r="Z28" s="3">
-        <f>IF($K28="","",(Y28-AB28)/K28*100)</f>
+        <f>IF($K28="","",(Y28-AB28)/J28*100)</f>
       </c>
       <c r="AA28" s="3">
         <f>IF($K28="","",M28-X28)</f>
@@ -2240,7 +2240,7 @@
         <f>IF($K29="","",L29-M29-R29-S29-T29-U29-V29-W29)</f>
       </c>
       <c r="Z29" s="3">
-        <f>IF($K29="","",(Y29-AB29)/K29*100)</f>
+        <f>IF($K29="","",(Y29-AB29)/J29*100)</f>
       </c>
       <c r="AA29" s="3">
         <f>IF($K29="","",M29-X29)</f>
@@ -2291,7 +2291,7 @@
         <f>IF($K30="","",L30-M30-R30-S30-T30-U30-V30-W30)</f>
       </c>
       <c r="Z30" s="3">
-        <f>IF($K30="","",(Y30-AB30)/K30*100)</f>
+        <f>IF($K30="","",(Y30-AB30)/J30*100)</f>
       </c>
       <c r="AA30" s="3">
         <f>IF($K30="","",M30-X30)</f>
@@ -2342,7 +2342,7 @@
         <f>IF($K31="","",L31-M31-R31-S31-T31-U31-V31-W31)</f>
       </c>
       <c r="Z31" s="3">
-        <f>IF($K31="","",(Y31-AB31)/K31*100)</f>
+        <f>IF($K31="","",(Y31-AB31)/J31*100)</f>
       </c>
       <c r="AA31" s="3">
         <f>IF($K31="","",M31-X31)</f>
@@ -2393,7 +2393,7 @@
         <f>IF($K32="","",L32-M32-R32-S32-T32-U32-V32-W32)</f>
       </c>
       <c r="Z32" s="3">
-        <f>IF($K32="","",(Y32-AB32)/K32*100)</f>
+        <f>IF($K32="","",(Y32-AB32)/J32*100)</f>
       </c>
       <c r="AA32" s="3">
         <f>IF($K32="","",M32-X32)</f>
@@ -2444,7 +2444,7 @@
         <f>IF($K33="","",L33-M33-R33-S33-T33-U33-V33-W33)</f>
       </c>
       <c r="Z33" s="3">
-        <f>IF($K33="","",(Y33-AB33)/K33*100)</f>
+        <f>IF($K33="","",(Y33-AB33)/J33*100)</f>
       </c>
       <c r="AA33" s="3">
         <f>IF($K33="","",M33-X33)</f>
@@ -2495,7 +2495,7 @@
         <f>IF($K34="","",L34-M34-R34-S34-T34-U34-V34-W34)</f>
       </c>
       <c r="Z34" s="3">
-        <f>IF($K34="","",(Y34-AB34)/K34*100)</f>
+        <f>IF($K34="","",(Y34-AB34)/J34*100)</f>
       </c>
       <c r="AA34" s="3">
         <f>IF($K34="","",M34-X34)</f>
@@ -2546,7 +2546,7 @@
         <f>IF($K35="","",L35-M35-R35-S35-T35-U35-V35-W35)</f>
       </c>
       <c r="Z35" s="3">
-        <f>IF($K35="","",(Y35-AB35)/K35*100)</f>
+        <f>IF($K35="","",(Y35-AB35)/J35*100)</f>
       </c>
       <c r="AA35" s="3">
         <f>IF($K35="","",M35-X35)</f>
@@ -2597,7 +2597,7 @@
         <f>IF($K36="","",L36-M36-R36-S36-T36-U36-V36-W36)</f>
       </c>
       <c r="Z36" s="3">
-        <f>IF($K36="","",(Y36-AB36)/K36*100)</f>
+        <f>IF($K36="","",(Y36-AB36)/J36*100)</f>
       </c>
       <c r="AA36" s="3">
         <f>IF($K36="","",M36-X36)</f>
@@ -2648,7 +2648,7 @@
         <f>IF($K37="","",L37-M37-R37-S37-T37-U37-V37-W37)</f>
       </c>
       <c r="Z37" s="3">
-        <f>IF($K37="","",(Y37-AB37)/K37*100)</f>
+        <f>IF($K37="","",(Y37-AB37)/J37*100)</f>
       </c>
       <c r="AA37" s="3">
         <f>IF($K37="","",M37-X37)</f>
@@ -2699,7 +2699,7 @@
         <f>IF($K38="","",L38-M38-R38-S38-T38-U38-V38-W38)</f>
       </c>
       <c r="Z38" s="3">
-        <f>IF($K38="","",(Y38-AB38)/K38*100)</f>
+        <f>IF($K38="","",(Y38-AB38)/J38*100)</f>
       </c>
       <c r="AA38" s="3">
         <f>IF($K38="","",M38-X38)</f>
@@ -2750,7 +2750,7 @@
         <f>IF($K39="","",L39-M39-R39-S39-T39-U39-V39-W39)</f>
       </c>
       <c r="Z39" s="3">
-        <f>IF($K39="","",(Y39-AB39)/K39*100)</f>
+        <f>IF($K39="","",(Y39-AB39)/J39*100)</f>
       </c>
       <c r="AA39" s="3">
         <f>IF($K39="","",M39-X39)</f>
@@ -2801,7 +2801,7 @@
         <f>IF($K40="","",L40-M40-R40-S40-T40-U40-V40-W40)</f>
       </c>
       <c r="Z40" s="3">
-        <f>IF($K40="","",(Y40-AB40)/K40*100)</f>
+        <f>IF($K40="","",(Y40-AB40)/J40*100)</f>
       </c>
       <c r="AA40" s="3">
         <f>IF($K40="","",M40-X40)</f>
@@ -2852,7 +2852,7 @@
         <f>IF($K41="","",L41-M41-R41-S41-T41-U41-V41-W41)</f>
       </c>
       <c r="Z41" s="3">
-        <f>IF($K41="","",(Y41-AB41)/K41*100)</f>
+        <f>IF($K41="","",(Y41-AB41)/J41*100)</f>
       </c>
       <c r="AA41" s="3">
         <f>IF($K41="","",M41-X41)</f>
@@ -2903,7 +2903,7 @@
         <f>IF($K42="","",L42-M42-R42-S42-T42-U42-V42-W42)</f>
       </c>
       <c r="Z42" s="3">
-        <f>IF($K42="","",(Y42-AB42)/K42*100)</f>
+        <f>IF($K42="","",(Y42-AB42)/J42*100)</f>
       </c>
       <c r="AA42" s="3">
         <f>IF($K42="","",M42-X42)</f>
@@ -2954,7 +2954,7 @@
         <f>IF($K43="","",L43-M43-R43-S43-T43-U43-V43-W43)</f>
       </c>
       <c r="Z43" s="3">
-        <f>IF($K43="","",(Y43-AB43)/K43*100)</f>
+        <f>IF($K43="","",(Y43-AB43)/J43*100)</f>
       </c>
       <c r="AA43" s="3">
         <f>IF($K43="","",M43-X43)</f>
@@ -3005,7 +3005,7 @@
         <f>IF($K44="","",L44-M44-R44-S44-T44-U44-V44-W44)</f>
       </c>
       <c r="Z44" s="3">
-        <f>IF($K44="","",(Y44-AB44)/K44*100)</f>
+        <f>IF($K44="","",(Y44-AB44)/J44*100)</f>
       </c>
       <c r="AA44" s="3">
         <f>IF($K44="","",M44-X44)</f>
@@ -3056,7 +3056,7 @@
         <f>IF($K45="","",L45-M45-R45-S45-T45-U45-V45-W45)</f>
       </c>
       <c r="Z45" s="3">
-        <f>IF($K45="","",(Y45-AB45)/K45*100)</f>
+        <f>IF($K45="","",(Y45-AB45)/J45*100)</f>
       </c>
       <c r="AA45" s="3">
         <f>IF($K45="","",M45-X45)</f>
@@ -3107,7 +3107,7 @@
         <f>IF($K46="","",L46-M46-R46-S46-T46-U46-V46-W46)</f>
       </c>
       <c r="Z46" s="3">
-        <f>IF($K46="","",(Y46-AB46)/K46*100)</f>
+        <f>IF($K46="","",(Y46-AB46)/J46*100)</f>
       </c>
       <c r="AA46" s="3">
         <f>IF($K46="","",M46-X46)</f>
@@ -3158,7 +3158,7 @@
         <f>IF($K47="","",L47-M47-R47-S47-T47-U47-V47-W47)</f>
       </c>
       <c r="Z47" s="3">
-        <f>IF($K47="","",(Y47-AB47)/K47*100)</f>
+        <f>IF($K47="","",(Y47-AB47)/J47*100)</f>
       </c>
       <c r="AA47" s="3">
         <f>IF($K47="","",M47-X47)</f>
@@ -3209,7 +3209,7 @@
         <f>IF($K48="","",L48-M48-R48-S48-T48-U48-V48-W48)</f>
       </c>
       <c r="Z48" s="3">
-        <f>IF($K48="","",(Y48-AB48)/K48*100)</f>
+        <f>IF($K48="","",(Y48-AB48)/J48*100)</f>
       </c>
       <c r="AA48" s="3">
         <f>IF($K48="","",M48-X48)</f>
@@ -3260,7 +3260,7 @@
         <f>IF($K49="","",L49-M49-R49-S49-T49-U49-V49-W49)</f>
       </c>
       <c r="Z49" s="3">
-        <f>IF($K49="","",(Y49-AB49)/K49*100)</f>
+        <f>IF($K49="","",(Y49-AB49)/J49*100)</f>
       </c>
       <c r="AA49" s="3">
         <f>IF($K49="","",M49-X49)</f>
@@ -3311,7 +3311,7 @@
         <f>IF($K50="","",L50-M50-R50-S50-T50-U50-V50-W50)</f>
       </c>
       <c r="Z50" s="3">
-        <f>IF($K50="","",(Y50-AB50)/K50*100)</f>
+        <f>IF($K50="","",(Y50-AB50)/J50*100)</f>
       </c>
       <c r="AA50" s="3">
         <f>IF($K50="","",M50-X50)</f>
@@ -3362,7 +3362,7 @@
         <f>IF($K51="","",L51-M51-R51-S51-T51-U51-V51-W51)</f>
       </c>
       <c r="Z51" s="3">
-        <f>IF($K51="","",(Y51-AB51)/K51*100)</f>
+        <f>IF($K51="","",(Y51-AB51)/J51*100)</f>
       </c>
       <c r="AA51" s="3">
         <f>IF($K51="","",M51-X51)</f>
@@ -3413,7 +3413,7 @@
         <f>IF($K52="","",L52-M52-R52-S52-T52-U52-V52-W52)</f>
       </c>
       <c r="Z52" s="3">
-        <f>IF($K52="","",(Y52-AB52)/K52*100)</f>
+        <f>IF($K52="","",(Y52-AB52)/J52*100)</f>
       </c>
       <c r="AA52" s="3">
         <f>IF($K52="","",M52-X52)</f>
@@ -3464,7 +3464,7 @@
         <f>IF($K53="","",L53-M53-R53-S53-T53-U53-V53-W53)</f>
       </c>
       <c r="Z53" s="3">
-        <f>IF($K53="","",(Y53-AB53)/K53*100)</f>
+        <f>IF($K53="","",(Y53-AB53)/J53*100)</f>
       </c>
       <c r="AA53" s="3">
         <f>IF($K53="","",M53-X53)</f>
@@ -3515,7 +3515,7 @@
         <f>IF($K54="","",L54-M54-R54-S54-T54-U54-V54-W54)</f>
       </c>
       <c r="Z54" s="3">
-        <f>IF($K54="","",(Y54-AB54)/K54*100)</f>
+        <f>IF($K54="","",(Y54-AB54)/J54*100)</f>
       </c>
       <c r="AA54" s="3">
         <f>IF($K54="","",M54-X54)</f>
@@ -3566,7 +3566,7 @@
         <f>IF($K55="","",L55-M55-R55-S55-T55-U55-V55-W55)</f>
       </c>
       <c r="Z55" s="3">
-        <f>IF($K55="","",(Y55-AB55)/K55*100)</f>
+        <f>IF($K55="","",(Y55-AB55)/J55*100)</f>
       </c>
       <c r="AA55" s="3">
         <f>IF($K55="","",M55-X55)</f>
@@ -3617,7 +3617,7 @@
         <f>IF($K56="","",L56-M56-R56-S56-T56-U56-V56-W56)</f>
       </c>
       <c r="Z56" s="3">
-        <f>IF($K56="","",(Y56-AB56)/K56*100)</f>
+        <f>IF($K56="","",(Y56-AB56)/J56*100)</f>
       </c>
       <c r="AA56" s="3">
         <f>IF($K56="","",M56-X56)</f>
@@ -3668,7 +3668,7 @@
         <f>IF($K57="","",L57-M57-R57-S57-T57-U57-V57-W57)</f>
       </c>
       <c r="Z57" s="3">
-        <f>IF($K57="","",(Y57-AB57)/K57*100)</f>
+        <f>IF($K57="","",(Y57-AB57)/J57*100)</f>
       </c>
       <c r="AA57" s="3">
         <f>IF($K57="","",M57-X57)</f>
@@ -3719,7 +3719,7 @@
         <f>IF($K58="","",L58-M58-R58-S58-T58-U58-V58-W58)</f>
       </c>
       <c r="Z58" s="3">
-        <f>IF($K58="","",(Y58-AB58)/K58*100)</f>
+        <f>IF($K58="","",(Y58-AB58)/J58*100)</f>
       </c>
       <c r="AA58" s="3">
         <f>IF($K58="","",M58-X58)</f>
@@ -3770,7 +3770,7 @@
         <f>IF($K59="","",L59-M59-R59-S59-T59-U59-V59-W59)</f>
       </c>
       <c r="Z59" s="3">
-        <f>IF($K59="","",(Y59-AB59)/K59*100)</f>
+        <f>IF($K59="","",(Y59-AB59)/J59*100)</f>
       </c>
       <c r="AA59" s="3">
         <f>IF($K59="","",M59-X59)</f>
@@ -3821,7 +3821,7 @@
         <f>IF($K60="","",L60-M60-R60-S60-T60-U60-V60-W60)</f>
       </c>
       <c r="Z60" s="3">
-        <f>IF($K60="","",(Y60-AB60)/K60*100)</f>
+        <f>IF($K60="","",(Y60-AB60)/J60*100)</f>
       </c>
       <c r="AA60" s="3">
         <f>IF($K60="","",M60-X60)</f>
@@ -3872,7 +3872,7 @@
         <f>IF($K61="","",L61-M61-R61-S61-T61-U61-V61-W61)</f>
       </c>
       <c r="Z61" s="3">
-        <f>IF($K61="","",(Y61-AB61)/K61*100)</f>
+        <f>IF($K61="","",(Y61-AB61)/J61*100)</f>
       </c>
       <c r="AA61" s="3">
         <f>IF($K61="","",M61-X61)</f>
@@ -3923,7 +3923,7 @@
         <f>IF($K62="","",L62-M62-R62-S62-T62-U62-V62-W62)</f>
       </c>
       <c r="Z62" s="3">
-        <f>IF($K62="","",(Y62-AB62)/K62*100)</f>
+        <f>IF($K62="","",(Y62-AB62)/J62*100)</f>
       </c>
       <c r="AA62" s="3">
         <f>IF($K62="","",M62-X62)</f>
@@ -3974,7 +3974,7 @@
         <f>IF($K63="","",L63-M63-R63-S63-T63-U63-V63-W63)</f>
       </c>
       <c r="Z63" s="3">
-        <f>IF($K63="","",(Y63-AB63)/K63*100)</f>
+        <f>IF($K63="","",(Y63-AB63)/J63*100)</f>
       </c>
       <c r="AA63" s="3">
         <f>IF($K63="","",M63-X63)</f>
@@ -4025,7 +4025,7 @@
         <f>IF($K64="","",L64-M64-R64-S64-T64-U64-V64-W64)</f>
       </c>
       <c r="Z64" s="3">
-        <f>IF($K64="","",(Y64-AB64)/K64*100)</f>
+        <f>IF($K64="","",(Y64-AB64)/J64*100)</f>
       </c>
       <c r="AA64" s="3">
         <f>IF($K64="","",M64-X64)</f>
@@ -4076,7 +4076,7 @@
         <f>IF($K65="","",L65-M65-R65-S65-T65-U65-V65-W65)</f>
       </c>
       <c r="Z65" s="3">
-        <f>IF($K65="","",(Y65-AB65)/K65*100)</f>
+        <f>IF($K65="","",(Y65-AB65)/J65*100)</f>
       </c>
       <c r="AA65" s="3">
         <f>IF($K65="","",M65-X65)</f>
@@ -4127,7 +4127,7 @@
         <f>IF($K66="","",L66-M66-R66-S66-T66-U66-V66-W66)</f>
       </c>
       <c r="Z66" s="3">
-        <f>IF($K66="","",(Y66-AB66)/K66*100)</f>
+        <f>IF($K66="","",(Y66-AB66)/J66*100)</f>
       </c>
       <c r="AA66" s="3">
         <f>IF($K66="","",M66-X66)</f>
@@ -4178,7 +4178,7 @@
         <f>IF($K67="","",L67-M67-R67-S67-T67-U67-V67-W67)</f>
       </c>
       <c r="Z67" s="3">
-        <f>IF($K67="","",(Y67-AB67)/K67*100)</f>
+        <f>IF($K67="","",(Y67-AB67)/J67*100)</f>
       </c>
       <c r="AA67" s="3">
         <f>IF($K67="","",M67-X67)</f>
@@ -4229,7 +4229,7 @@
         <f>IF($K68="","",L68-M68-R68-S68-T68-U68-V68-W68)</f>
       </c>
       <c r="Z68" s="3">
-        <f>IF($K68="","",(Y68-AB68)/K68*100)</f>
+        <f>IF($K68="","",(Y68-AB68)/J68*100)</f>
       </c>
       <c r="AA68" s="3">
         <f>IF($K68="","",M68-X68)</f>
@@ -4280,7 +4280,7 @@
         <f>IF($K69="","",L69-M69-R69-S69-T69-U69-V69-W69)</f>
       </c>
       <c r="Z69" s="3">
-        <f>IF($K69="","",(Y69-AB69)/K69*100)</f>
+        <f>IF($K69="","",(Y69-AB69)/J69*100)</f>
       </c>
       <c r="AA69" s="3">
         <f>IF($K69="","",M69-X69)</f>
@@ -4331,7 +4331,7 @@
         <f>IF($K70="","",L70-M70-R70-S70-T70-U70-V70-W70)</f>
       </c>
       <c r="Z70" s="3">
-        <f>IF($K70="","",(Y70-AB70)/K70*100)</f>
+        <f>IF($K70="","",(Y70-AB70)/J70*100)</f>
       </c>
       <c r="AA70" s="3">
         <f>IF($K70="","",M70-X70)</f>
@@ -4382,7 +4382,7 @@
         <f>IF($K71="","",L71-M71-R71-S71-T71-U71-V71-W71)</f>
       </c>
       <c r="Z71" s="3">
-        <f>IF($K71="","",(Y71-AB71)/K71*100)</f>
+        <f>IF($K71="","",(Y71-AB71)/J71*100)</f>
       </c>
       <c r="AA71" s="3">
         <f>IF($K71="","",M71-X71)</f>
@@ -4433,7 +4433,7 @@
         <f>IF($K72="","",L72-M72-R72-S72-T72-U72-V72-W72)</f>
       </c>
       <c r="Z72" s="3">
-        <f>IF($K72="","",(Y72-AB72)/K72*100)</f>
+        <f>IF($K72="","",(Y72-AB72)/J72*100)</f>
       </c>
       <c r="AA72" s="3">
         <f>IF($K72="","",M72-X72)</f>
@@ -4484,7 +4484,7 @@
         <f>IF($K73="","",L73-M73-R73-S73-T73-U73-V73-W73)</f>
       </c>
       <c r="Z73" s="3">
-        <f>IF($K73="","",(Y73-AB73)/K73*100)</f>
+        <f>IF($K73="","",(Y73-AB73)/J73*100)</f>
       </c>
       <c r="AA73" s="3">
         <f>IF($K73="","",M73-X73)</f>
@@ -4535,7 +4535,7 @@
         <f>IF($K74="","",L74-M74-R74-S74-T74-U74-V74-W74)</f>
       </c>
       <c r="Z74" s="3">
-        <f>IF($K74="","",(Y74-AB74)/K74*100)</f>
+        <f>IF($K74="","",(Y74-AB74)/J74*100)</f>
       </c>
       <c r="AA74" s="3">
         <f>IF($K74="","",M74-X74)</f>
@@ -4586,7 +4586,7 @@
         <f>IF($K75="","",L75-M75-R75-S75-T75-U75-V75-W75)</f>
       </c>
       <c r="Z75" s="3">
-        <f>IF($K75="","",(Y75-AB75)/K75*100)</f>
+        <f>IF($K75="","",(Y75-AB75)/J75*100)</f>
       </c>
       <c r="AA75" s="3">
         <f>IF($K75="","",M75-X75)</f>
@@ -4637,7 +4637,7 @@
         <f>IF($K76="","",L76-M76-R76-S76-T76-U76-V76-W76)</f>
       </c>
       <c r="Z76" s="3">
-        <f>IF($K76="","",(Y76-AB76)/K76*100)</f>
+        <f>IF($K76="","",(Y76-AB76)/J76*100)</f>
       </c>
       <c r="AA76" s="3">
         <f>IF($K76="","",M76-X76)</f>
@@ -4688,7 +4688,7 @@
         <f>IF($K77="","",L77-M77-R77-S77-T77-U77-V77-W77)</f>
       </c>
       <c r="Z77" s="3">
-        <f>IF($K77="","",(Y77-AB77)/K77*100)</f>
+        <f>IF($K77="","",(Y77-AB77)/J77*100)</f>
       </c>
       <c r="AA77" s="3">
         <f>IF($K77="","",M77-X77)</f>
@@ -4739,7 +4739,7 @@
         <f>IF($K78="","",L78-M78-R78-S78-T78-U78-V78-W78)</f>
       </c>
       <c r="Z78" s="3">
-        <f>IF($K78="","",(Y78-AB78)/K78*100)</f>
+        <f>IF($K78="","",(Y78-AB78)/J78*100)</f>
       </c>
       <c r="AA78" s="3">
         <f>IF($K78="","",M78-X78)</f>
@@ -4790,7 +4790,7 @@
         <f>IF($K79="","",L79-M79-R79-S79-T79-U79-V79-W79)</f>
       </c>
       <c r="Z79" s="3">
-        <f>IF($K79="","",(Y79-AB79)/K79*100)</f>
+        <f>IF($K79="","",(Y79-AB79)/J79*100)</f>
       </c>
       <c r="AA79" s="3">
         <f>IF($K79="","",M79-X79)</f>
@@ -4841,7 +4841,7 @@
         <f>IF($K80="","",L80-M80-R80-S80-T80-U80-V80-W80)</f>
       </c>
       <c r="Z80" s="3">
-        <f>IF($K80="","",(Y80-AB80)/K80*100)</f>
+        <f>IF($K80="","",(Y80-AB80)/J80*100)</f>
       </c>
       <c r="AA80" s="3">
         <f>IF($K80="","",M80-X80)</f>
@@ -4892,7 +4892,7 @@
         <f>IF($K81="","",L81-M81-R81-S81-T81-U81-V81-W81)</f>
       </c>
       <c r="Z81" s="3">
-        <f>IF($K81="","",(Y81-AB81)/K81*100)</f>
+        <f>IF($K81="","",(Y81-AB81)/J81*100)</f>
       </c>
       <c r="AA81" s="3">
         <f>IF($K81="","",M81-X81)</f>
@@ -4943,7 +4943,7 @@
         <f>IF($K82="","",L82-M82-R82-S82-T82-U82-V82-W82)</f>
       </c>
       <c r="Z82" s="3">
-        <f>IF($K82="","",(Y82-AB82)/K82*100)</f>
+        <f>IF($K82="","",(Y82-AB82)/J82*100)</f>
       </c>
       <c r="AA82" s="3">
         <f>IF($K82="","",M82-X82)</f>
@@ -4994,7 +4994,7 @@
         <f>IF($K83="","",L83-M83-R83-S83-T83-U83-V83-W83)</f>
       </c>
       <c r="Z83" s="3">
-        <f>IF($K83="","",(Y83-AB83)/K83*100)</f>
+        <f>IF($K83="","",(Y83-AB83)/J83*100)</f>
       </c>
       <c r="AA83" s="3">
         <f>IF($K83="","",M83-X83)</f>
@@ -5045,7 +5045,7 @@
         <f>IF($K84="","",L84-M84-R84-S84-T84-U84-V84-W84)</f>
       </c>
       <c r="Z84" s="3">
-        <f>IF($K84="","",(Y84-AB84)/K84*100)</f>
+        <f>IF($K84="","",(Y84-AB84)/J84*100)</f>
       </c>
       <c r="AA84" s="3">
         <f>IF($K84="","",M84-X84)</f>
@@ -5096,7 +5096,7 @@
         <f>IF($K85="","",L85-M85-R85-S85-T85-U85-V85-W85)</f>
       </c>
       <c r="Z85" s="3">
-        <f>IF($K85="","",(Y85-AB85)/K85*100)</f>
+        <f>IF($K85="","",(Y85-AB85)/J85*100)</f>
       </c>
       <c r="AA85" s="3">
         <f>IF($K85="","",M85-X85)</f>
@@ -5147,7 +5147,7 @@
         <f>IF($K86="","",L86-M86-R86-S86-T86-U86-V86-W86)</f>
       </c>
       <c r="Z86" s="3">
-        <f>IF($K86="","",(Y86-AB86)/K86*100)</f>
+        <f>IF($K86="","",(Y86-AB86)/J86*100)</f>
       </c>
       <c r="AA86" s="3">
         <f>IF($K86="","",M86-X86)</f>
@@ -5198,7 +5198,7 @@
         <f>IF($K87="","",L87-M87-R87-S87-T87-U87-V87-W87)</f>
       </c>
       <c r="Z87" s="3">
-        <f>IF($K87="","",(Y87-AB87)/K87*100)</f>
+        <f>IF($K87="","",(Y87-AB87)/J87*100)</f>
       </c>
       <c r="AA87" s="3">
         <f>IF($K87="","",M87-X87)</f>
@@ -5249,7 +5249,7 @@
         <f>IF($K88="","",L88-M88-R88-S88-T88-U88-V88-W88)</f>
       </c>
       <c r="Z88" s="3">
-        <f>IF($K88="","",(Y88-AB88)/K88*100)</f>
+        <f>IF($K88="","",(Y88-AB88)/J88*100)</f>
       </c>
       <c r="AA88" s="3">
         <f>IF($K88="","",M88-X88)</f>
@@ -5300,7 +5300,7 @@
         <f>IF($K89="","",L89-M89-R89-S89-T89-U89-V89-W89)</f>
       </c>
       <c r="Z89" s="3">
-        <f>IF($K89="","",(Y89-AB89)/K89*100)</f>
+        <f>IF($K89="","",(Y89-AB89)/J89*100)</f>
       </c>
       <c r="AA89" s="3">
         <f>IF($K89="","",M89-X89)</f>
@@ -5351,7 +5351,7 @@
         <f>IF($K90="","",L90-M90-R90-S90-T90-U90-V90-W90)</f>
       </c>
       <c r="Z90" s="3">
-        <f>IF($K90="","",(Y90-AB90)/K90*100)</f>
+        <f>IF($K90="","",(Y90-AB90)/J90*100)</f>
       </c>
       <c r="AA90" s="3">
         <f>IF($K90="","",M90-X90)</f>
@@ -5402,7 +5402,7 @@
         <f>IF($K91="","",L91-M91-R91-S91-T91-U91-V91-W91)</f>
       </c>
       <c r="Z91" s="3">
-        <f>IF($K91="","",(Y91-AB91)/K91*100)</f>
+        <f>IF($K91="","",(Y91-AB91)/J91*100)</f>
       </c>
       <c r="AA91" s="3">
         <f>IF($K91="","",M91-X91)</f>
@@ -5453,7 +5453,7 @@
         <f>IF($K92="","",L92-M92-R92-S92-T92-U92-V92-W92)</f>
       </c>
       <c r="Z92" s="3">
-        <f>IF($K92="","",(Y92-AB92)/K92*100)</f>
+        <f>IF($K92="","",(Y92-AB92)/J92*100)</f>
       </c>
       <c r="AA92" s="3">
         <f>IF($K92="","",M92-X92)</f>
@@ -5504,7 +5504,7 @@
         <f>IF($K93="","",L93-M93-R93-S93-T93-U93-V93-W93)</f>
       </c>
       <c r="Z93" s="3">
-        <f>IF($K93="","",(Y93-AB93)/K93*100)</f>
+        <f>IF($K93="","",(Y93-AB93)/J93*100)</f>
       </c>
       <c r="AA93" s="3">
         <f>IF($K93="","",M93-X93)</f>
@@ -5555,7 +5555,7 @@
         <f>IF($K94="","",L94-M94-R94-S94-T94-U94-V94-W94)</f>
       </c>
       <c r="Z94" s="3">
-        <f>IF($K94="","",(Y94-AB94)/K94*100)</f>
+        <f>IF($K94="","",(Y94-AB94)/J94*100)</f>
       </c>
       <c r="AA94" s="3">
         <f>IF($K94="","",M94-X94)</f>
@@ -5606,7 +5606,7 @@
         <f>IF($K95="","",L95-M95-R95-S95-T95-U95-V95-W95)</f>
       </c>
       <c r="Z95" s="3">
-        <f>IF($K95="","",(Y95-AB95)/K95*100)</f>
+        <f>IF($K95="","",(Y95-AB95)/J95*100)</f>
       </c>
       <c r="AA95" s="3">
         <f>IF($K95="","",M95-X95)</f>
@@ -5657,7 +5657,7 @@
         <f>IF($K96="","",L96-M96-R96-S96-T96-U96-V96-W96)</f>
       </c>
       <c r="Z96" s="3">
-        <f>IF($K96="","",(Y96-AB96)/K96*100)</f>
+        <f>IF($K96="","",(Y96-AB96)/J96*100)</f>
       </c>
       <c r="AA96" s="3">
         <f>IF($K96="","",M96-X96)</f>
@@ -5708,7 +5708,7 @@
         <f>IF($K97="","",L97-M97-R97-S97-T97-U97-V97-W97)</f>
       </c>
       <c r="Z97" s="3">
-        <f>IF($K97="","",(Y97-AB97)/K97*100)</f>
+        <f>IF($K97="","",(Y97-AB97)/J97*100)</f>
       </c>
       <c r="AA97" s="3">
         <f>IF($K97="","",M97-X97)</f>
@@ -5759,7 +5759,7 @@
         <f>IF($K98="","",L98-M98-R98-S98-T98-U98-V98-W98)</f>
       </c>
       <c r="Z98" s="3">
-        <f>IF($K98="","",(Y98-AB98)/K98*100)</f>
+        <f>IF($K98="","",(Y98-AB98)/J98*100)</f>
       </c>
       <c r="AA98" s="3">
         <f>IF($K98="","",M98-X98)</f>
@@ -5810,7 +5810,7 @@
         <f>IF($K99="","",L99-M99-R99-S99-T99-U99-V99-W99)</f>
       </c>
       <c r="Z99" s="3">
-        <f>IF($K99="","",(Y99-AB99)/K99*100)</f>
+        <f>IF($K99="","",(Y99-AB99)/J99*100)</f>
       </c>
       <c r="AA99" s="3">
         <f>IF($K99="","",M99-X99)</f>
@@ -5861,7 +5861,7 @@
         <f>IF($K100="","",L100-M100-R100-S100-T100-U100-V100-W100)</f>
       </c>
       <c r="Z100" s="3">
-        <f>IF($K100="","",(Y100-AB100)/K100*100)</f>
+        <f>IF($K100="","",(Y100-AB100)/J100*100)</f>
       </c>
       <c r="AA100" s="3">
         <f>IF($K100="","",M100-X100)</f>
@@ -5912,7 +5912,7 @@
         <f>IF($K101="","",L101-M101-R101-S101-T101-U101-V101-W101)</f>
       </c>
       <c r="Z101" s="3">
-        <f>IF($K101="","",(Y101-AB101)/K101*100)</f>
+        <f>IF($K101="","",(Y101-AB101)/J101*100)</f>
       </c>
       <c r="AA101" s="3">
         <f>IF($K101="","",M101-X101)</f>
@@ -5963,7 +5963,7 @@
         <f>IF($K102="","",L102-M102-R102-S102-T102-U102-V102-W102)</f>
       </c>
       <c r="Z102" s="3">
-        <f>IF($K102="","",(Y102-AB102)/K102*100)</f>
+        <f>IF($K102="","",(Y102-AB102)/J102*100)</f>
       </c>
       <c r="AA102" s="3">
         <f>IF($K102="","",M102-X102)</f>
@@ -6014,7 +6014,7 @@
         <f>IF($K103="","",L103-M103-R103-S103-T103-U103-V103-W103)</f>
       </c>
       <c r="Z103" s="3">
-        <f>IF($K103="","",(Y103-AB103)/K103*100)</f>
+        <f>IF($K103="","",(Y103-AB103)/J103*100)</f>
       </c>
       <c r="AA103" s="3">
         <f>IF($K103="","",M103-X103)</f>
@@ -6065,7 +6065,7 @@
         <f>IF($K104="","",L104-M104-R104-S104-T104-U104-V104-W104)</f>
       </c>
       <c r="Z104" s="3">
-        <f>IF($K104="","",(Y104-AB104)/K104*100)</f>
+        <f>IF($K104="","",(Y104-AB104)/J104*100)</f>
       </c>
       <c r="AA104" s="3">
         <f>IF($K104="","",M104-X104)</f>
@@ -6116,7 +6116,7 @@
         <f>IF($K105="","",L105-M105-R105-S105-T105-U105-V105-W105)</f>
       </c>
       <c r="Z105" s="3">
-        <f>IF($K105="","",(Y105-AB105)/K105*100)</f>
+        <f>IF($K105="","",(Y105-AB105)/J105*100)</f>
       </c>
       <c r="AA105" s="3">
         <f>IF($K105="","",M105-X105)</f>
@@ -6167,7 +6167,7 @@
         <f>IF($K106="","",L106-M106-R106-S106-T106-U106-V106-W106)</f>
       </c>
       <c r="Z106" s="3">
-        <f>IF($K106="","",(Y106-AB106)/K106*100)</f>
+        <f>IF($K106="","",(Y106-AB106)/J106*100)</f>
       </c>
       <c r="AA106" s="3">
         <f>IF($K106="","",M106-X106)</f>
@@ -6218,7 +6218,7 @@
         <f>IF($K107="","",L107-M107-R107-S107-T107-U107-V107-W107)</f>
       </c>
       <c r="Z107" s="3">
-        <f>IF($K107="","",(Y107-AB107)/K107*100)</f>
+        <f>IF($K107="","",(Y107-AB107)/J107*100)</f>
       </c>
       <c r="AA107" s="3">
         <f>IF($K107="","",M107-X107)</f>
@@ -6269,7 +6269,7 @@
         <f>IF($K108="","",L108-M108-R108-S108-T108-U108-V108-W108)</f>
       </c>
       <c r="Z108" s="3">
-        <f>IF($K108="","",(Y108-AB108)/K108*100)</f>
+        <f>IF($K108="","",(Y108-AB108)/J108*100)</f>
       </c>
       <c r="AA108" s="3">
         <f>IF($K108="","",M108-X108)</f>
@@ -6320,7 +6320,7 @@
         <f>IF($K109="","",L109-M109-R109-S109-T109-U109-V109-W109)</f>
       </c>
       <c r="Z109" s="3">
-        <f>IF($K109="","",(Y109-AB109)/K109*100)</f>
+        <f>IF($K109="","",(Y109-AB109)/J109*100)</f>
       </c>
       <c r="AA109" s="3">
         <f>IF($K109="","",M109-X109)</f>
@@ -6371,7 +6371,7 @@
         <f>IF($K110="","",L110-M110-R110-S110-T110-U110-V110-W110)</f>
       </c>
       <c r="Z110" s="3">
-        <f>IF($K110="","",(Y110-AB110)/K110*100)</f>
+        <f>IF($K110="","",(Y110-AB110)/J110*100)</f>
       </c>
       <c r="AA110" s="3">
         <f>IF($K110="","",M110-X110)</f>
@@ -6422,7 +6422,7 @@
         <f>IF($K111="","",L111-M111-R111-S111-T111-U111-V111-W111)</f>
       </c>
       <c r="Z111" s="3">
-        <f>IF($K111="","",(Y111-AB111)/K111*100)</f>
+        <f>IF($K111="","",(Y111-AB111)/J111*100)</f>
       </c>
       <c r="AA111" s="3">
         <f>IF($K111="","",M111-X111)</f>
@@ -6473,7 +6473,7 @@
         <f>IF($K112="","",L112-M112-R112-S112-T112-U112-V112-W112)</f>
       </c>
       <c r="Z112" s="3">
-        <f>IF($K112="","",(Y112-AB112)/K112*100)</f>
+        <f>IF($K112="","",(Y112-AB112)/J112*100)</f>
       </c>
       <c r="AA112" s="3">
         <f>IF($K112="","",M112-X112)</f>
@@ -6524,7 +6524,7 @@
         <f>IF($K113="","",L113-M113-R113-S113-T113-U113-V113-W113)</f>
       </c>
       <c r="Z113" s="3">
-        <f>IF($K113="","",(Y113-AB113)/K113*100)</f>
+        <f>IF($K113="","",(Y113-AB113)/J113*100)</f>
       </c>
       <c r="AA113" s="3">
         <f>IF($K113="","",M113-X113)</f>
@@ -6575,7 +6575,7 @@
         <f>IF($K114="","",L114-M114-R114-S114-T114-U114-V114-W114)</f>
       </c>
       <c r="Z114" s="3">
-        <f>IF($K114="","",(Y114-AB114)/K114*100)</f>
+        <f>IF($K114="","",(Y114-AB114)/J114*100)</f>
       </c>
       <c r="AA114" s="3">
         <f>IF($K114="","",M114-X114)</f>
@@ -6626,7 +6626,7 @@
         <f>IF($K115="","",L115-M115-R115-S115-T115-U115-V115-W115)</f>
       </c>
       <c r="Z115" s="3">
-        <f>IF($K115="","",(Y115-AB115)/K115*100)</f>
+        <f>IF($K115="","",(Y115-AB115)/J115*100)</f>
       </c>
       <c r="AA115" s="3">
         <f>IF($K115="","",M115-X115)</f>
@@ -6677,7 +6677,7 @@
         <f>IF($K116="","",L116-M116-R116-S116-T116-U116-V116-W116)</f>
       </c>
       <c r="Z116" s="3">
-        <f>IF($K116="","",(Y116-AB116)/K116*100)</f>
+        <f>IF($K116="","",(Y116-AB116)/J116*100)</f>
       </c>
       <c r="AA116" s="3">
         <f>IF($K116="","",M116-X116)</f>
@@ -6728,7 +6728,7 @@
         <f>IF($K117="","",L117-M117-R117-S117-T117-U117-V117-W117)</f>
       </c>
       <c r="Z117" s="3">
-        <f>IF($K117="","",(Y117-AB117)/K117*100)</f>
+        <f>IF($K117="","",(Y117-AB117)/J117*100)</f>
       </c>
       <c r="AA117" s="3">
         <f>IF($K117="","",M117-X117)</f>
@@ -6779,7 +6779,7 @@
         <f>IF($K118="","",L118-M118-R118-S118-T118-U118-V118-W118)</f>
       </c>
       <c r="Z118" s="3">
-        <f>IF($K118="","",(Y118-AB118)/K118*100)</f>
+        <f>IF($K118="","",(Y118-AB118)/J118*100)</f>
       </c>
       <c r="AA118" s="3">
         <f>IF($K118="","",M118-X118)</f>
@@ -6830,7 +6830,7 @@
         <f>IF($K119="","",L119-M119-R119-S119-T119-U119-V119-W119)</f>
       </c>
       <c r="Z119" s="3">
-        <f>IF($K119="","",(Y119-AB119)/K119*100)</f>
+        <f>IF($K119="","",(Y119-AB119)/J119*100)</f>
       </c>
       <c r="AA119" s="3">
         <f>IF($K119="","",M119-X119)</f>
@@ -6881,7 +6881,7 @@
         <f>IF($K120="","",L120-M120-R120-S120-T120-U120-V120-W120)</f>
       </c>
       <c r="Z120" s="3">
-        <f>IF($K120="","",(Y120-AB120)/K120*100)</f>
+        <f>IF($K120="","",(Y120-AB120)/J120*100)</f>
       </c>
       <c r="AA120" s="3">
         <f>IF($K120="","",M120-X120)</f>
@@ -6932,7 +6932,7 @@
         <f>IF($K121="","",L121-M121-R121-S121-T121-U121-V121-W121)</f>
       </c>
       <c r="Z121" s="3">
-        <f>IF($K121="","",(Y121-AB121)/K121*100)</f>
+        <f>IF($K121="","",(Y121-AB121)/J121*100)</f>
       </c>
       <c r="AA121" s="3">
         <f>IF($K121="","",M121-X121)</f>
@@ -6983,7 +6983,7 @@
         <f>IF($K122="","",L122-M122-R122-S122-T122-U122-V122-W122)</f>
       </c>
       <c r="Z122" s="3">
-        <f>IF($K122="","",(Y122-AB122)/K122*100)</f>
+        <f>IF($K122="","",(Y122-AB122)/J122*100)</f>
       </c>
       <c r="AA122" s="3">
         <f>IF($K122="","",M122-X122)</f>
@@ -7034,7 +7034,7 @@
         <f>IF($K123="","",L123-M123-R123-S123-T123-U123-V123-W123)</f>
       </c>
       <c r="Z123" s="3">
-        <f>IF($K123="","",(Y123-AB123)/K123*100)</f>
+        <f>IF($K123="","",(Y123-AB123)/J123*100)</f>
       </c>
       <c r="AA123" s="3">
         <f>IF($K123="","",M123-X123)</f>
@@ -7085,7 +7085,7 @@
         <f>IF($K124="","",L124-M124-R124-S124-T124-U124-V124-W124)</f>
       </c>
       <c r="Z124" s="3">
-        <f>IF($K124="","",(Y124-AB124)/K124*100)</f>
+        <f>IF($K124="","",(Y124-AB124)/J124*100)</f>
       </c>
       <c r="AA124" s="3">
         <f>IF($K124="","",M124-X124)</f>
@@ -7136,7 +7136,7 @@
         <f>IF($K125="","",L125-M125-R125-S125-T125-U125-V125-W125)</f>
       </c>
       <c r="Z125" s="3">
-        <f>IF($K125="","",(Y125-AB125)/K125*100)</f>
+        <f>IF($K125="","",(Y125-AB125)/J125*100)</f>
       </c>
       <c r="AA125" s="3">
         <f>IF($K125="","",M125-X125)</f>
@@ -7187,7 +7187,7 @@
         <f>IF($K126="","",L126-M126-R126-S126-T126-U126-V126-W126)</f>
       </c>
       <c r="Z126" s="3">
-        <f>IF($K126="","",(Y126-AB126)/K126*100)</f>
+        <f>IF($K126="","",(Y126-AB126)/J126*100)</f>
       </c>
       <c r="AA126" s="3">
         <f>IF($K126="","",M126-X126)</f>
@@ -7238,7 +7238,7 @@
         <f>IF($K127="","",L127-M127-R127-S127-T127-U127-V127-W127)</f>
       </c>
       <c r="Z127" s="3">
-        <f>IF($K127="","",(Y127-AB127)/K127*100)</f>
+        <f>IF($K127="","",(Y127-AB127)/J127*100)</f>
       </c>
       <c r="AA127" s="3">
         <f>IF($K127="","",M127-X127)</f>
@@ -7289,7 +7289,7 @@
         <f>IF($K128="","",L128-M128-R128-S128-T128-U128-V128-W128)</f>
       </c>
       <c r="Z128" s="3">
-        <f>IF($K128="","",(Y128-AB128)/K128*100)</f>
+        <f>IF($K128="","",(Y128-AB128)/J128*100)</f>
       </c>
       <c r="AA128" s="3">
         <f>IF($K128="","",M128-X128)</f>
@@ -7340,7 +7340,7 @@
         <f>IF($K129="","",L129-M129-R129-S129-T129-U129-V129-W129)</f>
       </c>
       <c r="Z129" s="3">
-        <f>IF($K129="","",(Y129-AB129)/K129*100)</f>
+        <f>IF($K129="","",(Y129-AB129)/J129*100)</f>
       </c>
       <c r="AA129" s="3">
         <f>IF($K129="","",M129-X129)</f>
@@ -7391,7 +7391,7 @@
         <f>IF($K130="","",L130-M130-R130-S130-T130-U130-V130-W130)</f>
       </c>
       <c r="Z130" s="3">
-        <f>IF($K130="","",(Y130-AB130)/K130*100)</f>
+        <f>IF($K130="","",(Y130-AB130)/J130*100)</f>
       </c>
       <c r="AA130" s="3">
         <f>IF($K130="","",M130-X130)</f>
@@ -7442,7 +7442,7 @@
         <f>IF($K131="","",L131-M131-R131-S131-T131-U131-V131-W131)</f>
       </c>
       <c r="Z131" s="3">
-        <f>IF($K131="","",(Y131-AB131)/K131*100)</f>
+        <f>IF($K131="","",(Y131-AB131)/J131*100)</f>
       </c>
       <c r="AA131" s="3">
         <f>IF($K131="","",M131-X131)</f>
@@ -7493,7 +7493,7 @@
         <f>IF($K132="","",L132-M132-R132-S132-T132-U132-V132-W132)</f>
       </c>
       <c r="Z132" s="3">
-        <f>IF($K132="","",(Y132-AB132)/K132*100)</f>
+        <f>IF($K132="","",(Y132-AB132)/J132*100)</f>
       </c>
       <c r="AA132" s="3">
         <f>IF($K132="","",M132-X132)</f>
@@ -7544,7 +7544,7 @@
         <f>IF($K133="","",L133-M133-R133-S133-T133-U133-V133-W133)</f>
       </c>
       <c r="Z133" s="3">
-        <f>IF($K133="","",(Y133-AB133)/K133*100)</f>
+        <f>IF($K133="","",(Y133-AB133)/J133*100)</f>
       </c>
       <c r="AA133" s="3">
         <f>IF($K133="","",M133-X133)</f>
@@ -7595,7 +7595,7 @@
         <f>IF($K134="","",L134-M134-R134-S134-T134-U134-V134-W134)</f>
       </c>
       <c r="Z134" s="3">
-        <f>IF($K134="","",(Y134-AB134)/K134*100)</f>
+        <f>IF($K134="","",(Y134-AB134)/J134*100)</f>
       </c>
       <c r="AA134" s="3">
         <f>IF($K134="","",M134-X134)</f>
@@ -7646,7 +7646,7 @@
         <f>IF($K135="","",L135-M135-R135-S135-T135-U135-V135-W135)</f>
       </c>
       <c r="Z135" s="3">
-        <f>IF($K135="","",(Y135-AB135)/K135*100)</f>
+        <f>IF($K135="","",(Y135-AB135)/J135*100)</f>
       </c>
       <c r="AA135" s="3">
         <f>IF($K135="","",M135-X135)</f>
@@ -7697,7 +7697,7 @@
         <f>IF($K136="","",L136-M136-R136-S136-T136-U136-V136-W136)</f>
       </c>
       <c r="Z136" s="3">
-        <f>IF($K136="","",(Y136-AB136)/K136*100)</f>
+        <f>IF($K136="","",(Y136-AB136)/J136*100)</f>
       </c>
       <c r="AA136" s="3">
         <f>IF($K136="","",M136-X136)</f>
@@ -7748,7 +7748,7 @@
         <f>IF($K137="","",L137-M137-R137-S137-T137-U137-V137-W137)</f>
       </c>
       <c r="Z137" s="3">
-        <f>IF($K137="","",(Y137-AB137)/K137*100)</f>
+        <f>IF($K137="","",(Y137-AB137)/J137*100)</f>
       </c>
       <c r="AA137" s="3">
         <f>IF($K137="","",M137-X137)</f>
@@ -7799,7 +7799,7 @@
         <f>IF($K138="","",L138-M138-R138-S138-T138-U138-V138-W138)</f>
       </c>
       <c r="Z138" s="3">
-        <f>IF($K138="","",(Y138-AB138)/K138*100)</f>
+        <f>IF($K138="","",(Y138-AB138)/J138*100)</f>
       </c>
       <c r="AA138" s="3">
         <f>IF($K138="","",M138-X138)</f>
@@ -7850,7 +7850,7 @@
         <f>IF($K139="","",L139-M139-R139-S139-T139-U139-V139-W139)</f>
       </c>
       <c r="Z139" s="3">
-        <f>IF($K139="","",(Y139-AB139)/K139*100)</f>
+        <f>IF($K139="","",(Y139-AB139)/J139*100)</f>
       </c>
       <c r="AA139" s="3">
         <f>IF($K139="","",M139-X139)</f>
@@ -7901,7 +7901,7 @@
         <f>IF($K140="","",L140-M140-R140-S140-T140-U140-V140-W140)</f>
       </c>
       <c r="Z140" s="3">
-        <f>IF($K140="","",(Y140-AB140)/K140*100)</f>
+        <f>IF($K140="","",(Y140-AB140)/J140*100)</f>
       </c>
       <c r="AA140" s="3">
         <f>IF($K140="","",M140-X140)</f>
@@ -7952,7 +7952,7 @@
         <f>IF($K141="","",L141-M141-R141-S141-T141-U141-V141-W141)</f>
       </c>
       <c r="Z141" s="3">
-        <f>IF($K141="","",(Y141-AB141)/K141*100)</f>
+        <f>IF($K141="","",(Y141-AB141)/J141*100)</f>
       </c>
       <c r="AA141" s="3">
         <f>IF($K141="","",M141-X141)</f>
@@ -8003,7 +8003,7 @@
         <f>IF($K142="","",L142-M142-R142-S142-T142-U142-V142-W142)</f>
       </c>
       <c r="Z142" s="3">
-        <f>IF($K142="","",(Y142-AB142)/K142*100)</f>
+        <f>IF($K142="","",(Y142-AB142)/J142*100)</f>
       </c>
       <c r="AA142" s="3">
         <f>IF($K142="","",M142-X142)</f>
@@ -8054,7 +8054,7 @@
         <f>IF($K143="","",L143-M143-R143-S143-T143-U143-V143-W143)</f>
       </c>
       <c r="Z143" s="3">
-        <f>IF($K143="","",(Y143-AB143)/K143*100)</f>
+        <f>IF($K143="","",(Y143-AB143)/J143*100)</f>
       </c>
       <c r="AA143" s="3">
         <f>IF($K143="","",M143-X143)</f>
@@ -8105,7 +8105,7 @@
         <f>IF($K144="","",L144-M144-R144-S144-T144-U144-V144-W144)</f>
       </c>
       <c r="Z144" s="3">
-        <f>IF($K144="","",(Y144-AB144)/K144*100)</f>
+        <f>IF($K144="","",(Y144-AB144)/J144*100)</f>
       </c>
       <c r="AA144" s="3">
         <f>IF($K144="","",M144-X144)</f>
@@ -8156,7 +8156,7 @@
         <f>IF($K145="","",L145-M145-R145-S145-T145-U145-V145-W145)</f>
       </c>
       <c r="Z145" s="3">
-        <f>IF($K145="","",(Y145-AB145)/K145*100)</f>
+        <f>IF($K145="","",(Y145-AB145)/J145*100)</f>
       </c>
       <c r="AA145" s="3">
         <f>IF($K145="","",M145-X145)</f>
@@ -8207,7 +8207,7 @@
         <f>IF($K146="","",L146-M146-R146-S146-T146-U146-V146-W146)</f>
       </c>
       <c r="Z146" s="3">
-        <f>IF($K146="","",(Y146-AB146)/K146*100)</f>
+        <f>IF($K146="","",(Y146-AB146)/J146*100)</f>
       </c>
       <c r="AA146" s="3">
         <f>IF($K146="","",M146-X146)</f>
@@ -8258,7 +8258,7 @@
         <f>IF($K147="","",L147-M147-R147-S147-T147-U147-V147-W147)</f>
       </c>
       <c r="Z147" s="3">
-        <f>IF($K147="","",(Y147-AB147)/K147*100)</f>
+        <f>IF($K147="","",(Y147-AB147)/J147*100)</f>
       </c>
       <c r="AA147" s="3">
         <f>IF($K147="","",M147-X147)</f>
@@ -8309,7 +8309,7 @@
         <f>IF($K148="","",L148-M148-R148-S148-T148-U148-V148-W148)</f>
       </c>
       <c r="Z148" s="3">
-        <f>IF($K148="","",(Y148-AB148)/K148*100)</f>
+        <f>IF($K148="","",(Y148-AB148)/J148*100)</f>
       </c>
       <c r="AA148" s="3">
         <f>IF($K148="","",M148-X148)</f>
@@ -8360,7 +8360,7 @@
         <f>IF($K149="","",L149-M149-R149-S149-T149-U149-V149-W149)</f>
       </c>
       <c r="Z149" s="3">
-        <f>IF($K149="","",(Y149-AB149)/K149*100)</f>
+        <f>IF($K149="","",(Y149-AB149)/J149*100)</f>
       </c>
       <c r="AA149" s="3">
         <f>IF($K149="","",M149-X149)</f>
@@ -8411,7 +8411,7 @@
         <f>IF($K150="","",L150-M150-R150-S150-T150-U150-V150-W150)</f>
       </c>
       <c r="Z150" s="3">
-        <f>IF($K150="","",(Y150-AB150)/K150*100)</f>
+        <f>IF($K150="","",(Y150-AB150)/J150*100)</f>
       </c>
       <c r="AA150" s="3">
         <f>IF($K150="","",M150-X150)</f>
@@ -8462,7 +8462,7 @@
         <f>IF($K151="","",L151-M151-R151-S151-T151-U151-V151-W151)</f>
       </c>
       <c r="Z151" s="3">
-        <f>IF($K151="","",(Y151-AB151)/K151*100)</f>
+        <f>IF($K151="","",(Y151-AB151)/J151*100)</f>
       </c>
       <c r="AA151" s="3">
         <f>IF($K151="","",M151-X151)</f>
@@ -8513,7 +8513,7 @@
         <f>IF($K152="","",L152-M152-R152-S152-T152-U152-V152-W152)</f>
       </c>
       <c r="Z152" s="3">
-        <f>IF($K152="","",(Y152-AB152)/K152*100)</f>
+        <f>IF($K152="","",(Y152-AB152)/J152*100)</f>
       </c>
       <c r="AA152" s="3">
         <f>IF($K152="","",M152-X152)</f>
@@ -8564,7 +8564,7 @@
         <f>IF($K153="","",L153-M153-R153-S153-T153-U153-V153-W153)</f>
       </c>
       <c r="Z153" s="3">
-        <f>IF($K153="","",(Y153-AB153)/K153*100)</f>
+        <f>IF($K153="","",(Y153-AB153)/J153*100)</f>
       </c>
       <c r="AA153" s="3">
         <f>IF($K153="","",M153-X153)</f>
@@ -8615,7 +8615,7 @@
         <f>IF($K154="","",L154-M154-R154-S154-T154-U154-V154-W154)</f>
       </c>
       <c r="Z154" s="3">
-        <f>IF($K154="","",(Y154-AB154)/K154*100)</f>
+        <f>IF($K154="","",(Y154-AB154)/J154*100)</f>
       </c>
       <c r="AA154" s="3">
         <f>IF($K154="","",M154-X154)</f>
@@ -8666,7 +8666,7 @@
         <f>IF($K155="","",L155-M155-R155-S155-T155-U155-V155-W155)</f>
       </c>
       <c r="Z155" s="3">
-        <f>IF($K155="","",(Y155-AB155)/K155*100)</f>
+        <f>IF($K155="","",(Y155-AB155)/J155*100)</f>
       </c>
       <c r="AA155" s="3">
         <f>IF($K155="","",M155-X155)</f>
@@ -8717,7 +8717,7 @@
         <f>IF($K156="","",L156-M156-R156-S156-T156-U156-V156-W156)</f>
       </c>
       <c r="Z156" s="3">
-        <f>IF($K156="","",(Y156-AB156)/K156*100)</f>
+        <f>IF($K156="","",(Y156-AB156)/J156*100)</f>
       </c>
       <c r="AA156" s="3">
         <f>IF($K156="","",M156-X156)</f>
@@ -8768,7 +8768,7 @@
         <f>IF($K157="","",L157-M157-R157-S157-T157-U157-V157-W157)</f>
       </c>
       <c r="Z157" s="3">
-        <f>IF($K157="","",(Y157-AB157)/K157*100)</f>
+        <f>IF($K157="","",(Y157-AB157)/J157*100)</f>
       </c>
       <c r="AA157" s="3">
         <f>IF($K157="","",M157-X157)</f>
@@ -8819,7 +8819,7 @@
         <f>IF($K158="","",L158-M158-R158-S158-T158-U158-V158-W158)</f>
       </c>
       <c r="Z158" s="3">
-        <f>IF($K158="","",(Y158-AB158)/K158*100)</f>
+        <f>IF($K158="","",(Y158-AB158)/J158*100)</f>
       </c>
       <c r="AA158" s="3">
         <f>IF($K158="","",M158-X158)</f>
@@ -8870,7 +8870,7 @@
         <f>IF($K159="","",L159-M159-R159-S159-T159-U159-V159-W159)</f>
       </c>
       <c r="Z159" s="3">
-        <f>IF($K159="","",(Y159-AB159)/K159*100)</f>
+        <f>IF($K159="","",(Y159-AB159)/J159*100)</f>
       </c>
       <c r="AA159" s="3">
         <f>IF($K159="","",M159-X159)</f>
@@ -8921,7 +8921,7 @@
         <f>IF($K160="","",L160-M160-R160-S160-T160-U160-V160-W160)</f>
       </c>
       <c r="Z160" s="3">
-        <f>IF($K160="","",(Y160-AB160)/K160*100)</f>
+        <f>IF($K160="","",(Y160-AB160)/J160*100)</f>
       </c>
       <c r="AA160" s="3">
         <f>IF($K160="","",M160-X160)</f>
@@ -8972,7 +8972,7 @@
         <f>IF($K161="","",L161-M161-R161-S161-T161-U161-V161-W161)</f>
       </c>
       <c r="Z161" s="3">
-        <f>IF($K161="","",(Y161-AB161)/K161*100)</f>
+        <f>IF($K161="","",(Y161-AB161)/J161*100)</f>
       </c>
       <c r="AA161" s="3">
         <f>IF($K161="","",M161-X161)</f>
@@ -9023,7 +9023,7 @@
         <f>IF($K162="","",L162-M162-R162-S162-T162-U162-V162-W162)</f>
       </c>
       <c r="Z162" s="3">
-        <f>IF($K162="","",(Y162-AB162)/K162*100)</f>
+        <f>IF($K162="","",(Y162-AB162)/J162*100)</f>
       </c>
       <c r="AA162" s="3">
         <f>IF($K162="","",M162-X162)</f>
@@ -9074,7 +9074,7 @@
         <f>IF($K163="","",L163-M163-R163-S163-T163-U163-V163-W163)</f>
       </c>
       <c r="Z163" s="3">
-        <f>IF($K163="","",(Y163-AB163)/K163*100)</f>
+        <f>IF($K163="","",(Y163-AB163)/J163*100)</f>
       </c>
       <c r="AA163" s="3">
         <f>IF($K163="","",M163-X163)</f>
@@ -9125,7 +9125,7 @@
         <f>IF($K164="","",L164-M164-R164-S164-T164-U164-V164-W164)</f>
       </c>
       <c r="Z164" s="3">
-        <f>IF($K164="","",(Y164-AB164)/K164*100)</f>
+        <f>IF($K164="","",(Y164-AB164)/J164*100)</f>
       </c>
       <c r="AA164" s="3">
         <f>IF($K164="","",M164-X164)</f>
@@ -9176,7 +9176,7 @@
         <f>IF($K165="","",L165-M165-R165-S165-T165-U165-V165-W165)</f>
       </c>
       <c r="Z165" s="3">
-        <f>IF($K165="","",(Y165-AB165)/K165*100)</f>
+        <f>IF($K165="","",(Y165-AB165)/J165*100)</f>
       </c>
       <c r="AA165" s="3">
         <f>IF($K165="","",M165-X165)</f>
@@ -9227,7 +9227,7 @@
         <f>IF($K166="","",L166-M166-R166-S166-T166-U166-V166-W166)</f>
       </c>
       <c r="Z166" s="3">
-        <f>IF($K166="","",(Y166-AB166)/K166*100)</f>
+        <f>IF($K166="","",(Y166-AB166)/J166*100)</f>
       </c>
       <c r="AA166" s="3">
         <f>IF($K166="","",M166-X166)</f>
@@ -9278,7 +9278,7 @@
         <f>IF($K167="","",L167-M167-R167-S167-T167-U167-V167-W167)</f>
       </c>
       <c r="Z167" s="3">
-        <f>IF($K167="","",(Y167-AB167)/K167*100)</f>
+        <f>IF($K167="","",(Y167-AB167)/J167*100)</f>
       </c>
       <c r="AA167" s="3">
         <f>IF($K167="","",M167-X167)</f>
@@ -9329,7 +9329,7 @@
         <f>IF($K168="","",L168-M168-R168-S168-T168-U168-V168-W168)</f>
       </c>
       <c r="Z168" s="3">
-        <f>IF($K168="","",(Y168-AB168)/K168*100)</f>
+        <f>IF($K168="","",(Y168-AB168)/J168*100)</f>
       </c>
       <c r="AA168" s="3">
         <f>IF($K168="","",M168-X168)</f>
@@ -9380,7 +9380,7 @@
         <f>IF($K169="","",L169-M169-R169-S169-T169-U169-V169-W169)</f>
       </c>
       <c r="Z169" s="3">
-        <f>IF($K169="","",(Y169-AB169)/K169*100)</f>
+        <f>IF($K169="","",(Y169-AB169)/J169*100)</f>
       </c>
       <c r="AA169" s="3">
         <f>IF($K169="","",M169-X169)</f>
@@ -9431,7 +9431,7 @@
         <f>IF($K170="","",L170-M170-R170-S170-T170-U170-V170-W170)</f>
       </c>
       <c r="Z170" s="3">
-        <f>IF($K170="","",(Y170-AB170)/K170*100)</f>
+        <f>IF($K170="","",(Y170-AB170)/J170*100)</f>
       </c>
       <c r="AA170" s="3">
         <f>IF($K170="","",M170-X170)</f>
@@ -9482,7 +9482,7 @@
         <f>IF($K171="","",L171-M171-R171-S171-T171-U171-V171-W171)</f>
       </c>
       <c r="Z171" s="3">
-        <f>IF($K171="","",(Y171-AB171)/K171*100)</f>
+        <f>IF($K171="","",(Y171-AB171)/J171*100)</f>
       </c>
       <c r="AA171" s="3">
         <f>IF($K171="","",M171-X171)</f>
@@ -9533,7 +9533,7 @@
         <f>IF($K172="","",L172-M172-R172-S172-T172-U172-V172-W172)</f>
       </c>
       <c r="Z172" s="3">
-        <f>IF($K172="","",(Y172-AB172)/K172*100)</f>
+        <f>IF($K172="","",(Y172-AB172)/J172*100)</f>
       </c>
       <c r="AA172" s="3">
         <f>IF($K172="","",M172-X172)</f>
@@ -9584,7 +9584,7 @@
         <f>IF($K173="","",L173-M173-R173-S173-T173-U173-V173-W173)</f>
       </c>
       <c r="Z173" s="3">
-        <f>IF($K173="","",(Y173-AB173)/K173*100)</f>
+        <f>IF($K173="","",(Y173-AB173)/J173*100)</f>
       </c>
       <c r="AA173" s="3">
         <f>IF($K173="","",M173-X173)</f>
@@ -9635,7 +9635,7 @@
         <f>IF($K174="","",L174-M174-R174-S174-T174-U174-V174-W174)</f>
       </c>
       <c r="Z174" s="3">
-        <f>IF($K174="","",(Y174-AB174)/K174*100)</f>
+        <f>IF($K174="","",(Y174-AB174)/J174*100)</f>
       </c>
       <c r="AA174" s="3">
         <f>IF($K174="","",M174-X174)</f>
@@ -9686,7 +9686,7 @@
         <f>IF($K175="","",L175-M175-R175-S175-T175-U175-V175-W175)</f>
       </c>
       <c r="Z175" s="3">
-        <f>IF($K175="","",(Y175-AB175)/K175*100)</f>
+        <f>IF($K175="","",(Y175-AB175)/J175*100)</f>
       </c>
       <c r="AA175" s="3">
         <f>IF($K175="","",M175-X175)</f>
@@ -9737,7 +9737,7 @@
         <f>IF($K176="","",L176-M176-R176-S176-T176-U176-V176-W176)</f>
       </c>
       <c r="Z176" s="3">
-        <f>IF($K176="","",(Y176-AB176)/K176*100)</f>
+        <f>IF($K176="","",(Y176-AB176)/J176*100)</f>
       </c>
       <c r="AA176" s="3">
         <f>IF($K176="","",M176-X176)</f>
@@ -9788,7 +9788,7 @@
         <f>IF($K177="","",L177-M177-R177-S177-T177-U177-V177-W177)</f>
       </c>
       <c r="Z177" s="3">
-        <f>IF($K177="","",(Y177-AB177)/K177*100)</f>
+        <f>IF($K177="","",(Y177-AB177)/J177*100)</f>
       </c>
       <c r="AA177" s="3">
         <f>IF($K177="","",M177-X177)</f>
@@ -9839,7 +9839,7 @@
         <f>IF($K178="","",L178-M178-R178-S178-T178-U178-V178-W178)</f>
       </c>
       <c r="Z178" s="3">
-        <f>IF($K178="","",(Y178-AB178)/K178*100)</f>
+        <f>IF($K178="","",(Y178-AB178)/J178*100)</f>
       </c>
       <c r="AA178" s="3">
         <f>IF($K178="","",M178-X178)</f>
@@ -9890,7 +9890,7 @@
         <f>IF($K179="","",L179-M179-R179-S179-T179-U179-V179-W179)</f>
       </c>
       <c r="Z179" s="3">
-        <f>IF($K179="","",(Y179-AB179)/K179*100)</f>
+        <f>IF($K179="","",(Y179-AB179)/J179*100)</f>
       </c>
       <c r="AA179" s="3">
         <f>IF($K179="","",M179-X179)</f>
@@ -9941,7 +9941,7 @@
         <f>IF($K180="","",L180-M180-R180-S180-T180-U180-V180-W180)</f>
       </c>
       <c r="Z180" s="3">
-        <f>IF($K180="","",(Y180-AB180)/K180*100)</f>
+        <f>IF($K180="","",(Y180-AB180)/J180*100)</f>
       </c>
       <c r="AA180" s="3">
         <f>IF($K180="","",M180-X180)</f>
@@ -9992,7 +9992,7 @@
         <f>IF($K181="","",L181-M181-R181-S181-T181-U181-V181-W181)</f>
       </c>
       <c r="Z181" s="3">
-        <f>IF($K181="","",(Y181-AB181)/K181*100)</f>
+        <f>IF($K181="","",(Y181-AB181)/J181*100)</f>
       </c>
       <c r="AA181" s="3">
         <f>IF($K181="","",M181-X181)</f>
@@ -10043,7 +10043,7 @@
         <f>IF($K182="","",L182-M182-R182-S182-T182-U182-V182-W182)</f>
       </c>
       <c r="Z182" s="3">
-        <f>IF($K182="","",(Y182-AB182)/K182*100)</f>
+        <f>IF($K182="","",(Y182-AB182)/J182*100)</f>
       </c>
       <c r="AA182" s="3">
         <f>IF($K182="","",M182-X182)</f>
@@ -10094,7 +10094,7 @@
         <f>IF($K183="","",L183-M183-R183-S183-T183-U183-V183-W183)</f>
       </c>
       <c r="Z183" s="3">
-        <f>IF($K183="","",(Y183-AB183)/K183*100)</f>
+        <f>IF($K183="","",(Y183-AB183)/J183*100)</f>
       </c>
       <c r="AA183" s="3">
         <f>IF($K183="","",M183-X183)</f>
@@ -10145,7 +10145,7 @@
         <f>IF($K184="","",L184-M184-R184-S184-T184-U184-V184-W184)</f>
       </c>
       <c r="Z184" s="3">
-        <f>IF($K184="","",(Y184-AB184)/K184*100)</f>
+        <f>IF($K184="","",(Y184-AB184)/J184*100)</f>
       </c>
       <c r="AA184" s="3">
         <f>IF($K184="","",M184-X184)</f>
@@ -10196,7 +10196,7 @@
         <f>IF($K185="","",L185-M185-R185-S185-T185-U185-V185-W185)</f>
       </c>
       <c r="Z185" s="3">
-        <f>IF($K185="","",(Y185-AB185)/K185*100)</f>
+        <f>IF($K185="","",(Y185-AB185)/J185*100)</f>
       </c>
       <c r="AA185" s="3">
         <f>IF($K185="","",M185-X185)</f>
@@ -10247,7 +10247,7 @@
         <f>IF($K186="","",L186-M186-R186-S186-T186-U186-V186-W186)</f>
       </c>
       <c r="Z186" s="3">
-        <f>IF($K186="","",(Y186-AB186)/K186*100)</f>
+        <f>IF($K186="","",(Y186-AB186)/J186*100)</f>
       </c>
       <c r="AA186" s="3">
         <f>IF($K186="","",M186-X186)</f>
@@ -10298,7 +10298,7 @@
         <f>IF($K187="","",L187-M187-R187-S187-T187-U187-V187-W187)</f>
       </c>
       <c r="Z187" s="3">
-        <f>IF($K187="","",(Y187-AB187)/K187*100)</f>
+        <f>IF($K187="","",(Y187-AB187)/J187*100)</f>
       </c>
       <c r="AA187" s="3">
         <f>IF($K187="","",M187-X187)</f>
@@ -10349,7 +10349,7 @@
         <f>IF($K188="","",L188-M188-R188-S188-T188-U188-V188-W188)</f>
       </c>
       <c r="Z188" s="3">
-        <f>IF($K188="","",(Y188-AB188)/K188*100)</f>
+        <f>IF($K188="","",(Y188-AB188)/J188*100)</f>
       </c>
       <c r="AA188" s="3">
         <f>IF($K188="","",M188-X188)</f>
@@ -10400,7 +10400,7 @@
         <f>IF($K189="","",L189-M189-R189-S189-T189-U189-V189-W189)</f>
       </c>
       <c r="Z189" s="3">
-        <f>IF($K189="","",(Y189-AB189)/K189*100)</f>
+        <f>IF($K189="","",(Y189-AB189)/J189*100)</f>
       </c>
       <c r="AA189" s="3">
         <f>IF($K189="","",M189-X189)</f>
@@ -10451,7 +10451,7 @@
         <f>IF($K190="","",L190-M190-R190-S190-T190-U190-V190-W190)</f>
       </c>
       <c r="Z190" s="3">
-        <f>IF($K190="","",(Y190-AB190)/K190*100)</f>
+        <f>IF($K190="","",(Y190-AB190)/J190*100)</f>
       </c>
       <c r="AA190" s="3">
         <f>IF($K190="","",M190-X190)</f>
@@ -10502,7 +10502,7 @@
         <f>IF($K191="","",L191-M191-R191-S191-T191-U191-V191-W191)</f>
       </c>
       <c r="Z191" s="3">
-        <f>IF($K191="","",(Y191-AB191)/K191*100)</f>
+        <f>IF($K191="","",(Y191-AB191)/J191*100)</f>
       </c>
       <c r="AA191" s="3">
         <f>IF($K191="","",M191-X191)</f>
@@ -10553,7 +10553,7 @@
         <f>IF($K192="","",L192-M192-R192-S192-T192-U192-V192-W192)</f>
       </c>
       <c r="Z192" s="3">
-        <f>IF($K192="","",(Y192-AB192)/K192*100)</f>
+        <f>IF($K192="","",(Y192-AB192)/J192*100)</f>
       </c>
       <c r="AA192" s="3">
         <f>IF($K192="","",M192-X192)</f>
@@ -10604,7 +10604,7 @@
         <f>IF($K193="","",L193-M193-R193-S193-T193-U193-V193-W193)</f>
       </c>
       <c r="Z193" s="3">
-        <f>IF($K193="","",(Y193-AB193)/K193*100)</f>
+        <f>IF($K193="","",(Y193-AB193)/J193*100)</f>
       </c>
       <c r="AA193" s="3">
         <f>IF($K193="","",M193-X193)</f>
@@ -10655,7 +10655,7 @@
         <f>IF($K194="","",L194-M194-R194-S194-T194-U194-V194-W194)</f>
       </c>
       <c r="Z194" s="3">
-        <f>IF($K194="","",(Y194-AB194)/K194*100)</f>
+        <f>IF($K194="","",(Y194-AB194)/J194*100)</f>
       </c>
       <c r="AA194" s="3">
         <f>IF($K194="","",M194-X194)</f>
@@ -10706,7 +10706,7 @@
         <f>IF($K195="","",L195-M195-R195-S195-T195-U195-V195-W195)</f>
       </c>
       <c r="Z195" s="3">
-        <f>IF($K195="","",(Y195-AB195)/K195*100)</f>
+        <f>IF($K195="","",(Y195-AB195)/J195*100)</f>
       </c>
       <c r="AA195" s="3">
         <f>IF($K195="","",M195-X195)</f>
@@ -10757,7 +10757,7 @@
         <f>IF($K196="","",L196-M196-R196-S196-T196-U196-V196-W196)</f>
       </c>
       <c r="Z196" s="3">
-        <f>IF($K196="","",(Y196-AB196)/K196*100)</f>
+        <f>IF($K196="","",(Y196-AB196)/J196*100)</f>
       </c>
       <c r="AA196" s="3">
         <f>IF($K196="","",M196-X196)</f>
@@ -10808,7 +10808,7 @@
         <f>IF($K197="","",L197-M197-R197-S197-T197-U197-V197-W197)</f>
       </c>
       <c r="Z197" s="3">
-        <f>IF($K197="","",(Y197-AB197)/K197*100)</f>
+        <f>IF($K197="","",(Y197-AB197)/J197*100)</f>
       </c>
       <c r="AA197" s="3">
         <f>IF($K197="","",M197-X197)</f>
@@ -10859,7 +10859,7 @@
         <f>IF($K198="","",L198-M198-R198-S198-T198-U198-V198-W198)</f>
       </c>
       <c r="Z198" s="3">
-        <f>IF($K198="","",(Y198-AB198)/K198*100)</f>
+        <f>IF($K198="","",(Y198-AB198)/J198*100)</f>
       </c>
       <c r="AA198" s="3">
         <f>IF($K198="","",M198-X198)</f>
@@ -10910,7 +10910,7 @@
         <f>IF($K199="","",L199-M199-R199-S199-T199-U199-V199-W199)</f>
       </c>
       <c r="Z199" s="3">
-        <f>IF($K199="","",(Y199-AB199)/K199*100)</f>
+        <f>IF($K199="","",(Y199-AB199)/J199*100)</f>
       </c>
       <c r="AA199" s="3">
         <f>IF($K199="","",M199-X199)</f>
@@ -10961,7 +10961,7 @@
         <f>IF($K200="","",L200-M200-R200-S200-T200-U200-V200-W200)</f>
       </c>
       <c r="Z200" s="3">
-        <f>IF($K200="","",(Y200-AB200)/K200*100)</f>
+        <f>IF($K200="","",(Y200-AB200)/J200*100)</f>
       </c>
       <c r="AA200" s="3">
         <f>IF($K200="","",M200-X200)</f>
@@ -11012,7 +11012,7 @@
         <f>IF($K201="","",L201-M201-R201-S201-T201-U201-V201-W201)</f>
       </c>
       <c r="Z201" s="3">
-        <f>IF($K201="","",(Y201-AB201)/K201*100)</f>
+        <f>IF($K201="","",(Y201-AB201)/J201*100)</f>
       </c>
       <c r="AA201" s="3">
         <f>IF($K201="","",M201-X201)</f>
@@ -11063,7 +11063,7 @@
         <f>IF($K202="","",L202-M202-R202-S202-T202-U202-V202-W202)</f>
       </c>
       <c r="Z202" s="3">
-        <f>IF($K202="","",(Y202-AB202)/K202*100)</f>
+        <f>IF($K202="","",(Y202-AB202)/J202*100)</f>
       </c>
       <c r="AA202" s="3">
         <f>IF($K202="","",M202-X202)</f>

--- a/public/templates/SALES_EBAY_TEMPLATE.xlsx
+++ b/public/templates/SALES_EBAY_TEMPLATE.xlsx
@@ -80,7 +80,7 @@
     <t>M. VAT</t>
   </si>
   <si>
-    <t>Accessories</t>
+    <t>Acc</t>
   </si>
   <si>
     <t>Total VAT</t>

--- a/public/templates/SALES_EBAY_TEMPLATE.xlsx
+++ b/public/templates/SALES_EBAY_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>Date</t>
   </si>
@@ -96,6 +96,18 @@
   </si>
   <si>
     <t>Postage Loss</t>
+  </si>
+  <si>
+    <t>Fees Kept</t>
+  </si>
+  <si>
+    <t>Repair Cost</t>
+  </si>
+  <si>
+    <t>Supplier Credit</t>
+  </si>
+  <si>
+    <t>Return Cost</t>
   </si>
   <si>
     <t>Net GP £</t>
@@ -598,74 +610,74 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -676,10 +688,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH203"/>
+  <dimension ref="A1:AL203"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -782,31 +794,43 @@
       <c r="AH1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46235.5</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -860,19 +884,19 @@
         <f>L2-M2-R2-S2-T2-U2-V2-W2</f>
       </c>
       <c r="Z2" s="3">
-        <f>(Y2-AB2)/J2*100</f>
+        <f>(Y2-AF2)/J2*100</f>
       </c>
       <c r="AA2" s="3">
         <f>M2-X2</f>
       </c>
-      <c r="AC2" s="3">
-        <f>Y2-AB2</f>
-      </c>
-      <c r="AH2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG2" s="3">
+        <f>Y2-AF2</f>
+      </c>
+      <c r="AL2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="D3" s="2"/>
       <c r="J3" s="3"/>
@@ -914,16 +938,16 @@
         <f>IF($K3="","",L3-M3-R3-S3-T3-U3-V3-W3)</f>
       </c>
       <c r="Z3" s="3">
-        <f>IF($K3="","",(Y3-AB3)/J3*100)</f>
+        <f>IF($K3="","",(Y3-AF3)/J3*100)</f>
       </c>
       <c r="AA3" s="3">
         <f>IF($K3="","",M3-X3)</f>
       </c>
-      <c r="AC3" s="3">
-        <f>IF($K3="","",Y3-AB3)</f>
-      </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG3" s="3">
+        <f>IF($K3="","",Y3-AF3)</f>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="D4" s="2"/>
       <c r="J4" s="3"/>
@@ -965,16 +989,16 @@
         <f>IF($K4="","",L4-M4-R4-S4-T4-U4-V4-W4)</f>
       </c>
       <c r="Z4" s="3">
-        <f>IF($K4="","",(Y4-AB4)/J4*100)</f>
+        <f>IF($K4="","",(Y4-AF4)/J4*100)</f>
       </c>
       <c r="AA4" s="3">
         <f>IF($K4="","",M4-X4)</f>
       </c>
-      <c r="AC4" s="3">
-        <f>IF($K4="","",Y4-AB4)</f>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG4" s="3">
+        <f>IF($K4="","",Y4-AF4)</f>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="D5" s="2"/>
       <c r="J5" s="3"/>
@@ -1016,16 +1040,16 @@
         <f>IF($K5="","",L5-M5-R5-S5-T5-U5-V5-W5)</f>
       </c>
       <c r="Z5" s="3">
-        <f>IF($K5="","",(Y5-AB5)/J5*100)</f>
+        <f>IF($K5="","",(Y5-AF5)/J5*100)</f>
       </c>
       <c r="AA5" s="3">
         <f>IF($K5="","",M5-X5)</f>
       </c>
-      <c r="AC5" s="3">
-        <f>IF($K5="","",Y5-AB5)</f>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG5" s="3">
+        <f>IF($K5="","",Y5-AF5)</f>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="D6" s="2"/>
       <c r="J6" s="3"/>
@@ -1067,16 +1091,16 @@
         <f>IF($K6="","",L6-M6-R6-S6-T6-U6-V6-W6)</f>
       </c>
       <c r="Z6" s="3">
-        <f>IF($K6="","",(Y6-AB6)/J6*100)</f>
+        <f>IF($K6="","",(Y6-AF6)/J6*100)</f>
       </c>
       <c r="AA6" s="3">
         <f>IF($K6="","",M6-X6)</f>
       </c>
-      <c r="AC6" s="3">
-        <f>IF($K6="","",Y6-AB6)</f>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG6" s="3">
+        <f>IF($K6="","",Y6-AF6)</f>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="D7" s="2"/>
       <c r="J7" s="3"/>
@@ -1118,16 +1142,16 @@
         <f>IF($K7="","",L7-M7-R7-S7-T7-U7-V7-W7)</f>
       </c>
       <c r="Z7" s="3">
-        <f>IF($K7="","",(Y7-AB7)/J7*100)</f>
+        <f>IF($K7="","",(Y7-AF7)/J7*100)</f>
       </c>
       <c r="AA7" s="3">
         <f>IF($K7="","",M7-X7)</f>
       </c>
-      <c r="AC7" s="3">
-        <f>IF($K7="","",Y7-AB7)</f>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG7" s="3">
+        <f>IF($K7="","",Y7-AF7)</f>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="D8" s="2"/>
       <c r="J8" s="3"/>
@@ -1169,16 +1193,16 @@
         <f>IF($K8="","",L8-M8-R8-S8-T8-U8-V8-W8)</f>
       </c>
       <c r="Z8" s="3">
-        <f>IF($K8="","",(Y8-AB8)/J8*100)</f>
+        <f>IF($K8="","",(Y8-AF8)/J8*100)</f>
       </c>
       <c r="AA8" s="3">
         <f>IF($K8="","",M8-X8)</f>
       </c>
-      <c r="AC8" s="3">
-        <f>IF($K8="","",Y8-AB8)</f>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG8" s="3">
+        <f>IF($K8="","",Y8-AF8)</f>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="D9" s="2"/>
       <c r="J9" s="3"/>
@@ -1220,16 +1244,16 @@
         <f>IF($K9="","",L9-M9-R9-S9-T9-U9-V9-W9)</f>
       </c>
       <c r="Z9" s="3">
-        <f>IF($K9="","",(Y9-AB9)/J9*100)</f>
+        <f>IF($K9="","",(Y9-AF9)/J9*100)</f>
       </c>
       <c r="AA9" s="3">
         <f>IF($K9="","",M9-X9)</f>
       </c>
-      <c r="AC9" s="3">
-        <f>IF($K9="","",Y9-AB9)</f>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG9" s="3">
+        <f>IF($K9="","",Y9-AF9)</f>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="D10" s="2"/>
       <c r="J10" s="3"/>
@@ -1271,16 +1295,16 @@
         <f>IF($K10="","",L10-M10-R10-S10-T10-U10-V10-W10)</f>
       </c>
       <c r="Z10" s="3">
-        <f>IF($K10="","",(Y10-AB10)/J10*100)</f>
+        <f>IF($K10="","",(Y10-AF10)/J10*100)</f>
       </c>
       <c r="AA10" s="3">
         <f>IF($K10="","",M10-X10)</f>
       </c>
-      <c r="AC10" s="3">
-        <f>IF($K10="","",Y10-AB10)</f>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG10" s="3">
+        <f>IF($K10="","",Y10-AF10)</f>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="D11" s="2"/>
       <c r="J11" s="3"/>
@@ -1322,16 +1346,16 @@
         <f>IF($K11="","",L11-M11-R11-S11-T11-U11-V11-W11)</f>
       </c>
       <c r="Z11" s="3">
-        <f>IF($K11="","",(Y11-AB11)/J11*100)</f>
+        <f>IF($K11="","",(Y11-AF11)/J11*100)</f>
       </c>
       <c r="AA11" s="3">
         <f>IF($K11="","",M11-X11)</f>
       </c>
-      <c r="AC11" s="3">
-        <f>IF($K11="","",Y11-AB11)</f>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG11" s="3">
+        <f>IF($K11="","",Y11-AF11)</f>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="D12" s="2"/>
       <c r="J12" s="3"/>
@@ -1373,16 +1397,16 @@
         <f>IF($K12="","",L12-M12-R12-S12-T12-U12-V12-W12)</f>
       </c>
       <c r="Z12" s="3">
-        <f>IF($K12="","",(Y12-AB12)/J12*100)</f>
+        <f>IF($K12="","",(Y12-AF12)/J12*100)</f>
       </c>
       <c r="AA12" s="3">
         <f>IF($K12="","",M12-X12)</f>
       </c>
-      <c r="AC12" s="3">
-        <f>IF($K12="","",Y12-AB12)</f>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG12" s="3">
+        <f>IF($K12="","",Y12-AF12)</f>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="D13" s="2"/>
       <c r="J13" s="3"/>
@@ -1424,16 +1448,16 @@
         <f>IF($K13="","",L13-M13-R13-S13-T13-U13-V13-W13)</f>
       </c>
       <c r="Z13" s="3">
-        <f>IF($K13="","",(Y13-AB13)/J13*100)</f>
+        <f>IF($K13="","",(Y13-AF13)/J13*100)</f>
       </c>
       <c r="AA13" s="3">
         <f>IF($K13="","",M13-X13)</f>
       </c>
-      <c r="AC13" s="3">
-        <f>IF($K13="","",Y13-AB13)</f>
-      </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG13" s="3">
+        <f>IF($K13="","",Y13-AF13)</f>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="2"/>
       <c r="J14" s="3"/>
@@ -1475,16 +1499,16 @@
         <f>IF($K14="","",L14-M14-R14-S14-T14-U14-V14-W14)</f>
       </c>
       <c r="Z14" s="3">
-        <f>IF($K14="","",(Y14-AB14)/J14*100)</f>
+        <f>IF($K14="","",(Y14-AF14)/J14*100)</f>
       </c>
       <c r="AA14" s="3">
         <f>IF($K14="","",M14-X14)</f>
       </c>
-      <c r="AC14" s="3">
-        <f>IF($K14="","",Y14-AB14)</f>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG14" s="3">
+        <f>IF($K14="","",Y14-AF14)</f>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="D15" s="2"/>
       <c r="J15" s="3"/>
@@ -1526,16 +1550,16 @@
         <f>IF($K15="","",L15-M15-R15-S15-T15-U15-V15-W15)</f>
       </c>
       <c r="Z15" s="3">
-        <f>IF($K15="","",(Y15-AB15)/J15*100)</f>
+        <f>IF($K15="","",(Y15-AF15)/J15*100)</f>
       </c>
       <c r="AA15" s="3">
         <f>IF($K15="","",M15-X15)</f>
       </c>
-      <c r="AC15" s="3">
-        <f>IF($K15="","",Y15-AB15)</f>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG15" s="3">
+        <f>IF($K15="","",Y15-AF15)</f>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="D16" s="2"/>
       <c r="J16" s="3"/>
@@ -1577,16 +1601,16 @@
         <f>IF($K16="","",L16-M16-R16-S16-T16-U16-V16-W16)</f>
       </c>
       <c r="Z16" s="3">
-        <f>IF($K16="","",(Y16-AB16)/J16*100)</f>
+        <f>IF($K16="","",(Y16-AF16)/J16*100)</f>
       </c>
       <c r="AA16" s="3">
         <f>IF($K16="","",M16-X16)</f>
       </c>
-      <c r="AC16" s="3">
-        <f>IF($K16="","",Y16-AB16)</f>
-      </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG16" s="3">
+        <f>IF($K16="","",Y16-AF16)</f>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="D17" s="2"/>
       <c r="J17" s="3"/>
@@ -1628,16 +1652,16 @@
         <f>IF($K17="","",L17-M17-R17-S17-T17-U17-V17-W17)</f>
       </c>
       <c r="Z17" s="3">
-        <f>IF($K17="","",(Y17-AB17)/J17*100)</f>
+        <f>IF($K17="","",(Y17-AF17)/J17*100)</f>
       </c>
       <c r="AA17" s="3">
         <f>IF($K17="","",M17-X17)</f>
       </c>
-      <c r="AC17" s="3">
-        <f>IF($K17="","",Y17-AB17)</f>
-      </c>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG17" s="3">
+        <f>IF($K17="","",Y17-AF17)</f>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="D18" s="2"/>
       <c r="J18" s="3"/>
@@ -1679,16 +1703,16 @@
         <f>IF($K18="","",L18-M18-R18-S18-T18-U18-V18-W18)</f>
       </c>
       <c r="Z18" s="3">
-        <f>IF($K18="","",(Y18-AB18)/J18*100)</f>
+        <f>IF($K18="","",(Y18-AF18)/J18*100)</f>
       </c>
       <c r="AA18" s="3">
         <f>IF($K18="","",M18-X18)</f>
       </c>
-      <c r="AC18" s="3">
-        <f>IF($K18="","",Y18-AB18)</f>
-      </c>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG18" s="3">
+        <f>IF($K18="","",Y18-AF18)</f>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="D19" s="2"/>
       <c r="J19" s="3"/>
@@ -1730,16 +1754,16 @@
         <f>IF($K19="","",L19-M19-R19-S19-T19-U19-V19-W19)</f>
       </c>
       <c r="Z19" s="3">
-        <f>IF($K19="","",(Y19-AB19)/J19*100)</f>
+        <f>IF($K19="","",(Y19-AF19)/J19*100)</f>
       </c>
       <c r="AA19" s="3">
         <f>IF($K19="","",M19-X19)</f>
       </c>
-      <c r="AC19" s="3">
-        <f>IF($K19="","",Y19-AB19)</f>
-      </c>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG19" s="3">
+        <f>IF($K19="","",Y19-AF19)</f>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="D20" s="2"/>
       <c r="J20" s="3"/>
@@ -1781,16 +1805,16 @@
         <f>IF($K20="","",L20-M20-R20-S20-T20-U20-V20-W20)</f>
       </c>
       <c r="Z20" s="3">
-        <f>IF($K20="","",(Y20-AB20)/J20*100)</f>
+        <f>IF($K20="","",(Y20-AF20)/J20*100)</f>
       </c>
       <c r="AA20" s="3">
         <f>IF($K20="","",M20-X20)</f>
       </c>
-      <c r="AC20" s="3">
-        <f>IF($K20="","",Y20-AB20)</f>
-      </c>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG20" s="3">
+        <f>IF($K20="","",Y20-AF20)</f>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="D21" s="2"/>
       <c r="J21" s="3"/>
@@ -1832,16 +1856,16 @@
         <f>IF($K21="","",L21-M21-R21-S21-T21-U21-V21-W21)</f>
       </c>
       <c r="Z21" s="3">
-        <f>IF($K21="","",(Y21-AB21)/J21*100)</f>
+        <f>IF($K21="","",(Y21-AF21)/J21*100)</f>
       </c>
       <c r="AA21" s="3">
         <f>IF($K21="","",M21-X21)</f>
       </c>
-      <c r="AC21" s="3">
-        <f>IF($K21="","",Y21-AB21)</f>
-      </c>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG21" s="3">
+        <f>IF($K21="","",Y21-AF21)</f>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="D22" s="2"/>
       <c r="J22" s="3"/>
@@ -1883,16 +1907,16 @@
         <f>IF($K22="","",L22-M22-R22-S22-T22-U22-V22-W22)</f>
       </c>
       <c r="Z22" s="3">
-        <f>IF($K22="","",(Y22-AB22)/J22*100)</f>
+        <f>IF($K22="","",(Y22-AF22)/J22*100)</f>
       </c>
       <c r="AA22" s="3">
         <f>IF($K22="","",M22-X22)</f>
       </c>
-      <c r="AC22" s="3">
-        <f>IF($K22="","",Y22-AB22)</f>
-      </c>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG22" s="3">
+        <f>IF($K22="","",Y22-AF22)</f>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="D23" s="2"/>
       <c r="J23" s="3"/>
@@ -1934,16 +1958,16 @@
         <f>IF($K23="","",L23-M23-R23-S23-T23-U23-V23-W23)</f>
       </c>
       <c r="Z23" s="3">
-        <f>IF($K23="","",(Y23-AB23)/J23*100)</f>
+        <f>IF($K23="","",(Y23-AF23)/J23*100)</f>
       </c>
       <c r="AA23" s="3">
         <f>IF($K23="","",M23-X23)</f>
       </c>
-      <c r="AC23" s="3">
-        <f>IF($K23="","",Y23-AB23)</f>
-      </c>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG23" s="3">
+        <f>IF($K23="","",Y23-AF23)</f>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="2"/>
       <c r="J24" s="3"/>
@@ -1985,16 +2009,16 @@
         <f>IF($K24="","",L24-M24-R24-S24-T24-U24-V24-W24)</f>
       </c>
       <c r="Z24" s="3">
-        <f>IF($K24="","",(Y24-AB24)/J24*100)</f>
+        <f>IF($K24="","",(Y24-AF24)/J24*100)</f>
       </c>
       <c r="AA24" s="3">
         <f>IF($K24="","",M24-X24)</f>
       </c>
-      <c r="AC24" s="3">
-        <f>IF($K24="","",Y24-AB24)</f>
-      </c>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG24" s="3">
+        <f>IF($K24="","",Y24-AF24)</f>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="D25" s="2"/>
       <c r="J25" s="3"/>
@@ -2036,16 +2060,16 @@
         <f>IF($K25="","",L25-M25-R25-S25-T25-U25-V25-W25)</f>
       </c>
       <c r="Z25" s="3">
-        <f>IF($K25="","",(Y25-AB25)/J25*100)</f>
+        <f>IF($K25="","",(Y25-AF25)/J25*100)</f>
       </c>
       <c r="AA25" s="3">
         <f>IF($K25="","",M25-X25)</f>
       </c>
-      <c r="AC25" s="3">
-        <f>IF($K25="","",Y25-AB25)</f>
-      </c>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG25" s="3">
+        <f>IF($K25="","",Y25-AF25)</f>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="D26" s="2"/>
       <c r="J26" s="3"/>
@@ -2087,16 +2111,16 @@
         <f>IF($K26="","",L26-M26-R26-S26-T26-U26-V26-W26)</f>
       </c>
       <c r="Z26" s="3">
-        <f>IF($K26="","",(Y26-AB26)/J26*100)</f>
+        <f>IF($K26="","",(Y26-AF26)/J26*100)</f>
       </c>
       <c r="AA26" s="3">
         <f>IF($K26="","",M26-X26)</f>
       </c>
-      <c r="AC26" s="3">
-        <f>IF($K26="","",Y26-AB26)</f>
-      </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG26" s="3">
+        <f>IF($K26="","",Y26-AF26)</f>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="D27" s="2"/>
       <c r="J27" s="3"/>
@@ -2138,16 +2162,16 @@
         <f>IF($K27="","",L27-M27-R27-S27-T27-U27-V27-W27)</f>
       </c>
       <c r="Z27" s="3">
-        <f>IF($K27="","",(Y27-AB27)/J27*100)</f>
+        <f>IF($K27="","",(Y27-AF27)/J27*100)</f>
       </c>
       <c r="AA27" s="3">
         <f>IF($K27="","",M27-X27)</f>
       </c>
-      <c r="AC27" s="3">
-        <f>IF($K27="","",Y27-AB27)</f>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG27" s="3">
+        <f>IF($K27="","",Y27-AF27)</f>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="D28" s="2"/>
       <c r="J28" s="3"/>
@@ -2189,16 +2213,16 @@
         <f>IF($K28="","",L28-M28-R28-S28-T28-U28-V28-W28)</f>
       </c>
       <c r="Z28" s="3">
-        <f>IF($K28="","",(Y28-AB28)/J28*100)</f>
+        <f>IF($K28="","",(Y28-AF28)/J28*100)</f>
       </c>
       <c r="AA28" s="3">
         <f>IF($K28="","",M28-X28)</f>
       </c>
-      <c r="AC28" s="3">
-        <f>IF($K28="","",Y28-AB28)</f>
-      </c>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG28" s="3">
+        <f>IF($K28="","",Y28-AF28)</f>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="D29" s="2"/>
       <c r="J29" s="3"/>
@@ -2240,16 +2264,16 @@
         <f>IF($K29="","",L29-M29-R29-S29-T29-U29-V29-W29)</f>
       </c>
       <c r="Z29" s="3">
-        <f>IF($K29="","",(Y29-AB29)/J29*100)</f>
+        <f>IF($K29="","",(Y29-AF29)/J29*100)</f>
       </c>
       <c r="AA29" s="3">
         <f>IF($K29="","",M29-X29)</f>
       </c>
-      <c r="AC29" s="3">
-        <f>IF($K29="","",Y29-AB29)</f>
-      </c>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG29" s="3">
+        <f>IF($K29="","",Y29-AF29)</f>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="D30" s="2"/>
       <c r="J30" s="3"/>
@@ -2291,16 +2315,16 @@
         <f>IF($K30="","",L30-M30-R30-S30-T30-U30-V30-W30)</f>
       </c>
       <c r="Z30" s="3">
-        <f>IF($K30="","",(Y30-AB30)/J30*100)</f>
+        <f>IF($K30="","",(Y30-AF30)/J30*100)</f>
       </c>
       <c r="AA30" s="3">
         <f>IF($K30="","",M30-X30)</f>
       </c>
-      <c r="AC30" s="3">
-        <f>IF($K30="","",Y30-AB30)</f>
-      </c>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG30" s="3">
+        <f>IF($K30="","",Y30-AF30)</f>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="D31" s="2"/>
       <c r="J31" s="3"/>
@@ -2342,16 +2366,16 @@
         <f>IF($K31="","",L31-M31-R31-S31-T31-U31-V31-W31)</f>
       </c>
       <c r="Z31" s="3">
-        <f>IF($K31="","",(Y31-AB31)/J31*100)</f>
+        <f>IF($K31="","",(Y31-AF31)/J31*100)</f>
       </c>
       <c r="AA31" s="3">
         <f>IF($K31="","",M31-X31)</f>
       </c>
-      <c r="AC31" s="3">
-        <f>IF($K31="","",Y31-AB31)</f>
-      </c>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG31" s="3">
+        <f>IF($K31="","",Y31-AF31)</f>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="D32" s="2"/>
       <c r="J32" s="3"/>
@@ -2393,16 +2417,16 @@
         <f>IF($K32="","",L32-M32-R32-S32-T32-U32-V32-W32)</f>
       </c>
       <c r="Z32" s="3">
-        <f>IF($K32="","",(Y32-AB32)/J32*100)</f>
+        <f>IF($K32="","",(Y32-AF32)/J32*100)</f>
       </c>
       <c r="AA32" s="3">
         <f>IF($K32="","",M32-X32)</f>
       </c>
-      <c r="AC32" s="3">
-        <f>IF($K32="","",Y32-AB32)</f>
-      </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG32" s="3">
+        <f>IF($K32="","",Y32-AF32)</f>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="D33" s="2"/>
       <c r="J33" s="3"/>
@@ -2444,16 +2468,16 @@
         <f>IF($K33="","",L33-M33-R33-S33-T33-U33-V33-W33)</f>
       </c>
       <c r="Z33" s="3">
-        <f>IF($K33="","",(Y33-AB33)/J33*100)</f>
+        <f>IF($K33="","",(Y33-AF33)/J33*100)</f>
       </c>
       <c r="AA33" s="3">
         <f>IF($K33="","",M33-X33)</f>
       </c>
-      <c r="AC33" s="3">
-        <f>IF($K33="","",Y33-AB33)</f>
-      </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG33" s="3">
+        <f>IF($K33="","",Y33-AF33)</f>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="D34" s="2"/>
       <c r="J34" s="3"/>
@@ -2495,16 +2519,16 @@
         <f>IF($K34="","",L34-M34-R34-S34-T34-U34-V34-W34)</f>
       </c>
       <c r="Z34" s="3">
-        <f>IF($K34="","",(Y34-AB34)/J34*100)</f>
+        <f>IF($K34="","",(Y34-AF34)/J34*100)</f>
       </c>
       <c r="AA34" s="3">
         <f>IF($K34="","",M34-X34)</f>
       </c>
-      <c r="AC34" s="3">
-        <f>IF($K34="","",Y34-AB34)</f>
-      </c>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG34" s="3">
+        <f>IF($K34="","",Y34-AF34)</f>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="D35" s="2"/>
       <c r="J35" s="3"/>
@@ -2546,16 +2570,16 @@
         <f>IF($K35="","",L35-M35-R35-S35-T35-U35-V35-W35)</f>
       </c>
       <c r="Z35" s="3">
-        <f>IF($K35="","",(Y35-AB35)/J35*100)</f>
+        <f>IF($K35="","",(Y35-AF35)/J35*100)</f>
       </c>
       <c r="AA35" s="3">
         <f>IF($K35="","",M35-X35)</f>
       </c>
-      <c r="AC35" s="3">
-        <f>IF($K35="","",Y35-AB35)</f>
-      </c>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG35" s="3">
+        <f>IF($K35="","",Y35-AF35)</f>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="D36" s="2"/>
       <c r="J36" s="3"/>
@@ -2597,16 +2621,16 @@
         <f>IF($K36="","",L36-M36-R36-S36-T36-U36-V36-W36)</f>
       </c>
       <c r="Z36" s="3">
-        <f>IF($K36="","",(Y36-AB36)/J36*100)</f>
+        <f>IF($K36="","",(Y36-AF36)/J36*100)</f>
       </c>
       <c r="AA36" s="3">
         <f>IF($K36="","",M36-X36)</f>
       </c>
-      <c r="AC36" s="3">
-        <f>IF($K36="","",Y36-AB36)</f>
-      </c>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG36" s="3">
+        <f>IF($K36="","",Y36-AF36)</f>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="2"/>
       <c r="J37" s="3"/>
@@ -2648,16 +2672,16 @@
         <f>IF($K37="","",L37-M37-R37-S37-T37-U37-V37-W37)</f>
       </c>
       <c r="Z37" s="3">
-        <f>IF($K37="","",(Y37-AB37)/J37*100)</f>
+        <f>IF($K37="","",(Y37-AF37)/J37*100)</f>
       </c>
       <c r="AA37" s="3">
         <f>IF($K37="","",M37-X37)</f>
       </c>
-      <c r="AC37" s="3">
-        <f>IF($K37="","",Y37-AB37)</f>
-      </c>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG37" s="3">
+        <f>IF($K37="","",Y37-AF37)</f>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="D38" s="2"/>
       <c r="J38" s="3"/>
@@ -2699,16 +2723,16 @@
         <f>IF($K38="","",L38-M38-R38-S38-T38-U38-V38-W38)</f>
       </c>
       <c r="Z38" s="3">
-        <f>IF($K38="","",(Y38-AB38)/J38*100)</f>
+        <f>IF($K38="","",(Y38-AF38)/J38*100)</f>
       </c>
       <c r="AA38" s="3">
         <f>IF($K38="","",M38-X38)</f>
       </c>
-      <c r="AC38" s="3">
-        <f>IF($K38="","",Y38-AB38)</f>
-      </c>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG38" s="3">
+        <f>IF($K38="","",Y38-AF38)</f>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="D39" s="2"/>
       <c r="J39" s="3"/>
@@ -2750,16 +2774,16 @@
         <f>IF($K39="","",L39-M39-R39-S39-T39-U39-V39-W39)</f>
       </c>
       <c r="Z39" s="3">
-        <f>IF($K39="","",(Y39-AB39)/J39*100)</f>
+        <f>IF($K39="","",(Y39-AF39)/J39*100)</f>
       </c>
       <c r="AA39" s="3">
         <f>IF($K39="","",M39-X39)</f>
       </c>
-      <c r="AC39" s="3">
-        <f>IF($K39="","",Y39-AB39)</f>
-      </c>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG39" s="3">
+        <f>IF($K39="","",Y39-AF39)</f>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="D40" s="2"/>
       <c r="J40" s="3"/>
@@ -2801,16 +2825,16 @@
         <f>IF($K40="","",L40-M40-R40-S40-T40-U40-V40-W40)</f>
       </c>
       <c r="Z40" s="3">
-        <f>IF($K40="","",(Y40-AB40)/J40*100)</f>
+        <f>IF($K40="","",(Y40-AF40)/J40*100)</f>
       </c>
       <c r="AA40" s="3">
         <f>IF($K40="","",M40-X40)</f>
       </c>
-      <c r="AC40" s="3">
-        <f>IF($K40="","",Y40-AB40)</f>
-      </c>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG40" s="3">
+        <f>IF($K40="","",Y40-AF40)</f>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="D41" s="2"/>
       <c r="J41" s="3"/>
@@ -2852,16 +2876,16 @@
         <f>IF($K41="","",L41-M41-R41-S41-T41-U41-V41-W41)</f>
       </c>
       <c r="Z41" s="3">
-        <f>IF($K41="","",(Y41-AB41)/J41*100)</f>
+        <f>IF($K41="","",(Y41-AF41)/J41*100)</f>
       </c>
       <c r="AA41" s="3">
         <f>IF($K41="","",M41-X41)</f>
       </c>
-      <c r="AC41" s="3">
-        <f>IF($K41="","",Y41-AB41)</f>
-      </c>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG41" s="3">
+        <f>IF($K41="","",Y41-AF41)</f>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="D42" s="2"/>
       <c r="J42" s="3"/>
@@ -2903,16 +2927,16 @@
         <f>IF($K42="","",L42-M42-R42-S42-T42-U42-V42-W42)</f>
       </c>
       <c r="Z42" s="3">
-        <f>IF($K42="","",(Y42-AB42)/J42*100)</f>
+        <f>IF($K42="","",(Y42-AF42)/J42*100)</f>
       </c>
       <c r="AA42" s="3">
         <f>IF($K42="","",M42-X42)</f>
       </c>
-      <c r="AC42" s="3">
-        <f>IF($K42="","",Y42-AB42)</f>
-      </c>
-    </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG42" s="3">
+        <f>IF($K42="","",Y42-AF42)</f>
+      </c>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="2"/>
       <c r="J43" s="3"/>
@@ -2954,16 +2978,16 @@
         <f>IF($K43="","",L43-M43-R43-S43-T43-U43-V43-W43)</f>
       </c>
       <c r="Z43" s="3">
-        <f>IF($K43="","",(Y43-AB43)/J43*100)</f>
+        <f>IF($K43="","",(Y43-AF43)/J43*100)</f>
       </c>
       <c r="AA43" s="3">
         <f>IF($K43="","",M43-X43)</f>
       </c>
-      <c r="AC43" s="3">
-        <f>IF($K43="","",Y43-AB43)</f>
-      </c>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG43" s="3">
+        <f>IF($K43="","",Y43-AF43)</f>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="D44" s="2"/>
       <c r="J44" s="3"/>
@@ -3005,16 +3029,16 @@
         <f>IF($K44="","",L44-M44-R44-S44-T44-U44-V44-W44)</f>
       </c>
       <c r="Z44" s="3">
-        <f>IF($K44="","",(Y44-AB44)/J44*100)</f>
+        <f>IF($K44="","",(Y44-AF44)/J44*100)</f>
       </c>
       <c r="AA44" s="3">
         <f>IF($K44="","",M44-X44)</f>
       </c>
-      <c r="AC44" s="3">
-        <f>IF($K44="","",Y44-AB44)</f>
-      </c>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG44" s="3">
+        <f>IF($K44="","",Y44-AF44)</f>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="D45" s="2"/>
       <c r="J45" s="3"/>
@@ -3056,16 +3080,16 @@
         <f>IF($K45="","",L45-M45-R45-S45-T45-U45-V45-W45)</f>
       </c>
       <c r="Z45" s="3">
-        <f>IF($K45="","",(Y45-AB45)/J45*100)</f>
+        <f>IF($K45="","",(Y45-AF45)/J45*100)</f>
       </c>
       <c r="AA45" s="3">
         <f>IF($K45="","",M45-X45)</f>
       </c>
-      <c r="AC45" s="3">
-        <f>IF($K45="","",Y45-AB45)</f>
-      </c>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG45" s="3">
+        <f>IF($K45="","",Y45-AF45)</f>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="D46" s="2"/>
       <c r="J46" s="3"/>
@@ -3107,16 +3131,16 @@
         <f>IF($K46="","",L46-M46-R46-S46-T46-U46-V46-W46)</f>
       </c>
       <c r="Z46" s="3">
-        <f>IF($K46="","",(Y46-AB46)/J46*100)</f>
+        <f>IF($K46="","",(Y46-AF46)/J46*100)</f>
       </c>
       <c r="AA46" s="3">
         <f>IF($K46="","",M46-X46)</f>
       </c>
-      <c r="AC46" s="3">
-        <f>IF($K46="","",Y46-AB46)</f>
-      </c>
-    </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG46" s="3">
+        <f>IF($K46="","",Y46-AF46)</f>
+      </c>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="D47" s="2"/>
       <c r="J47" s="3"/>
@@ -3158,16 +3182,16 @@
         <f>IF($K47="","",L47-M47-R47-S47-T47-U47-V47-W47)</f>
       </c>
       <c r="Z47" s="3">
-        <f>IF($K47="","",(Y47-AB47)/J47*100)</f>
+        <f>IF($K47="","",(Y47-AF47)/J47*100)</f>
       </c>
       <c r="AA47" s="3">
         <f>IF($K47="","",M47-X47)</f>
       </c>
-      <c r="AC47" s="3">
-        <f>IF($K47="","",Y47-AB47)</f>
-      </c>
-    </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG47" s="3">
+        <f>IF($K47="","",Y47-AF47)</f>
+      </c>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="D48" s="2"/>
       <c r="J48" s="3"/>
@@ -3209,16 +3233,16 @@
         <f>IF($K48="","",L48-M48-R48-S48-T48-U48-V48-W48)</f>
       </c>
       <c r="Z48" s="3">
-        <f>IF($K48="","",(Y48-AB48)/J48*100)</f>
+        <f>IF($K48="","",(Y48-AF48)/J48*100)</f>
       </c>
       <c r="AA48" s="3">
         <f>IF($K48="","",M48-X48)</f>
       </c>
-      <c r="AC48" s="3">
-        <f>IF($K48="","",Y48-AB48)</f>
-      </c>
-    </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG48" s="3">
+        <f>IF($K48="","",Y48-AF48)</f>
+      </c>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="D49" s="2"/>
       <c r="J49" s="3"/>
@@ -3260,16 +3284,16 @@
         <f>IF($K49="","",L49-M49-R49-S49-T49-U49-V49-W49)</f>
       </c>
       <c r="Z49" s="3">
-        <f>IF($K49="","",(Y49-AB49)/J49*100)</f>
+        <f>IF($K49="","",(Y49-AF49)/J49*100)</f>
       </c>
       <c r="AA49" s="3">
         <f>IF($K49="","",M49-X49)</f>
       </c>
-      <c r="AC49" s="3">
-        <f>IF($K49="","",Y49-AB49)</f>
-      </c>
-    </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG49" s="3">
+        <f>IF($K49="","",Y49-AF49)</f>
+      </c>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="D50" s="2"/>
       <c r="J50" s="3"/>
@@ -3311,16 +3335,16 @@
         <f>IF($K50="","",L50-M50-R50-S50-T50-U50-V50-W50)</f>
       </c>
       <c r="Z50" s="3">
-        <f>IF($K50="","",(Y50-AB50)/J50*100)</f>
+        <f>IF($K50="","",(Y50-AF50)/J50*100)</f>
       </c>
       <c r="AA50" s="3">
         <f>IF($K50="","",M50-X50)</f>
       </c>
-      <c r="AC50" s="3">
-        <f>IF($K50="","",Y50-AB50)</f>
-      </c>
-    </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG50" s="3">
+        <f>IF($K50="","",Y50-AF50)</f>
+      </c>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="D51" s="2"/>
       <c r="J51" s="3"/>
@@ -3362,16 +3386,16 @@
         <f>IF($K51="","",L51-M51-R51-S51-T51-U51-V51-W51)</f>
       </c>
       <c r="Z51" s="3">
-        <f>IF($K51="","",(Y51-AB51)/J51*100)</f>
+        <f>IF($K51="","",(Y51-AF51)/J51*100)</f>
       </c>
       <c r="AA51" s="3">
         <f>IF($K51="","",M51-X51)</f>
       </c>
-      <c r="AC51" s="3">
-        <f>IF($K51="","",Y51-AB51)</f>
-      </c>
-    </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG51" s="3">
+        <f>IF($K51="","",Y51-AF51)</f>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="D52" s="2"/>
       <c r="J52" s="3"/>
@@ -3413,16 +3437,16 @@
         <f>IF($K52="","",L52-M52-R52-S52-T52-U52-V52-W52)</f>
       </c>
       <c r="Z52" s="3">
-        <f>IF($K52="","",(Y52-AB52)/J52*100)</f>
+        <f>IF($K52="","",(Y52-AF52)/J52*100)</f>
       </c>
       <c r="AA52" s="3">
         <f>IF($K52="","",M52-X52)</f>
       </c>
-      <c r="AC52" s="3">
-        <f>IF($K52="","",Y52-AB52)</f>
-      </c>
-    </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG52" s="3">
+        <f>IF($K52="","",Y52-AF52)</f>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="D53" s="2"/>
       <c r="J53" s="3"/>
@@ -3464,16 +3488,16 @@
         <f>IF($K53="","",L53-M53-R53-S53-T53-U53-V53-W53)</f>
       </c>
       <c r="Z53" s="3">
-        <f>IF($K53="","",(Y53-AB53)/J53*100)</f>
+        <f>IF($K53="","",(Y53-AF53)/J53*100)</f>
       </c>
       <c r="AA53" s="3">
         <f>IF($K53="","",M53-X53)</f>
       </c>
-      <c r="AC53" s="3">
-        <f>IF($K53="","",Y53-AB53)</f>
-      </c>
-    </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG53" s="3">
+        <f>IF($K53="","",Y53-AF53)</f>
+      </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="D54" s="2"/>
       <c r="J54" s="3"/>
@@ -3515,16 +3539,16 @@
         <f>IF($K54="","",L54-M54-R54-S54-T54-U54-V54-W54)</f>
       </c>
       <c r="Z54" s="3">
-        <f>IF($K54="","",(Y54-AB54)/J54*100)</f>
+        <f>IF($K54="","",(Y54-AF54)/J54*100)</f>
       </c>
       <c r="AA54" s="3">
         <f>IF($K54="","",M54-X54)</f>
       </c>
-      <c r="AC54" s="3">
-        <f>IF($K54="","",Y54-AB54)</f>
-      </c>
-    </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG54" s="3">
+        <f>IF($K54="","",Y54-AF54)</f>
+      </c>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="D55" s="2"/>
       <c r="J55" s="3"/>
@@ -3566,16 +3590,16 @@
         <f>IF($K55="","",L55-M55-R55-S55-T55-U55-V55-W55)</f>
       </c>
       <c r="Z55" s="3">
-        <f>IF($K55="","",(Y55-AB55)/J55*100)</f>
+        <f>IF($K55="","",(Y55-AF55)/J55*100)</f>
       </c>
       <c r="AA55" s="3">
         <f>IF($K55="","",M55-X55)</f>
       </c>
-      <c r="AC55" s="3">
-        <f>IF($K55="","",Y55-AB55)</f>
-      </c>
-    </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG55" s="3">
+        <f>IF($K55="","",Y55-AF55)</f>
+      </c>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="D56" s="2"/>
       <c r="J56" s="3"/>
@@ -3617,16 +3641,16 @@
         <f>IF($K56="","",L56-M56-R56-S56-T56-U56-V56-W56)</f>
       </c>
       <c r="Z56" s="3">
-        <f>IF($K56="","",(Y56-AB56)/J56*100)</f>
+        <f>IF($K56="","",(Y56-AF56)/J56*100)</f>
       </c>
       <c r="AA56" s="3">
         <f>IF($K56="","",M56-X56)</f>
       </c>
-      <c r="AC56" s="3">
-        <f>IF($K56="","",Y56-AB56)</f>
-      </c>
-    </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG56" s="3">
+        <f>IF($K56="","",Y56-AF56)</f>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="D57" s="2"/>
       <c r="J57" s="3"/>
@@ -3668,16 +3692,16 @@
         <f>IF($K57="","",L57-M57-R57-S57-T57-U57-V57-W57)</f>
       </c>
       <c r="Z57" s="3">
-        <f>IF($K57="","",(Y57-AB57)/J57*100)</f>
+        <f>IF($K57="","",(Y57-AF57)/J57*100)</f>
       </c>
       <c r="AA57" s="3">
         <f>IF($K57="","",M57-X57)</f>
       </c>
-      <c r="AC57" s="3">
-        <f>IF($K57="","",Y57-AB57)</f>
-      </c>
-    </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG57" s="3">
+        <f>IF($K57="","",Y57-AF57)</f>
+      </c>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="D58" s="2"/>
       <c r="J58" s="3"/>
@@ -3719,16 +3743,16 @@
         <f>IF($K58="","",L58-M58-R58-S58-T58-U58-V58-W58)</f>
       </c>
       <c r="Z58" s="3">
-        <f>IF($K58="","",(Y58-AB58)/J58*100)</f>
+        <f>IF($K58="","",(Y58-AF58)/J58*100)</f>
       </c>
       <c r="AA58" s="3">
         <f>IF($K58="","",M58-X58)</f>
       </c>
-      <c r="AC58" s="3">
-        <f>IF($K58="","",Y58-AB58)</f>
-      </c>
-    </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG58" s="3">
+        <f>IF($K58="","",Y58-AF58)</f>
+      </c>
+    </row>
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="D59" s="2"/>
       <c r="J59" s="3"/>
@@ -3770,16 +3794,16 @@
         <f>IF($K59="","",L59-M59-R59-S59-T59-U59-V59-W59)</f>
       </c>
       <c r="Z59" s="3">
-        <f>IF($K59="","",(Y59-AB59)/J59*100)</f>
+        <f>IF($K59="","",(Y59-AF59)/J59*100)</f>
       </c>
       <c r="AA59" s="3">
         <f>IF($K59="","",M59-X59)</f>
       </c>
-      <c r="AC59" s="3">
-        <f>IF($K59="","",Y59-AB59)</f>
-      </c>
-    </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG59" s="3">
+        <f>IF($K59="","",Y59-AF59)</f>
+      </c>
+    </row>
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="D60" s="2"/>
       <c r="J60" s="3"/>
@@ -3821,16 +3845,16 @@
         <f>IF($K60="","",L60-M60-R60-S60-T60-U60-V60-W60)</f>
       </c>
       <c r="Z60" s="3">
-        <f>IF($K60="","",(Y60-AB60)/J60*100)</f>
+        <f>IF($K60="","",(Y60-AF60)/J60*100)</f>
       </c>
       <c r="AA60" s="3">
         <f>IF($K60="","",M60-X60)</f>
       </c>
-      <c r="AC60" s="3">
-        <f>IF($K60="","",Y60-AB60)</f>
-      </c>
-    </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG60" s="3">
+        <f>IF($K60="","",Y60-AF60)</f>
+      </c>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="D61" s="2"/>
       <c r="J61" s="3"/>
@@ -3872,16 +3896,16 @@
         <f>IF($K61="","",L61-M61-R61-S61-T61-U61-V61-W61)</f>
       </c>
       <c r="Z61" s="3">
-        <f>IF($K61="","",(Y61-AB61)/J61*100)</f>
+        <f>IF($K61="","",(Y61-AF61)/J61*100)</f>
       </c>
       <c r="AA61" s="3">
         <f>IF($K61="","",M61-X61)</f>
       </c>
-      <c r="AC61" s="3">
-        <f>IF($K61="","",Y61-AB61)</f>
-      </c>
-    </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG61" s="3">
+        <f>IF($K61="","",Y61-AF61)</f>
+      </c>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="D62" s="2"/>
       <c r="J62" s="3"/>
@@ -3923,16 +3947,16 @@
         <f>IF($K62="","",L62-M62-R62-S62-T62-U62-V62-W62)</f>
       </c>
       <c r="Z62" s="3">
-        <f>IF($K62="","",(Y62-AB62)/J62*100)</f>
+        <f>IF($K62="","",(Y62-AF62)/J62*100)</f>
       </c>
       <c r="AA62" s="3">
         <f>IF($K62="","",M62-X62)</f>
       </c>
-      <c r="AC62" s="3">
-        <f>IF($K62="","",Y62-AB62)</f>
-      </c>
-    </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG62" s="3">
+        <f>IF($K62="","",Y62-AF62)</f>
+      </c>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="D63" s="2"/>
       <c r="J63" s="3"/>
@@ -3974,16 +3998,16 @@
         <f>IF($K63="","",L63-M63-R63-S63-T63-U63-V63-W63)</f>
       </c>
       <c r="Z63" s="3">
-        <f>IF($K63="","",(Y63-AB63)/J63*100)</f>
+        <f>IF($K63="","",(Y63-AF63)/J63*100)</f>
       </c>
       <c r="AA63" s="3">
         <f>IF($K63="","",M63-X63)</f>
       </c>
-      <c r="AC63" s="3">
-        <f>IF($K63="","",Y63-AB63)</f>
-      </c>
-    </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG63" s="3">
+        <f>IF($K63="","",Y63-AF63)</f>
+      </c>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="D64" s="2"/>
       <c r="J64" s="3"/>
@@ -4025,16 +4049,16 @@
         <f>IF($K64="","",L64-M64-R64-S64-T64-U64-V64-W64)</f>
       </c>
       <c r="Z64" s="3">
-        <f>IF($K64="","",(Y64-AB64)/J64*100)</f>
+        <f>IF($K64="","",(Y64-AF64)/J64*100)</f>
       </c>
       <c r="AA64" s="3">
         <f>IF($K64="","",M64-X64)</f>
       </c>
-      <c r="AC64" s="3">
-        <f>IF($K64="","",Y64-AB64)</f>
-      </c>
-    </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG64" s="3">
+        <f>IF($K64="","",Y64-AF64)</f>
+      </c>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="D65" s="2"/>
       <c r="J65" s="3"/>
@@ -4076,16 +4100,16 @@
         <f>IF($K65="","",L65-M65-R65-S65-T65-U65-V65-W65)</f>
       </c>
       <c r="Z65" s="3">
-        <f>IF($K65="","",(Y65-AB65)/J65*100)</f>
+        <f>IF($K65="","",(Y65-AF65)/J65*100)</f>
       </c>
       <c r="AA65" s="3">
         <f>IF($K65="","",M65-X65)</f>
       </c>
-      <c r="AC65" s="3">
-        <f>IF($K65="","",Y65-AB65)</f>
-      </c>
-    </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG65" s="3">
+        <f>IF($K65="","",Y65-AF65)</f>
+      </c>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="D66" s="2"/>
       <c r="J66" s="3"/>
@@ -4127,16 +4151,16 @@
         <f>IF($K66="","",L66-M66-R66-S66-T66-U66-V66-W66)</f>
       </c>
       <c r="Z66" s="3">
-        <f>IF($K66="","",(Y66-AB66)/J66*100)</f>
+        <f>IF($K66="","",(Y66-AF66)/J66*100)</f>
       </c>
       <c r="AA66" s="3">
         <f>IF($K66="","",M66-X66)</f>
       </c>
-      <c r="AC66" s="3">
-        <f>IF($K66="","",Y66-AB66)</f>
-      </c>
-    </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG66" s="3">
+        <f>IF($K66="","",Y66-AF66)</f>
+      </c>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="D67" s="2"/>
       <c r="J67" s="3"/>
@@ -4178,16 +4202,16 @@
         <f>IF($K67="","",L67-M67-R67-S67-T67-U67-V67-W67)</f>
       </c>
       <c r="Z67" s="3">
-        <f>IF($K67="","",(Y67-AB67)/J67*100)</f>
+        <f>IF($K67="","",(Y67-AF67)/J67*100)</f>
       </c>
       <c r="AA67" s="3">
         <f>IF($K67="","",M67-X67)</f>
       </c>
-      <c r="AC67" s="3">
-        <f>IF($K67="","",Y67-AB67)</f>
-      </c>
-    </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG67" s="3">
+        <f>IF($K67="","",Y67-AF67)</f>
+      </c>
+    </row>
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="D68" s="2"/>
       <c r="J68" s="3"/>
@@ -4229,16 +4253,16 @@
         <f>IF($K68="","",L68-M68-R68-S68-T68-U68-V68-W68)</f>
       </c>
       <c r="Z68" s="3">
-        <f>IF($K68="","",(Y68-AB68)/J68*100)</f>
+        <f>IF($K68="","",(Y68-AF68)/J68*100)</f>
       </c>
       <c r="AA68" s="3">
         <f>IF($K68="","",M68-X68)</f>
       </c>
-      <c r="AC68" s="3">
-        <f>IF($K68="","",Y68-AB68)</f>
-      </c>
-    </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG68" s="3">
+        <f>IF($K68="","",Y68-AF68)</f>
+      </c>
+    </row>
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="D69" s="2"/>
       <c r="J69" s="3"/>
@@ -4280,16 +4304,16 @@
         <f>IF($K69="","",L69-M69-R69-S69-T69-U69-V69-W69)</f>
       </c>
       <c r="Z69" s="3">
-        <f>IF($K69="","",(Y69-AB69)/J69*100)</f>
+        <f>IF($K69="","",(Y69-AF69)/J69*100)</f>
       </c>
       <c r="AA69" s="3">
         <f>IF($K69="","",M69-X69)</f>
       </c>
-      <c r="AC69" s="3">
-        <f>IF($K69="","",Y69-AB69)</f>
-      </c>
-    </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG69" s="3">
+        <f>IF($K69="","",Y69-AF69)</f>
+      </c>
+    </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="D70" s="2"/>
       <c r="J70" s="3"/>
@@ -4331,16 +4355,16 @@
         <f>IF($K70="","",L70-M70-R70-S70-T70-U70-V70-W70)</f>
       </c>
       <c r="Z70" s="3">
-        <f>IF($K70="","",(Y70-AB70)/J70*100)</f>
+        <f>IF($K70="","",(Y70-AF70)/J70*100)</f>
       </c>
       <c r="AA70" s="3">
         <f>IF($K70="","",M70-X70)</f>
       </c>
-      <c r="AC70" s="3">
-        <f>IF($K70="","",Y70-AB70)</f>
-      </c>
-    </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG70" s="3">
+        <f>IF($K70="","",Y70-AF70)</f>
+      </c>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="D71" s="2"/>
       <c r="J71" s="3"/>
@@ -4382,16 +4406,16 @@
         <f>IF($K71="","",L71-M71-R71-S71-T71-U71-V71-W71)</f>
       </c>
       <c r="Z71" s="3">
-        <f>IF($K71="","",(Y71-AB71)/J71*100)</f>
+        <f>IF($K71="","",(Y71-AF71)/J71*100)</f>
       </c>
       <c r="AA71" s="3">
         <f>IF($K71="","",M71-X71)</f>
       </c>
-      <c r="AC71" s="3">
-        <f>IF($K71="","",Y71-AB71)</f>
-      </c>
-    </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG71" s="3">
+        <f>IF($K71="","",Y71-AF71)</f>
+      </c>
+    </row>
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="D72" s="2"/>
       <c r="J72" s="3"/>
@@ -4433,16 +4457,16 @@
         <f>IF($K72="","",L72-M72-R72-S72-T72-U72-V72-W72)</f>
       </c>
       <c r="Z72" s="3">
-        <f>IF($K72="","",(Y72-AB72)/J72*100)</f>
+        <f>IF($K72="","",(Y72-AF72)/J72*100)</f>
       </c>
       <c r="AA72" s="3">
         <f>IF($K72="","",M72-X72)</f>
       </c>
-      <c r="AC72" s="3">
-        <f>IF($K72="","",Y72-AB72)</f>
-      </c>
-    </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG72" s="3">
+        <f>IF($K72="","",Y72-AF72)</f>
+      </c>
+    </row>
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="D73" s="2"/>
       <c r="J73" s="3"/>
@@ -4484,16 +4508,16 @@
         <f>IF($K73="","",L73-M73-R73-S73-T73-U73-V73-W73)</f>
       </c>
       <c r="Z73" s="3">
-        <f>IF($K73="","",(Y73-AB73)/J73*100)</f>
+        <f>IF($K73="","",(Y73-AF73)/J73*100)</f>
       </c>
       <c r="AA73" s="3">
         <f>IF($K73="","",M73-X73)</f>
       </c>
-      <c r="AC73" s="3">
-        <f>IF($K73="","",Y73-AB73)</f>
-      </c>
-    </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG73" s="3">
+        <f>IF($K73="","",Y73-AF73)</f>
+      </c>
+    </row>
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="D74" s="2"/>
       <c r="J74" s="3"/>
@@ -4535,16 +4559,16 @@
         <f>IF($K74="","",L74-M74-R74-S74-T74-U74-V74-W74)</f>
       </c>
       <c r="Z74" s="3">
-        <f>IF($K74="","",(Y74-AB74)/J74*100)</f>
+        <f>IF($K74="","",(Y74-AF74)/J74*100)</f>
       </c>
       <c r="AA74" s="3">
         <f>IF($K74="","",M74-X74)</f>
       </c>
-      <c r="AC74" s="3">
-        <f>IF($K74="","",Y74-AB74)</f>
-      </c>
-    </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG74" s="3">
+        <f>IF($K74="","",Y74-AF74)</f>
+      </c>
+    </row>
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="D75" s="2"/>
       <c r="J75" s="3"/>
@@ -4586,16 +4610,16 @@
         <f>IF($K75="","",L75-M75-R75-S75-T75-U75-V75-W75)</f>
       </c>
       <c r="Z75" s="3">
-        <f>IF($K75="","",(Y75-AB75)/J75*100)</f>
+        <f>IF($K75="","",(Y75-AF75)/J75*100)</f>
       </c>
       <c r="AA75" s="3">
         <f>IF($K75="","",M75-X75)</f>
       </c>
-      <c r="AC75" s="3">
-        <f>IF($K75="","",Y75-AB75)</f>
-      </c>
-    </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG75" s="3">
+        <f>IF($K75="","",Y75-AF75)</f>
+      </c>
+    </row>
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="D76" s="2"/>
       <c r="J76" s="3"/>
@@ -4637,16 +4661,16 @@
         <f>IF($K76="","",L76-M76-R76-S76-T76-U76-V76-W76)</f>
       </c>
       <c r="Z76" s="3">
-        <f>IF($K76="","",(Y76-AB76)/J76*100)</f>
+        <f>IF($K76="","",(Y76-AF76)/J76*100)</f>
       </c>
       <c r="AA76" s="3">
         <f>IF($K76="","",M76-X76)</f>
       </c>
-      <c r="AC76" s="3">
-        <f>IF($K76="","",Y76-AB76)</f>
-      </c>
-    </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG76" s="3">
+        <f>IF($K76="","",Y76-AF76)</f>
+      </c>
+    </row>
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="2"/>
       <c r="J77" s="3"/>
@@ -4688,16 +4712,16 @@
         <f>IF($K77="","",L77-M77-R77-S77-T77-U77-V77-W77)</f>
       </c>
       <c r="Z77" s="3">
-        <f>IF($K77="","",(Y77-AB77)/J77*100)</f>
+        <f>IF($K77="","",(Y77-AF77)/J77*100)</f>
       </c>
       <c r="AA77" s="3">
         <f>IF($K77="","",M77-X77)</f>
       </c>
-      <c r="AC77" s="3">
-        <f>IF($K77="","",Y77-AB77)</f>
-      </c>
-    </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG77" s="3">
+        <f>IF($K77="","",Y77-AF77)</f>
+      </c>
+    </row>
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="D78" s="2"/>
       <c r="J78" s="3"/>
@@ -4739,16 +4763,16 @@
         <f>IF($K78="","",L78-M78-R78-S78-T78-U78-V78-W78)</f>
       </c>
       <c r="Z78" s="3">
-        <f>IF($K78="","",(Y78-AB78)/J78*100)</f>
+        <f>IF($K78="","",(Y78-AF78)/J78*100)</f>
       </c>
       <c r="AA78" s="3">
         <f>IF($K78="","",M78-X78)</f>
       </c>
-      <c r="AC78" s="3">
-        <f>IF($K78="","",Y78-AB78)</f>
-      </c>
-    </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG78" s="3">
+        <f>IF($K78="","",Y78-AF78)</f>
+      </c>
+    </row>
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="D79" s="2"/>
       <c r="J79" s="3"/>
@@ -4790,16 +4814,16 @@
         <f>IF($K79="","",L79-M79-R79-S79-T79-U79-V79-W79)</f>
       </c>
       <c r="Z79" s="3">
-        <f>IF($K79="","",(Y79-AB79)/J79*100)</f>
+        <f>IF($K79="","",(Y79-AF79)/J79*100)</f>
       </c>
       <c r="AA79" s="3">
         <f>IF($K79="","",M79-X79)</f>
       </c>
-      <c r="AC79" s="3">
-        <f>IF($K79="","",Y79-AB79)</f>
-      </c>
-    </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG79" s="3">
+        <f>IF($K79="","",Y79-AF79)</f>
+      </c>
+    </row>
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="D80" s="2"/>
       <c r="J80" s="3"/>
@@ -4841,16 +4865,16 @@
         <f>IF($K80="","",L80-M80-R80-S80-T80-U80-V80-W80)</f>
       </c>
       <c r="Z80" s="3">
-        <f>IF($K80="","",(Y80-AB80)/J80*100)</f>
+        <f>IF($K80="","",(Y80-AF80)/J80*100)</f>
       </c>
       <c r="AA80" s="3">
         <f>IF($K80="","",M80-X80)</f>
       </c>
-      <c r="AC80" s="3">
-        <f>IF($K80="","",Y80-AB80)</f>
-      </c>
-    </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG80" s="3">
+        <f>IF($K80="","",Y80-AF80)</f>
+      </c>
+    </row>
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="D81" s="2"/>
       <c r="J81" s="3"/>
@@ -4892,16 +4916,16 @@
         <f>IF($K81="","",L81-M81-R81-S81-T81-U81-V81-W81)</f>
       </c>
       <c r="Z81" s="3">
-        <f>IF($K81="","",(Y81-AB81)/J81*100)</f>
+        <f>IF($K81="","",(Y81-AF81)/J81*100)</f>
       </c>
       <c r="AA81" s="3">
         <f>IF($K81="","",M81-X81)</f>
       </c>
-      <c r="AC81" s="3">
-        <f>IF($K81="","",Y81-AB81)</f>
-      </c>
-    </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG81" s="3">
+        <f>IF($K81="","",Y81-AF81)</f>
+      </c>
+    </row>
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="D82" s="2"/>
       <c r="J82" s="3"/>
@@ -4943,16 +4967,16 @@
         <f>IF($K82="","",L82-M82-R82-S82-T82-U82-V82-W82)</f>
       </c>
       <c r="Z82" s="3">
-        <f>IF($K82="","",(Y82-AB82)/J82*100)</f>
+        <f>IF($K82="","",(Y82-AF82)/J82*100)</f>
       </c>
       <c r="AA82" s="3">
         <f>IF($K82="","",M82-X82)</f>
       </c>
-      <c r="AC82" s="3">
-        <f>IF($K82="","",Y82-AB82)</f>
-      </c>
-    </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG82" s="3">
+        <f>IF($K82="","",Y82-AF82)</f>
+      </c>
+    </row>
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="D83" s="2"/>
       <c r="J83" s="3"/>
@@ -4994,16 +5018,16 @@
         <f>IF($K83="","",L83-M83-R83-S83-T83-U83-V83-W83)</f>
       </c>
       <c r="Z83" s="3">
-        <f>IF($K83="","",(Y83-AB83)/J83*100)</f>
+        <f>IF($K83="","",(Y83-AF83)/J83*100)</f>
       </c>
       <c r="AA83" s="3">
         <f>IF($K83="","",M83-X83)</f>
       </c>
-      <c r="AC83" s="3">
-        <f>IF($K83="","",Y83-AB83)</f>
-      </c>
-    </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG83" s="3">
+        <f>IF($K83="","",Y83-AF83)</f>
+      </c>
+    </row>
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="D84" s="2"/>
       <c r="J84" s="3"/>
@@ -5045,16 +5069,16 @@
         <f>IF($K84="","",L84-M84-R84-S84-T84-U84-V84-W84)</f>
       </c>
       <c r="Z84" s="3">
-        <f>IF($K84="","",(Y84-AB84)/J84*100)</f>
+        <f>IF($K84="","",(Y84-AF84)/J84*100)</f>
       </c>
       <c r="AA84" s="3">
         <f>IF($K84="","",M84-X84)</f>
       </c>
-      <c r="AC84" s="3">
-        <f>IF($K84="","",Y84-AB84)</f>
-      </c>
-    </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG84" s="3">
+        <f>IF($K84="","",Y84-AF84)</f>
+      </c>
+    </row>
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="D85" s="2"/>
       <c r="J85" s="3"/>
@@ -5096,16 +5120,16 @@
         <f>IF($K85="","",L85-M85-R85-S85-T85-U85-V85-W85)</f>
       </c>
       <c r="Z85" s="3">
-        <f>IF($K85="","",(Y85-AB85)/J85*100)</f>
+        <f>IF($K85="","",(Y85-AF85)/J85*100)</f>
       </c>
       <c r="AA85" s="3">
         <f>IF($K85="","",M85-X85)</f>
       </c>
-      <c r="AC85" s="3">
-        <f>IF($K85="","",Y85-AB85)</f>
-      </c>
-    </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG85" s="3">
+        <f>IF($K85="","",Y85-AF85)</f>
+      </c>
+    </row>
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="D86" s="2"/>
       <c r="J86" s="3"/>
@@ -5147,16 +5171,16 @@
         <f>IF($K86="","",L86-M86-R86-S86-T86-U86-V86-W86)</f>
       </c>
       <c r="Z86" s="3">
-        <f>IF($K86="","",(Y86-AB86)/J86*100)</f>
+        <f>IF($K86="","",(Y86-AF86)/J86*100)</f>
       </c>
       <c r="AA86" s="3">
         <f>IF($K86="","",M86-X86)</f>
       </c>
-      <c r="AC86" s="3">
-        <f>IF($K86="","",Y86-AB86)</f>
-      </c>
-    </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG86" s="3">
+        <f>IF($K86="","",Y86-AF86)</f>
+      </c>
+    </row>
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="D87" s="2"/>
       <c r="J87" s="3"/>
@@ -5198,16 +5222,16 @@
         <f>IF($K87="","",L87-M87-R87-S87-T87-U87-V87-W87)</f>
       </c>
       <c r="Z87" s="3">
-        <f>IF($K87="","",(Y87-AB87)/J87*100)</f>
+        <f>IF($K87="","",(Y87-AF87)/J87*100)</f>
       </c>
       <c r="AA87" s="3">
         <f>IF($K87="","",M87-X87)</f>
       </c>
-      <c r="AC87" s="3">
-        <f>IF($K87="","",Y87-AB87)</f>
-      </c>
-    </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG87" s="3">
+        <f>IF($K87="","",Y87-AF87)</f>
+      </c>
+    </row>
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="D88" s="2"/>
       <c r="J88" s="3"/>
@@ -5249,16 +5273,16 @@
         <f>IF($K88="","",L88-M88-R88-S88-T88-U88-V88-W88)</f>
       </c>
       <c r="Z88" s="3">
-        <f>IF($K88="","",(Y88-AB88)/J88*100)</f>
+        <f>IF($K88="","",(Y88-AF88)/J88*100)</f>
       </c>
       <c r="AA88" s="3">
         <f>IF($K88="","",M88-X88)</f>
       </c>
-      <c r="AC88" s="3">
-        <f>IF($K88="","",Y88-AB88)</f>
-      </c>
-    </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG88" s="3">
+        <f>IF($K88="","",Y88-AF88)</f>
+      </c>
+    </row>
+    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="D89" s="2"/>
       <c r="J89" s="3"/>
@@ -5300,16 +5324,16 @@
         <f>IF($K89="","",L89-M89-R89-S89-T89-U89-V89-W89)</f>
       </c>
       <c r="Z89" s="3">
-        <f>IF($K89="","",(Y89-AB89)/J89*100)</f>
+        <f>IF($K89="","",(Y89-AF89)/J89*100)</f>
       </c>
       <c r="AA89" s="3">
         <f>IF($K89="","",M89-X89)</f>
       </c>
-      <c r="AC89" s="3">
-        <f>IF($K89="","",Y89-AB89)</f>
-      </c>
-    </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG89" s="3">
+        <f>IF($K89="","",Y89-AF89)</f>
+      </c>
+    </row>
+    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="D90" s="2"/>
       <c r="J90" s="3"/>
@@ -5351,16 +5375,16 @@
         <f>IF($K90="","",L90-M90-R90-S90-T90-U90-V90-W90)</f>
       </c>
       <c r="Z90" s="3">
-        <f>IF($K90="","",(Y90-AB90)/J90*100)</f>
+        <f>IF($K90="","",(Y90-AF90)/J90*100)</f>
       </c>
       <c r="AA90" s="3">
         <f>IF($K90="","",M90-X90)</f>
       </c>
-      <c r="AC90" s="3">
-        <f>IF($K90="","",Y90-AB90)</f>
-      </c>
-    </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG90" s="3">
+        <f>IF($K90="","",Y90-AF90)</f>
+      </c>
+    </row>
+    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="D91" s="2"/>
       <c r="J91" s="3"/>
@@ -5402,16 +5426,16 @@
         <f>IF($K91="","",L91-M91-R91-S91-T91-U91-V91-W91)</f>
       </c>
       <c r="Z91" s="3">
-        <f>IF($K91="","",(Y91-AB91)/J91*100)</f>
+        <f>IF($K91="","",(Y91-AF91)/J91*100)</f>
       </c>
       <c r="AA91" s="3">
         <f>IF($K91="","",M91-X91)</f>
       </c>
-      <c r="AC91" s="3">
-        <f>IF($K91="","",Y91-AB91)</f>
-      </c>
-    </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG91" s="3">
+        <f>IF($K91="","",Y91-AF91)</f>
+      </c>
+    </row>
+    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="D92" s="2"/>
       <c r="J92" s="3"/>
@@ -5453,16 +5477,16 @@
         <f>IF($K92="","",L92-M92-R92-S92-T92-U92-V92-W92)</f>
       </c>
       <c r="Z92" s="3">
-        <f>IF($K92="","",(Y92-AB92)/J92*100)</f>
+        <f>IF($K92="","",(Y92-AF92)/J92*100)</f>
       </c>
       <c r="AA92" s="3">
         <f>IF($K92="","",M92-X92)</f>
       </c>
-      <c r="AC92" s="3">
-        <f>IF($K92="","",Y92-AB92)</f>
-      </c>
-    </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG92" s="3">
+        <f>IF($K92="","",Y92-AF92)</f>
+      </c>
+    </row>
+    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="D93" s="2"/>
       <c r="J93" s="3"/>
@@ -5504,16 +5528,16 @@
         <f>IF($K93="","",L93-M93-R93-S93-T93-U93-V93-W93)</f>
       </c>
       <c r="Z93" s="3">
-        <f>IF($K93="","",(Y93-AB93)/J93*100)</f>
+        <f>IF($K93="","",(Y93-AF93)/J93*100)</f>
       </c>
       <c r="AA93" s="3">
         <f>IF($K93="","",M93-X93)</f>
       </c>
-      <c r="AC93" s="3">
-        <f>IF($K93="","",Y93-AB93)</f>
-      </c>
-    </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG93" s="3">
+        <f>IF($K93="","",Y93-AF93)</f>
+      </c>
+    </row>
+    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="D94" s="2"/>
       <c r="J94" s="3"/>
@@ -5555,16 +5579,16 @@
         <f>IF($K94="","",L94-M94-R94-S94-T94-U94-V94-W94)</f>
       </c>
       <c r="Z94" s="3">
-        <f>IF($K94="","",(Y94-AB94)/J94*100)</f>
+        <f>IF($K94="","",(Y94-AF94)/J94*100)</f>
       </c>
       <c r="AA94" s="3">
         <f>IF($K94="","",M94-X94)</f>
       </c>
-      <c r="AC94" s="3">
-        <f>IF($K94="","",Y94-AB94)</f>
-      </c>
-    </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG94" s="3">
+        <f>IF($K94="","",Y94-AF94)</f>
+      </c>
+    </row>
+    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="D95" s="2"/>
       <c r="J95" s="3"/>
@@ -5606,16 +5630,16 @@
         <f>IF($K95="","",L95-M95-R95-S95-T95-U95-V95-W95)</f>
       </c>
       <c r="Z95" s="3">
-        <f>IF($K95="","",(Y95-AB95)/J95*100)</f>
+        <f>IF($K95="","",(Y95-AF95)/J95*100)</f>
       </c>
       <c r="AA95" s="3">
         <f>IF($K95="","",M95-X95)</f>
       </c>
-      <c r="AC95" s="3">
-        <f>IF($K95="","",Y95-AB95)</f>
-      </c>
-    </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG95" s="3">
+        <f>IF($K95="","",Y95-AF95)</f>
+      </c>
+    </row>
+    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="2"/>
       <c r="J96" s="3"/>
@@ -5657,16 +5681,16 @@
         <f>IF($K96="","",L96-M96-R96-S96-T96-U96-V96-W96)</f>
       </c>
       <c r="Z96" s="3">
-        <f>IF($K96="","",(Y96-AB96)/J96*100)</f>
+        <f>IF($K96="","",(Y96-AF96)/J96*100)</f>
       </c>
       <c r="AA96" s="3">
         <f>IF($K96="","",M96-X96)</f>
       </c>
-      <c r="AC96" s="3">
-        <f>IF($K96="","",Y96-AB96)</f>
-      </c>
-    </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG96" s="3">
+        <f>IF($K96="","",Y96-AF96)</f>
+      </c>
+    </row>
+    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="2"/>
       <c r="J97" s="3"/>
@@ -5708,16 +5732,16 @@
         <f>IF($K97="","",L97-M97-R97-S97-T97-U97-V97-W97)</f>
       </c>
       <c r="Z97" s="3">
-        <f>IF($K97="","",(Y97-AB97)/J97*100)</f>
+        <f>IF($K97="","",(Y97-AF97)/J97*100)</f>
       </c>
       <c r="AA97" s="3">
         <f>IF($K97="","",M97-X97)</f>
       </c>
-      <c r="AC97" s="3">
-        <f>IF($K97="","",Y97-AB97)</f>
-      </c>
-    </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG97" s="3">
+        <f>IF($K97="","",Y97-AF97)</f>
+      </c>
+    </row>
+    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="D98" s="2"/>
       <c r="J98" s="3"/>
@@ -5759,16 +5783,16 @@
         <f>IF($K98="","",L98-M98-R98-S98-T98-U98-V98-W98)</f>
       </c>
       <c r="Z98" s="3">
-        <f>IF($K98="","",(Y98-AB98)/J98*100)</f>
+        <f>IF($K98="","",(Y98-AF98)/J98*100)</f>
       </c>
       <c r="AA98" s="3">
         <f>IF($K98="","",M98-X98)</f>
       </c>
-      <c r="AC98" s="3">
-        <f>IF($K98="","",Y98-AB98)</f>
-      </c>
-    </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG98" s="3">
+        <f>IF($K98="","",Y98-AF98)</f>
+      </c>
+    </row>
+    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="D99" s="2"/>
       <c r="J99" s="3"/>
@@ -5810,16 +5834,16 @@
         <f>IF($K99="","",L99-M99-R99-S99-T99-U99-V99-W99)</f>
       </c>
       <c r="Z99" s="3">
-        <f>IF($K99="","",(Y99-AB99)/J99*100)</f>
+        <f>IF($K99="","",(Y99-AF99)/J99*100)</f>
       </c>
       <c r="AA99" s="3">
         <f>IF($K99="","",M99-X99)</f>
       </c>
-      <c r="AC99" s="3">
-        <f>IF($K99="","",Y99-AB99)</f>
-      </c>
-    </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG99" s="3">
+        <f>IF($K99="","",Y99-AF99)</f>
+      </c>
+    </row>
+    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="D100" s="2"/>
       <c r="J100" s="3"/>
@@ -5861,16 +5885,16 @@
         <f>IF($K100="","",L100-M100-R100-S100-T100-U100-V100-W100)</f>
       </c>
       <c r="Z100" s="3">
-        <f>IF($K100="","",(Y100-AB100)/J100*100)</f>
+        <f>IF($K100="","",(Y100-AF100)/J100*100)</f>
       </c>
       <c r="AA100" s="3">
         <f>IF($K100="","",M100-X100)</f>
       </c>
-      <c r="AC100" s="3">
-        <f>IF($K100="","",Y100-AB100)</f>
-      </c>
-    </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG100" s="3">
+        <f>IF($K100="","",Y100-AF100)</f>
+      </c>
+    </row>
+    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="D101" s="2"/>
       <c r="J101" s="3"/>
@@ -5912,16 +5936,16 @@
         <f>IF($K101="","",L101-M101-R101-S101-T101-U101-V101-W101)</f>
       </c>
       <c r="Z101" s="3">
-        <f>IF($K101="","",(Y101-AB101)/J101*100)</f>
+        <f>IF($K101="","",(Y101-AF101)/J101*100)</f>
       </c>
       <c r="AA101" s="3">
         <f>IF($K101="","",M101-X101)</f>
       </c>
-      <c r="AC101" s="3">
-        <f>IF($K101="","",Y101-AB101)</f>
-      </c>
-    </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG101" s="3">
+        <f>IF($K101="","",Y101-AF101)</f>
+      </c>
+    </row>
+    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="D102" s="2"/>
       <c r="J102" s="3"/>
@@ -5963,16 +5987,16 @@
         <f>IF($K102="","",L102-M102-R102-S102-T102-U102-V102-W102)</f>
       </c>
       <c r="Z102" s="3">
-        <f>IF($K102="","",(Y102-AB102)/J102*100)</f>
+        <f>IF($K102="","",(Y102-AF102)/J102*100)</f>
       </c>
       <c r="AA102" s="3">
         <f>IF($K102="","",M102-X102)</f>
       </c>
-      <c r="AC102" s="3">
-        <f>IF($K102="","",Y102-AB102)</f>
-      </c>
-    </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG102" s="3">
+        <f>IF($K102="","",Y102-AF102)</f>
+      </c>
+    </row>
+    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="D103" s="2"/>
       <c r="J103" s="3"/>
@@ -6014,16 +6038,16 @@
         <f>IF($K103="","",L103-M103-R103-S103-T103-U103-V103-W103)</f>
       </c>
       <c r="Z103" s="3">
-        <f>IF($K103="","",(Y103-AB103)/J103*100)</f>
+        <f>IF($K103="","",(Y103-AF103)/J103*100)</f>
       </c>
       <c r="AA103" s="3">
         <f>IF($K103="","",M103-X103)</f>
       </c>
-      <c r="AC103" s="3">
-        <f>IF($K103="","",Y103-AB103)</f>
-      </c>
-    </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG103" s="3">
+        <f>IF($K103="","",Y103-AF103)</f>
+      </c>
+    </row>
+    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="D104" s="2"/>
       <c r="J104" s="3"/>
@@ -6065,16 +6089,16 @@
         <f>IF($K104="","",L104-M104-R104-S104-T104-U104-V104-W104)</f>
       </c>
       <c r="Z104" s="3">
-        <f>IF($K104="","",(Y104-AB104)/J104*100)</f>
+        <f>IF($K104="","",(Y104-AF104)/J104*100)</f>
       </c>
       <c r="AA104" s="3">
         <f>IF($K104="","",M104-X104)</f>
       </c>
-      <c r="AC104" s="3">
-        <f>IF($K104="","",Y104-AB104)</f>
-      </c>
-    </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG104" s="3">
+        <f>IF($K104="","",Y104-AF104)</f>
+      </c>
+    </row>
+    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="D105" s="2"/>
       <c r="J105" s="3"/>
@@ -6116,16 +6140,16 @@
         <f>IF($K105="","",L105-M105-R105-S105-T105-U105-V105-W105)</f>
       </c>
       <c r="Z105" s="3">
-        <f>IF($K105="","",(Y105-AB105)/J105*100)</f>
+        <f>IF($K105="","",(Y105-AF105)/J105*100)</f>
       </c>
       <c r="AA105" s="3">
         <f>IF($K105="","",M105-X105)</f>
       </c>
-      <c r="AC105" s="3">
-        <f>IF($K105="","",Y105-AB105)</f>
-      </c>
-    </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG105" s="3">
+        <f>IF($K105="","",Y105-AF105)</f>
+      </c>
+    </row>
+    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="D106" s="2"/>
       <c r="J106" s="3"/>
@@ -6167,16 +6191,16 @@
         <f>IF($K106="","",L106-M106-R106-S106-T106-U106-V106-W106)</f>
       </c>
       <c r="Z106" s="3">
-        <f>IF($K106="","",(Y106-AB106)/J106*100)</f>
+        <f>IF($K106="","",(Y106-AF106)/J106*100)</f>
       </c>
       <c r="AA106" s="3">
         <f>IF($K106="","",M106-X106)</f>
       </c>
-      <c r="AC106" s="3">
-        <f>IF($K106="","",Y106-AB106)</f>
-      </c>
-    </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG106" s="3">
+        <f>IF($K106="","",Y106-AF106)</f>
+      </c>
+    </row>
+    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="D107" s="2"/>
       <c r="J107" s="3"/>
@@ -6218,16 +6242,16 @@
         <f>IF($K107="","",L107-M107-R107-S107-T107-U107-V107-W107)</f>
       </c>
       <c r="Z107" s="3">
-        <f>IF($K107="","",(Y107-AB107)/J107*100)</f>
+        <f>IF($K107="","",(Y107-AF107)/J107*100)</f>
       </c>
       <c r="AA107" s="3">
         <f>IF($K107="","",M107-X107)</f>
       </c>
-      <c r="AC107" s="3">
-        <f>IF($K107="","",Y107-AB107)</f>
-      </c>
-    </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG107" s="3">
+        <f>IF($K107="","",Y107-AF107)</f>
+      </c>
+    </row>
+    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="D108" s="2"/>
       <c r="J108" s="3"/>
@@ -6269,16 +6293,16 @@
         <f>IF($K108="","",L108-M108-R108-S108-T108-U108-V108-W108)</f>
       </c>
       <c r="Z108" s="3">
-        <f>IF($K108="","",(Y108-AB108)/J108*100)</f>
+        <f>IF($K108="","",(Y108-AF108)/J108*100)</f>
       </c>
       <c r="AA108" s="3">
         <f>IF($K108="","",M108-X108)</f>
       </c>
-      <c r="AC108" s="3">
-        <f>IF($K108="","",Y108-AB108)</f>
-      </c>
-    </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG108" s="3">
+        <f>IF($K108="","",Y108-AF108)</f>
+      </c>
+    </row>
+    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="D109" s="2"/>
       <c r="J109" s="3"/>
@@ -6320,16 +6344,16 @@
         <f>IF($K109="","",L109-M109-R109-S109-T109-U109-V109-W109)</f>
       </c>
       <c r="Z109" s="3">
-        <f>IF($K109="","",(Y109-AB109)/J109*100)</f>
+        <f>IF($K109="","",(Y109-AF109)/J109*100)</f>
       </c>
       <c r="AA109" s="3">
         <f>IF($K109="","",M109-X109)</f>
       </c>
-      <c r="AC109" s="3">
-        <f>IF($K109="","",Y109-AB109)</f>
-      </c>
-    </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG109" s="3">
+        <f>IF($K109="","",Y109-AF109)</f>
+      </c>
+    </row>
+    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="D110" s="2"/>
       <c r="J110" s="3"/>
@@ -6371,16 +6395,16 @@
         <f>IF($K110="","",L110-M110-R110-S110-T110-U110-V110-W110)</f>
       </c>
       <c r="Z110" s="3">
-        <f>IF($K110="","",(Y110-AB110)/J110*100)</f>
+        <f>IF($K110="","",(Y110-AF110)/J110*100)</f>
       </c>
       <c r="AA110" s="3">
         <f>IF($K110="","",M110-X110)</f>
       </c>
-      <c r="AC110" s="3">
-        <f>IF($K110="","",Y110-AB110)</f>
-      </c>
-    </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG110" s="3">
+        <f>IF($K110="","",Y110-AF110)</f>
+      </c>
+    </row>
+    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="D111" s="2"/>
       <c r="J111" s="3"/>
@@ -6422,16 +6446,16 @@
         <f>IF($K111="","",L111-M111-R111-S111-T111-U111-V111-W111)</f>
       </c>
       <c r="Z111" s="3">
-        <f>IF($K111="","",(Y111-AB111)/J111*100)</f>
+        <f>IF($K111="","",(Y111-AF111)/J111*100)</f>
       </c>
       <c r="AA111" s="3">
         <f>IF($K111="","",M111-X111)</f>
       </c>
-      <c r="AC111" s="3">
-        <f>IF($K111="","",Y111-AB111)</f>
-      </c>
-    </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG111" s="3">
+        <f>IF($K111="","",Y111-AF111)</f>
+      </c>
+    </row>
+    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="D112" s="2"/>
       <c r="J112" s="3"/>
@@ -6473,16 +6497,16 @@
         <f>IF($K112="","",L112-M112-R112-S112-T112-U112-V112-W112)</f>
       </c>
       <c r="Z112" s="3">
-        <f>IF($K112="","",(Y112-AB112)/J112*100)</f>
+        <f>IF($K112="","",(Y112-AF112)/J112*100)</f>
       </c>
       <c r="AA112" s="3">
         <f>IF($K112="","",M112-X112)</f>
       </c>
-      <c r="AC112" s="3">
-        <f>IF($K112="","",Y112-AB112)</f>
-      </c>
-    </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG112" s="3">
+        <f>IF($K112="","",Y112-AF112)</f>
+      </c>
+    </row>
+    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="D113" s="2"/>
       <c r="J113" s="3"/>
@@ -6524,16 +6548,16 @@
         <f>IF($K113="","",L113-M113-R113-S113-T113-U113-V113-W113)</f>
       </c>
       <c r="Z113" s="3">
-        <f>IF($K113="","",(Y113-AB113)/J113*100)</f>
+        <f>IF($K113="","",(Y113-AF113)/J113*100)</f>
       </c>
       <c r="AA113" s="3">
         <f>IF($K113="","",M113-X113)</f>
       </c>
-      <c r="AC113" s="3">
-        <f>IF($K113="","",Y113-AB113)</f>
-      </c>
-    </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG113" s="3">
+        <f>IF($K113="","",Y113-AF113)</f>
+      </c>
+    </row>
+    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="D114" s="2"/>
       <c r="J114" s="3"/>
@@ -6575,16 +6599,16 @@
         <f>IF($K114="","",L114-M114-R114-S114-T114-U114-V114-W114)</f>
       </c>
       <c r="Z114" s="3">
-        <f>IF($K114="","",(Y114-AB114)/J114*100)</f>
+        <f>IF($K114="","",(Y114-AF114)/J114*100)</f>
       </c>
       <c r="AA114" s="3">
         <f>IF($K114="","",M114-X114)</f>
       </c>
-      <c r="AC114" s="3">
-        <f>IF($K114="","",Y114-AB114)</f>
-      </c>
-    </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG114" s="3">
+        <f>IF($K114="","",Y114-AF114)</f>
+      </c>
+    </row>
+    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="D115" s="2"/>
       <c r="J115" s="3"/>
@@ -6626,16 +6650,16 @@
         <f>IF($K115="","",L115-M115-R115-S115-T115-U115-V115-W115)</f>
       </c>
       <c r="Z115" s="3">
-        <f>IF($K115="","",(Y115-AB115)/J115*100)</f>
+        <f>IF($K115="","",(Y115-AF115)/J115*100)</f>
       </c>
       <c r="AA115" s="3">
         <f>IF($K115="","",M115-X115)</f>
       </c>
-      <c r="AC115" s="3">
-        <f>IF($K115="","",Y115-AB115)</f>
-      </c>
-    </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG115" s="3">
+        <f>IF($K115="","",Y115-AF115)</f>
+      </c>
+    </row>
+    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="D116" s="2"/>
       <c r="J116" s="3"/>
@@ -6677,16 +6701,16 @@
         <f>IF($K116="","",L116-M116-R116-S116-T116-U116-V116-W116)</f>
       </c>
       <c r="Z116" s="3">
-        <f>IF($K116="","",(Y116-AB116)/J116*100)</f>
+        <f>IF($K116="","",(Y116-AF116)/J116*100)</f>
       </c>
       <c r="AA116" s="3">
         <f>IF($K116="","",M116-X116)</f>
       </c>
-      <c r="AC116" s="3">
-        <f>IF($K116="","",Y116-AB116)</f>
-      </c>
-    </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG116" s="3">
+        <f>IF($K116="","",Y116-AF116)</f>
+      </c>
+    </row>
+    <row r="117" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="D117" s="2"/>
       <c r="J117" s="3"/>
@@ -6728,16 +6752,16 @@
         <f>IF($K117="","",L117-M117-R117-S117-T117-U117-V117-W117)</f>
       </c>
       <c r="Z117" s="3">
-        <f>IF($K117="","",(Y117-AB117)/J117*100)</f>
+        <f>IF($K117="","",(Y117-AF117)/J117*100)</f>
       </c>
       <c r="AA117" s="3">
         <f>IF($K117="","",M117-X117)</f>
       </c>
-      <c r="AC117" s="3">
-        <f>IF($K117="","",Y117-AB117)</f>
-      </c>
-    </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG117" s="3">
+        <f>IF($K117="","",Y117-AF117)</f>
+      </c>
+    </row>
+    <row r="118" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="D118" s="2"/>
       <c r="J118" s="3"/>
@@ -6779,16 +6803,16 @@
         <f>IF($K118="","",L118-M118-R118-S118-T118-U118-V118-W118)</f>
       </c>
       <c r="Z118" s="3">
-        <f>IF($K118="","",(Y118-AB118)/J118*100)</f>
+        <f>IF($K118="","",(Y118-AF118)/J118*100)</f>
       </c>
       <c r="AA118" s="3">
         <f>IF($K118="","",M118-X118)</f>
       </c>
-      <c r="AC118" s="3">
-        <f>IF($K118="","",Y118-AB118)</f>
-      </c>
-    </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG118" s="3">
+        <f>IF($K118="","",Y118-AF118)</f>
+      </c>
+    </row>
+    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="D119" s="2"/>
       <c r="J119" s="3"/>
@@ -6830,16 +6854,16 @@
         <f>IF($K119="","",L119-M119-R119-S119-T119-U119-V119-W119)</f>
       </c>
       <c r="Z119" s="3">
-        <f>IF($K119="","",(Y119-AB119)/J119*100)</f>
+        <f>IF($K119="","",(Y119-AF119)/J119*100)</f>
       </c>
       <c r="AA119" s="3">
         <f>IF($K119="","",M119-X119)</f>
       </c>
-      <c r="AC119" s="3">
-        <f>IF($K119="","",Y119-AB119)</f>
-      </c>
-    </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG119" s="3">
+        <f>IF($K119="","",Y119-AF119)</f>
+      </c>
+    </row>
+    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="D120" s="2"/>
       <c r="J120" s="3"/>
@@ -6881,16 +6905,16 @@
         <f>IF($K120="","",L120-M120-R120-S120-T120-U120-V120-W120)</f>
       </c>
       <c r="Z120" s="3">
-        <f>IF($K120="","",(Y120-AB120)/J120*100)</f>
+        <f>IF($K120="","",(Y120-AF120)/J120*100)</f>
       </c>
       <c r="AA120" s="3">
         <f>IF($K120="","",M120-X120)</f>
       </c>
-      <c r="AC120" s="3">
-        <f>IF($K120="","",Y120-AB120)</f>
-      </c>
-    </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG120" s="3">
+        <f>IF($K120="","",Y120-AF120)</f>
+      </c>
+    </row>
+    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="D121" s="2"/>
       <c r="J121" s="3"/>
@@ -6932,16 +6956,16 @@
         <f>IF($K121="","",L121-M121-R121-S121-T121-U121-V121-W121)</f>
       </c>
       <c r="Z121" s="3">
-        <f>IF($K121="","",(Y121-AB121)/J121*100)</f>
+        <f>IF($K121="","",(Y121-AF121)/J121*100)</f>
       </c>
       <c r="AA121" s="3">
         <f>IF($K121="","",M121-X121)</f>
       </c>
-      <c r="AC121" s="3">
-        <f>IF($K121="","",Y121-AB121)</f>
-      </c>
-    </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG121" s="3">
+        <f>IF($K121="","",Y121-AF121)</f>
+      </c>
+    </row>
+    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="D122" s="2"/>
       <c r="J122" s="3"/>
@@ -6983,16 +7007,16 @@
         <f>IF($K122="","",L122-M122-R122-S122-T122-U122-V122-W122)</f>
       </c>
       <c r="Z122" s="3">
-        <f>IF($K122="","",(Y122-AB122)/J122*100)</f>
+        <f>IF($K122="","",(Y122-AF122)/J122*100)</f>
       </c>
       <c r="AA122" s="3">
         <f>IF($K122="","",M122-X122)</f>
       </c>
-      <c r="AC122" s="3">
-        <f>IF($K122="","",Y122-AB122)</f>
-      </c>
-    </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG122" s="3">
+        <f>IF($K122="","",Y122-AF122)</f>
+      </c>
+    </row>
+    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="D123" s="2"/>
       <c r="J123" s="3"/>
@@ -7034,16 +7058,16 @@
         <f>IF($K123="","",L123-M123-R123-S123-T123-U123-V123-W123)</f>
       </c>
       <c r="Z123" s="3">
-        <f>IF($K123="","",(Y123-AB123)/J123*100)</f>
+        <f>IF($K123="","",(Y123-AF123)/J123*100)</f>
       </c>
       <c r="AA123" s="3">
         <f>IF($K123="","",M123-X123)</f>
       </c>
-      <c r="AC123" s="3">
-        <f>IF($K123="","",Y123-AB123)</f>
-      </c>
-    </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG123" s="3">
+        <f>IF($K123="","",Y123-AF123)</f>
+      </c>
+    </row>
+    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="D124" s="2"/>
       <c r="J124" s="3"/>
@@ -7085,16 +7109,16 @@
         <f>IF($K124="","",L124-M124-R124-S124-T124-U124-V124-W124)</f>
       </c>
       <c r="Z124" s="3">
-        <f>IF($K124="","",(Y124-AB124)/J124*100)</f>
+        <f>IF($K124="","",(Y124-AF124)/J124*100)</f>
       </c>
       <c r="AA124" s="3">
         <f>IF($K124="","",M124-X124)</f>
       </c>
-      <c r="AC124" s="3">
-        <f>IF($K124="","",Y124-AB124)</f>
-      </c>
-    </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG124" s="3">
+        <f>IF($K124="","",Y124-AF124)</f>
+      </c>
+    </row>
+    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="D125" s="2"/>
       <c r="J125" s="3"/>
@@ -7136,16 +7160,16 @@
         <f>IF($K125="","",L125-M125-R125-S125-T125-U125-V125-W125)</f>
       </c>
       <c r="Z125" s="3">
-        <f>IF($K125="","",(Y125-AB125)/J125*100)</f>
+        <f>IF($K125="","",(Y125-AF125)/J125*100)</f>
       </c>
       <c r="AA125" s="3">
         <f>IF($K125="","",M125-X125)</f>
       </c>
-      <c r="AC125" s="3">
-        <f>IF($K125="","",Y125-AB125)</f>
-      </c>
-    </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG125" s="3">
+        <f>IF($K125="","",Y125-AF125)</f>
+      </c>
+    </row>
+    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="D126" s="2"/>
       <c r="J126" s="3"/>
@@ -7187,16 +7211,16 @@
         <f>IF($K126="","",L126-M126-R126-S126-T126-U126-V126-W126)</f>
       </c>
       <c r="Z126" s="3">
-        <f>IF($K126="","",(Y126-AB126)/J126*100)</f>
+        <f>IF($K126="","",(Y126-AF126)/J126*100)</f>
       </c>
       <c r="AA126" s="3">
         <f>IF($K126="","",M126-X126)</f>
       </c>
-      <c r="AC126" s="3">
-        <f>IF($K126="","",Y126-AB126)</f>
-      </c>
-    </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG126" s="3">
+        <f>IF($K126="","",Y126-AF126)</f>
+      </c>
+    </row>
+    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="D127" s="2"/>
       <c r="J127" s="3"/>
@@ -7238,16 +7262,16 @@
         <f>IF($K127="","",L127-M127-R127-S127-T127-U127-V127-W127)</f>
       </c>
       <c r="Z127" s="3">
-        <f>IF($K127="","",(Y127-AB127)/J127*100)</f>
+        <f>IF($K127="","",(Y127-AF127)/J127*100)</f>
       </c>
       <c r="AA127" s="3">
         <f>IF($K127="","",M127-X127)</f>
       </c>
-      <c r="AC127" s="3">
-        <f>IF($K127="","",Y127-AB127)</f>
-      </c>
-    </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG127" s="3">
+        <f>IF($K127="","",Y127-AF127)</f>
+      </c>
+    </row>
+    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="D128" s="2"/>
       <c r="J128" s="3"/>
@@ -7289,16 +7313,16 @@
         <f>IF($K128="","",L128-M128-R128-S128-T128-U128-V128-W128)</f>
       </c>
       <c r="Z128" s="3">
-        <f>IF($K128="","",(Y128-AB128)/J128*100)</f>
+        <f>IF($K128="","",(Y128-AF128)/J128*100)</f>
       </c>
       <c r="AA128" s="3">
         <f>IF($K128="","",M128-X128)</f>
       </c>
-      <c r="AC128" s="3">
-        <f>IF($K128="","",Y128-AB128)</f>
-      </c>
-    </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG128" s="3">
+        <f>IF($K128="","",Y128-AF128)</f>
+      </c>
+    </row>
+    <row r="129" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="D129" s="2"/>
       <c r="J129" s="3"/>
@@ -7340,16 +7364,16 @@
         <f>IF($K129="","",L129-M129-R129-S129-T129-U129-V129-W129)</f>
       </c>
       <c r="Z129" s="3">
-        <f>IF($K129="","",(Y129-AB129)/J129*100)</f>
+        <f>IF($K129="","",(Y129-AF129)/J129*100)</f>
       </c>
       <c r="AA129" s="3">
         <f>IF($K129="","",M129-X129)</f>
       </c>
-      <c r="AC129" s="3">
-        <f>IF($K129="","",Y129-AB129)</f>
-      </c>
-    </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG129" s="3">
+        <f>IF($K129="","",Y129-AF129)</f>
+      </c>
+    </row>
+    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="D130" s="2"/>
       <c r="J130" s="3"/>
@@ -7391,16 +7415,16 @@
         <f>IF($K130="","",L130-M130-R130-S130-T130-U130-V130-W130)</f>
       </c>
       <c r="Z130" s="3">
-        <f>IF($K130="","",(Y130-AB130)/J130*100)</f>
+        <f>IF($K130="","",(Y130-AF130)/J130*100)</f>
       </c>
       <c r="AA130" s="3">
         <f>IF($K130="","",M130-X130)</f>
       </c>
-      <c r="AC130" s="3">
-        <f>IF($K130="","",Y130-AB130)</f>
-      </c>
-    </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG130" s="3">
+        <f>IF($K130="","",Y130-AF130)</f>
+      </c>
+    </row>
+    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="D131" s="2"/>
       <c r="J131" s="3"/>
@@ -7442,16 +7466,16 @@
         <f>IF($K131="","",L131-M131-R131-S131-T131-U131-V131-W131)</f>
       </c>
       <c r="Z131" s="3">
-        <f>IF($K131="","",(Y131-AB131)/J131*100)</f>
+        <f>IF($K131="","",(Y131-AF131)/J131*100)</f>
       </c>
       <c r="AA131" s="3">
         <f>IF($K131="","",M131-X131)</f>
       </c>
-      <c r="AC131" s="3">
-        <f>IF($K131="","",Y131-AB131)</f>
-      </c>
-    </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG131" s="3">
+        <f>IF($K131="","",Y131-AF131)</f>
+      </c>
+    </row>
+    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="D132" s="2"/>
       <c r="J132" s="3"/>
@@ -7493,16 +7517,16 @@
         <f>IF($K132="","",L132-M132-R132-S132-T132-U132-V132-W132)</f>
       </c>
       <c r="Z132" s="3">
-        <f>IF($K132="","",(Y132-AB132)/J132*100)</f>
+        <f>IF($K132="","",(Y132-AF132)/J132*100)</f>
       </c>
       <c r="AA132" s="3">
         <f>IF($K132="","",M132-X132)</f>
       </c>
-      <c r="AC132" s="3">
-        <f>IF($K132="","",Y132-AB132)</f>
-      </c>
-    </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG132" s="3">
+        <f>IF($K132="","",Y132-AF132)</f>
+      </c>
+    </row>
+    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="D133" s="2"/>
       <c r="J133" s="3"/>
@@ -7544,16 +7568,16 @@
         <f>IF($K133="","",L133-M133-R133-S133-T133-U133-V133-W133)</f>
       </c>
       <c r="Z133" s="3">
-        <f>IF($K133="","",(Y133-AB133)/J133*100)</f>
+        <f>IF($K133="","",(Y133-AF133)/J133*100)</f>
       </c>
       <c r="AA133" s="3">
         <f>IF($K133="","",M133-X133)</f>
       </c>
-      <c r="AC133" s="3">
-        <f>IF($K133="","",Y133-AB133)</f>
-      </c>
-    </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG133" s="3">
+        <f>IF($K133="","",Y133-AF133)</f>
+      </c>
+    </row>
+    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="D134" s="2"/>
       <c r="J134" s="3"/>
@@ -7595,16 +7619,16 @@
         <f>IF($K134="","",L134-M134-R134-S134-T134-U134-V134-W134)</f>
       </c>
       <c r="Z134" s="3">
-        <f>IF($K134="","",(Y134-AB134)/J134*100)</f>
+        <f>IF($K134="","",(Y134-AF134)/J134*100)</f>
       </c>
       <c r="AA134" s="3">
         <f>IF($K134="","",M134-X134)</f>
       </c>
-      <c r="AC134" s="3">
-        <f>IF($K134="","",Y134-AB134)</f>
-      </c>
-    </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG134" s="3">
+        <f>IF($K134="","",Y134-AF134)</f>
+      </c>
+    </row>
+    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="D135" s="2"/>
       <c r="J135" s="3"/>
@@ -7646,16 +7670,16 @@
         <f>IF($K135="","",L135-M135-R135-S135-T135-U135-V135-W135)</f>
       </c>
       <c r="Z135" s="3">
-        <f>IF($K135="","",(Y135-AB135)/J135*100)</f>
+        <f>IF($K135="","",(Y135-AF135)/J135*100)</f>
       </c>
       <c r="AA135" s="3">
         <f>IF($K135="","",M135-X135)</f>
       </c>
-      <c r="AC135" s="3">
-        <f>IF($K135="","",Y135-AB135)</f>
-      </c>
-    </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG135" s="3">
+        <f>IF($K135="","",Y135-AF135)</f>
+      </c>
+    </row>
+    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="D136" s="2"/>
       <c r="J136" s="3"/>
@@ -7697,16 +7721,16 @@
         <f>IF($K136="","",L136-M136-R136-S136-T136-U136-V136-W136)</f>
       </c>
       <c r="Z136" s="3">
-        <f>IF($K136="","",(Y136-AB136)/J136*100)</f>
+        <f>IF($K136="","",(Y136-AF136)/J136*100)</f>
       </c>
       <c r="AA136" s="3">
         <f>IF($K136="","",M136-X136)</f>
       </c>
-      <c r="AC136" s="3">
-        <f>IF($K136="","",Y136-AB136)</f>
-      </c>
-    </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG136" s="3">
+        <f>IF($K136="","",Y136-AF136)</f>
+      </c>
+    </row>
+    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="D137" s="2"/>
       <c r="J137" s="3"/>
@@ -7748,16 +7772,16 @@
         <f>IF($K137="","",L137-M137-R137-S137-T137-U137-V137-W137)</f>
       </c>
       <c r="Z137" s="3">
-        <f>IF($K137="","",(Y137-AB137)/J137*100)</f>
+        <f>IF($K137="","",(Y137-AF137)/J137*100)</f>
       </c>
       <c r="AA137" s="3">
         <f>IF($K137="","",M137-X137)</f>
       </c>
-      <c r="AC137" s="3">
-        <f>IF($K137="","",Y137-AB137)</f>
-      </c>
-    </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG137" s="3">
+        <f>IF($K137="","",Y137-AF137)</f>
+      </c>
+    </row>
+    <row r="138" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="D138" s="2"/>
       <c r="J138" s="3"/>
@@ -7799,16 +7823,16 @@
         <f>IF($K138="","",L138-M138-R138-S138-T138-U138-V138-W138)</f>
       </c>
       <c r="Z138" s="3">
-        <f>IF($K138="","",(Y138-AB138)/J138*100)</f>
+        <f>IF($K138="","",(Y138-AF138)/J138*100)</f>
       </c>
       <c r="AA138" s="3">
         <f>IF($K138="","",M138-X138)</f>
       </c>
-      <c r="AC138" s="3">
-        <f>IF($K138="","",Y138-AB138)</f>
-      </c>
-    </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG138" s="3">
+        <f>IF($K138="","",Y138-AF138)</f>
+      </c>
+    </row>
+    <row r="139" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="D139" s="2"/>
       <c r="J139" s="3"/>
@@ -7850,16 +7874,16 @@
         <f>IF($K139="","",L139-M139-R139-S139-T139-U139-V139-W139)</f>
       </c>
       <c r="Z139" s="3">
-        <f>IF($K139="","",(Y139-AB139)/J139*100)</f>
+        <f>IF($K139="","",(Y139-AF139)/J139*100)</f>
       </c>
       <c r="AA139" s="3">
         <f>IF($K139="","",M139-X139)</f>
       </c>
-      <c r="AC139" s="3">
-        <f>IF($K139="","",Y139-AB139)</f>
-      </c>
-    </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG139" s="3">
+        <f>IF($K139="","",Y139-AF139)</f>
+      </c>
+    </row>
+    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="D140" s="2"/>
       <c r="J140" s="3"/>
@@ -7901,16 +7925,16 @@
         <f>IF($K140="","",L140-M140-R140-S140-T140-U140-V140-W140)</f>
       </c>
       <c r="Z140" s="3">
-        <f>IF($K140="","",(Y140-AB140)/J140*100)</f>
+        <f>IF($K140="","",(Y140-AF140)/J140*100)</f>
       </c>
       <c r="AA140" s="3">
         <f>IF($K140="","",M140-X140)</f>
       </c>
-      <c r="AC140" s="3">
-        <f>IF($K140="","",Y140-AB140)</f>
-      </c>
-    </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG140" s="3">
+        <f>IF($K140="","",Y140-AF140)</f>
+      </c>
+    </row>
+    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="D141" s="2"/>
       <c r="J141" s="3"/>
@@ -7952,16 +7976,16 @@
         <f>IF($K141="","",L141-M141-R141-S141-T141-U141-V141-W141)</f>
       </c>
       <c r="Z141" s="3">
-        <f>IF($K141="","",(Y141-AB141)/J141*100)</f>
+        <f>IF($K141="","",(Y141-AF141)/J141*100)</f>
       </c>
       <c r="AA141" s="3">
         <f>IF($K141="","",M141-X141)</f>
       </c>
-      <c r="AC141" s="3">
-        <f>IF($K141="","",Y141-AB141)</f>
-      </c>
-    </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG141" s="3">
+        <f>IF($K141="","",Y141-AF141)</f>
+      </c>
+    </row>
+    <row r="142" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="D142" s="2"/>
       <c r="J142" s="3"/>
@@ -8003,16 +8027,16 @@
         <f>IF($K142="","",L142-M142-R142-S142-T142-U142-V142-W142)</f>
       </c>
       <c r="Z142" s="3">
-        <f>IF($K142="","",(Y142-AB142)/J142*100)</f>
+        <f>IF($K142="","",(Y142-AF142)/J142*100)</f>
       </c>
       <c r="AA142" s="3">
         <f>IF($K142="","",M142-X142)</f>
       </c>
-      <c r="AC142" s="3">
-        <f>IF($K142="","",Y142-AB142)</f>
-      </c>
-    </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG142" s="3">
+        <f>IF($K142="","",Y142-AF142)</f>
+      </c>
+    </row>
+    <row r="143" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="D143" s="2"/>
       <c r="J143" s="3"/>
@@ -8054,16 +8078,16 @@
         <f>IF($K143="","",L143-M143-R143-S143-T143-U143-V143-W143)</f>
       </c>
       <c r="Z143" s="3">
-        <f>IF($K143="","",(Y143-AB143)/J143*100)</f>
+        <f>IF($K143="","",(Y143-AF143)/J143*100)</f>
       </c>
       <c r="AA143" s="3">
         <f>IF($K143="","",M143-X143)</f>
       </c>
-      <c r="AC143" s="3">
-        <f>IF($K143="","",Y143-AB143)</f>
-      </c>
-    </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG143" s="3">
+        <f>IF($K143="","",Y143-AF143)</f>
+      </c>
+    </row>
+    <row r="144" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="D144" s="2"/>
       <c r="J144" s="3"/>
@@ -8105,16 +8129,16 @@
         <f>IF($K144="","",L144-M144-R144-S144-T144-U144-V144-W144)</f>
       </c>
       <c r="Z144" s="3">
-        <f>IF($K144="","",(Y144-AB144)/J144*100)</f>
+        <f>IF($K144="","",(Y144-AF144)/J144*100)</f>
       </c>
       <c r="AA144" s="3">
         <f>IF($K144="","",M144-X144)</f>
       </c>
-      <c r="AC144" s="3">
-        <f>IF($K144="","",Y144-AB144)</f>
-      </c>
-    </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG144" s="3">
+        <f>IF($K144="","",Y144-AF144)</f>
+      </c>
+    </row>
+    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="D145" s="2"/>
       <c r="J145" s="3"/>
@@ -8156,16 +8180,16 @@
         <f>IF($K145="","",L145-M145-R145-S145-T145-U145-V145-W145)</f>
       </c>
       <c r="Z145" s="3">
-        <f>IF($K145="","",(Y145-AB145)/J145*100)</f>
+        <f>IF($K145="","",(Y145-AF145)/J145*100)</f>
       </c>
       <c r="AA145" s="3">
         <f>IF($K145="","",M145-X145)</f>
       </c>
-      <c r="AC145" s="3">
-        <f>IF($K145="","",Y145-AB145)</f>
-      </c>
-    </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG145" s="3">
+        <f>IF($K145="","",Y145-AF145)</f>
+      </c>
+    </row>
+    <row r="146" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="D146" s="2"/>
       <c r="J146" s="3"/>
@@ -8207,16 +8231,16 @@
         <f>IF($K146="","",L146-M146-R146-S146-T146-U146-V146-W146)</f>
       </c>
       <c r="Z146" s="3">
-        <f>IF($K146="","",(Y146-AB146)/J146*100)</f>
+        <f>IF($K146="","",(Y146-AF146)/J146*100)</f>
       </c>
       <c r="AA146" s="3">
         <f>IF($K146="","",M146-X146)</f>
       </c>
-      <c r="AC146" s="3">
-        <f>IF($K146="","",Y146-AB146)</f>
-      </c>
-    </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG146" s="3">
+        <f>IF($K146="","",Y146-AF146)</f>
+      </c>
+    </row>
+    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="D147" s="2"/>
       <c r="J147" s="3"/>
@@ -8258,16 +8282,16 @@
         <f>IF($K147="","",L147-M147-R147-S147-T147-U147-V147-W147)</f>
       </c>
       <c r="Z147" s="3">
-        <f>IF($K147="","",(Y147-AB147)/J147*100)</f>
+        <f>IF($K147="","",(Y147-AF147)/J147*100)</f>
       </c>
       <c r="AA147" s="3">
         <f>IF($K147="","",M147-X147)</f>
       </c>
-      <c r="AC147" s="3">
-        <f>IF($K147="","",Y147-AB147)</f>
-      </c>
-    </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG147" s="3">
+        <f>IF($K147="","",Y147-AF147)</f>
+      </c>
+    </row>
+    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="D148" s="2"/>
       <c r="J148" s="3"/>
@@ -8309,16 +8333,16 @@
         <f>IF($K148="","",L148-M148-R148-S148-T148-U148-V148-W148)</f>
       </c>
       <c r="Z148" s="3">
-        <f>IF($K148="","",(Y148-AB148)/J148*100)</f>
+        <f>IF($K148="","",(Y148-AF148)/J148*100)</f>
       </c>
       <c r="AA148" s="3">
         <f>IF($K148="","",M148-X148)</f>
       </c>
-      <c r="AC148" s="3">
-        <f>IF($K148="","",Y148-AB148)</f>
-      </c>
-    </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG148" s="3">
+        <f>IF($K148="","",Y148-AF148)</f>
+      </c>
+    </row>
+    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="D149" s="2"/>
       <c r="J149" s="3"/>
@@ -8360,16 +8384,16 @@
         <f>IF($K149="","",L149-M149-R149-S149-T149-U149-V149-W149)</f>
       </c>
       <c r="Z149" s="3">
-        <f>IF($K149="","",(Y149-AB149)/J149*100)</f>
+        <f>IF($K149="","",(Y149-AF149)/J149*100)</f>
       </c>
       <c r="AA149" s="3">
         <f>IF($K149="","",M149-X149)</f>
       </c>
-      <c r="AC149" s="3">
-        <f>IF($K149="","",Y149-AB149)</f>
-      </c>
-    </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG149" s="3">
+        <f>IF($K149="","",Y149-AF149)</f>
+      </c>
+    </row>
+    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="D150" s="2"/>
       <c r="J150" s="3"/>
@@ -8411,16 +8435,16 @@
         <f>IF($K150="","",L150-M150-R150-S150-T150-U150-V150-W150)</f>
       </c>
       <c r="Z150" s="3">
-        <f>IF($K150="","",(Y150-AB150)/J150*100)</f>
+        <f>IF($K150="","",(Y150-AF150)/J150*100)</f>
       </c>
       <c r="AA150" s="3">
         <f>IF($K150="","",M150-X150)</f>
       </c>
-      <c r="AC150" s="3">
-        <f>IF($K150="","",Y150-AB150)</f>
-      </c>
-    </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG150" s="3">
+        <f>IF($K150="","",Y150-AF150)</f>
+      </c>
+    </row>
+    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="D151" s="2"/>
       <c r="J151" s="3"/>
@@ -8462,16 +8486,16 @@
         <f>IF($K151="","",L151-M151-R151-S151-T151-U151-V151-W151)</f>
       </c>
       <c r="Z151" s="3">
-        <f>IF($K151="","",(Y151-AB151)/J151*100)</f>
+        <f>IF($K151="","",(Y151-AF151)/J151*100)</f>
       </c>
       <c r="AA151" s="3">
         <f>IF($K151="","",M151-X151)</f>
       </c>
-      <c r="AC151" s="3">
-        <f>IF($K151="","",Y151-AB151)</f>
-      </c>
-    </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG151" s="3">
+        <f>IF($K151="","",Y151-AF151)</f>
+      </c>
+    </row>
+    <row r="152" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="D152" s="2"/>
       <c r="J152" s="3"/>
@@ -8513,16 +8537,16 @@
         <f>IF($K152="","",L152-M152-R152-S152-T152-U152-V152-W152)</f>
       </c>
       <c r="Z152" s="3">
-        <f>IF($K152="","",(Y152-AB152)/J152*100)</f>
+        <f>IF($K152="","",(Y152-AF152)/J152*100)</f>
       </c>
       <c r="AA152" s="3">
         <f>IF($K152="","",M152-X152)</f>
       </c>
-      <c r="AC152" s="3">
-        <f>IF($K152="","",Y152-AB152)</f>
-      </c>
-    </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG152" s="3">
+        <f>IF($K152="","",Y152-AF152)</f>
+      </c>
+    </row>
+    <row r="153" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="D153" s="2"/>
       <c r="J153" s="3"/>
@@ -8564,16 +8588,16 @@
         <f>IF($K153="","",L153-M153-R153-S153-T153-U153-V153-W153)</f>
       </c>
       <c r="Z153" s="3">
-        <f>IF($K153="","",(Y153-AB153)/J153*100)</f>
+        <f>IF($K153="","",(Y153-AF153)/J153*100)</f>
       </c>
       <c r="AA153" s="3">
         <f>IF($K153="","",M153-X153)</f>
       </c>
-      <c r="AC153" s="3">
-        <f>IF($K153="","",Y153-AB153)</f>
-      </c>
-    </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG153" s="3">
+        <f>IF($K153="","",Y153-AF153)</f>
+      </c>
+    </row>
+    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="D154" s="2"/>
       <c r="J154" s="3"/>
@@ -8615,16 +8639,16 @@
         <f>IF($K154="","",L154-M154-R154-S154-T154-U154-V154-W154)</f>
       </c>
       <c r="Z154" s="3">
-        <f>IF($K154="","",(Y154-AB154)/J154*100)</f>
+        <f>IF($K154="","",(Y154-AF154)/J154*100)</f>
       </c>
       <c r="AA154" s="3">
         <f>IF($K154="","",M154-X154)</f>
       </c>
-      <c r="AC154" s="3">
-        <f>IF($K154="","",Y154-AB154)</f>
-      </c>
-    </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG154" s="3">
+        <f>IF($K154="","",Y154-AF154)</f>
+      </c>
+    </row>
+    <row r="155" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="D155" s="2"/>
       <c r="J155" s="3"/>
@@ -8666,16 +8690,16 @@
         <f>IF($K155="","",L155-M155-R155-S155-T155-U155-V155-W155)</f>
       </c>
       <c r="Z155" s="3">
-        <f>IF($K155="","",(Y155-AB155)/J155*100)</f>
+        <f>IF($K155="","",(Y155-AF155)/J155*100)</f>
       </c>
       <c r="AA155" s="3">
         <f>IF($K155="","",M155-X155)</f>
       </c>
-      <c r="AC155" s="3">
-        <f>IF($K155="","",Y155-AB155)</f>
-      </c>
-    </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG155" s="3">
+        <f>IF($K155="","",Y155-AF155)</f>
+      </c>
+    </row>
+    <row r="156" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="D156" s="2"/>
       <c r="J156" s="3"/>
@@ -8717,16 +8741,16 @@
         <f>IF($K156="","",L156-M156-R156-S156-T156-U156-V156-W156)</f>
       </c>
       <c r="Z156" s="3">
-        <f>IF($K156="","",(Y156-AB156)/J156*100)</f>
+        <f>IF($K156="","",(Y156-AF156)/J156*100)</f>
       </c>
       <c r="AA156" s="3">
         <f>IF($K156="","",M156-X156)</f>
       </c>
-      <c r="AC156" s="3">
-        <f>IF($K156="","",Y156-AB156)</f>
-      </c>
-    </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG156" s="3">
+        <f>IF($K156="","",Y156-AF156)</f>
+      </c>
+    </row>
+    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="D157" s="2"/>
       <c r="J157" s="3"/>
@@ -8768,16 +8792,16 @@
         <f>IF($K157="","",L157-M157-R157-S157-T157-U157-V157-W157)</f>
       </c>
       <c r="Z157" s="3">
-        <f>IF($K157="","",(Y157-AB157)/J157*100)</f>
+        <f>IF($K157="","",(Y157-AF157)/J157*100)</f>
       </c>
       <c r="AA157" s="3">
         <f>IF($K157="","",M157-X157)</f>
       </c>
-      <c r="AC157" s="3">
-        <f>IF($K157="","",Y157-AB157)</f>
-      </c>
-    </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG157" s="3">
+        <f>IF($K157="","",Y157-AF157)</f>
+      </c>
+    </row>
+    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="D158" s="2"/>
       <c r="J158" s="3"/>
@@ -8819,16 +8843,16 @@
         <f>IF($K158="","",L158-M158-R158-S158-T158-U158-V158-W158)</f>
       </c>
       <c r="Z158" s="3">
-        <f>IF($K158="","",(Y158-AB158)/J158*100)</f>
+        <f>IF($K158="","",(Y158-AF158)/J158*100)</f>
       </c>
       <c r="AA158" s="3">
         <f>IF($K158="","",M158-X158)</f>
       </c>
-      <c r="AC158" s="3">
-        <f>IF($K158="","",Y158-AB158)</f>
-      </c>
-    </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG158" s="3">
+        <f>IF($K158="","",Y158-AF158)</f>
+      </c>
+    </row>
+    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="D159" s="2"/>
       <c r="J159" s="3"/>
@@ -8870,16 +8894,16 @@
         <f>IF($K159="","",L159-M159-R159-S159-T159-U159-V159-W159)</f>
       </c>
       <c r="Z159" s="3">
-        <f>IF($K159="","",(Y159-AB159)/J159*100)</f>
+        <f>IF($K159="","",(Y159-AF159)/J159*100)</f>
       </c>
       <c r="AA159" s="3">
         <f>IF($K159="","",M159-X159)</f>
       </c>
-      <c r="AC159" s="3">
-        <f>IF($K159="","",Y159-AB159)</f>
-      </c>
-    </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG159" s="3">
+        <f>IF($K159="","",Y159-AF159)</f>
+      </c>
+    </row>
+    <row r="160" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="D160" s="2"/>
       <c r="J160" s="3"/>
@@ -8921,16 +8945,16 @@
         <f>IF($K160="","",L160-M160-R160-S160-T160-U160-V160-W160)</f>
       </c>
       <c r="Z160" s="3">
-        <f>IF($K160="","",(Y160-AB160)/J160*100)</f>
+        <f>IF($K160="","",(Y160-AF160)/J160*100)</f>
       </c>
       <c r="AA160" s="3">
         <f>IF($K160="","",M160-X160)</f>
       </c>
-      <c r="AC160" s="3">
-        <f>IF($K160="","",Y160-AB160)</f>
-      </c>
-    </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG160" s="3">
+        <f>IF($K160="","",Y160-AF160)</f>
+      </c>
+    </row>
+    <row r="161" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="D161" s="2"/>
       <c r="J161" s="3"/>
@@ -8972,16 +8996,16 @@
         <f>IF($K161="","",L161-M161-R161-S161-T161-U161-V161-W161)</f>
       </c>
       <c r="Z161" s="3">
-        <f>IF($K161="","",(Y161-AB161)/J161*100)</f>
+        <f>IF($K161="","",(Y161-AF161)/J161*100)</f>
       </c>
       <c r="AA161" s="3">
         <f>IF($K161="","",M161-X161)</f>
       </c>
-      <c r="AC161" s="3">
-        <f>IF($K161="","",Y161-AB161)</f>
-      </c>
-    </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG161" s="3">
+        <f>IF($K161="","",Y161-AF161)</f>
+      </c>
+    </row>
+    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="D162" s="2"/>
       <c r="J162" s="3"/>
@@ -9023,16 +9047,16 @@
         <f>IF($K162="","",L162-M162-R162-S162-T162-U162-V162-W162)</f>
       </c>
       <c r="Z162" s="3">
-        <f>IF($K162="","",(Y162-AB162)/J162*100)</f>
+        <f>IF($K162="","",(Y162-AF162)/J162*100)</f>
       </c>
       <c r="AA162" s="3">
         <f>IF($K162="","",M162-X162)</f>
       </c>
-      <c r="AC162" s="3">
-        <f>IF($K162="","",Y162-AB162)</f>
-      </c>
-    </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG162" s="3">
+        <f>IF($K162="","",Y162-AF162)</f>
+      </c>
+    </row>
+    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="D163" s="2"/>
       <c r="J163" s="3"/>
@@ -9074,16 +9098,16 @@
         <f>IF($K163="","",L163-M163-R163-S163-T163-U163-V163-W163)</f>
       </c>
       <c r="Z163" s="3">
-        <f>IF($K163="","",(Y163-AB163)/J163*100)</f>
+        <f>IF($K163="","",(Y163-AF163)/J163*100)</f>
       </c>
       <c r="AA163" s="3">
         <f>IF($K163="","",M163-X163)</f>
       </c>
-      <c r="AC163" s="3">
-        <f>IF($K163="","",Y163-AB163)</f>
-      </c>
-    </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG163" s="3">
+        <f>IF($K163="","",Y163-AF163)</f>
+      </c>
+    </row>
+    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="D164" s="2"/>
       <c r="J164" s="3"/>
@@ -9125,16 +9149,16 @@
         <f>IF($K164="","",L164-M164-R164-S164-T164-U164-V164-W164)</f>
       </c>
       <c r="Z164" s="3">
-        <f>IF($K164="","",(Y164-AB164)/J164*100)</f>
+        <f>IF($K164="","",(Y164-AF164)/J164*100)</f>
       </c>
       <c r="AA164" s="3">
         <f>IF($K164="","",M164-X164)</f>
       </c>
-      <c r="AC164" s="3">
-        <f>IF($K164="","",Y164-AB164)</f>
-      </c>
-    </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG164" s="3">
+        <f>IF($K164="","",Y164-AF164)</f>
+      </c>
+    </row>
+    <row r="165" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="D165" s="2"/>
       <c r="J165" s="3"/>
@@ -9176,16 +9200,16 @@
         <f>IF($K165="","",L165-M165-R165-S165-T165-U165-V165-W165)</f>
       </c>
       <c r="Z165" s="3">
-        <f>IF($K165="","",(Y165-AB165)/J165*100)</f>
+        <f>IF($K165="","",(Y165-AF165)/J165*100)</f>
       </c>
       <c r="AA165" s="3">
         <f>IF($K165="","",M165-X165)</f>
       </c>
-      <c r="AC165" s="3">
-        <f>IF($K165="","",Y165-AB165)</f>
-      </c>
-    </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG165" s="3">
+        <f>IF($K165="","",Y165-AF165)</f>
+      </c>
+    </row>
+    <row r="166" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="D166" s="2"/>
       <c r="J166" s="3"/>
@@ -9227,16 +9251,16 @@
         <f>IF($K166="","",L166-M166-R166-S166-T166-U166-V166-W166)</f>
       </c>
       <c r="Z166" s="3">
-        <f>IF($K166="","",(Y166-AB166)/J166*100)</f>
+        <f>IF($K166="","",(Y166-AF166)/J166*100)</f>
       </c>
       <c r="AA166" s="3">
         <f>IF($K166="","",M166-X166)</f>
       </c>
-      <c r="AC166" s="3">
-        <f>IF($K166="","",Y166-AB166)</f>
-      </c>
-    </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG166" s="3">
+        <f>IF($K166="","",Y166-AF166)</f>
+      </c>
+    </row>
+    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="D167" s="2"/>
       <c r="J167" s="3"/>
@@ -9278,16 +9302,16 @@
         <f>IF($K167="","",L167-M167-R167-S167-T167-U167-V167-W167)</f>
       </c>
       <c r="Z167" s="3">
-        <f>IF($K167="","",(Y167-AB167)/J167*100)</f>
+        <f>IF($K167="","",(Y167-AF167)/J167*100)</f>
       </c>
       <c r="AA167" s="3">
         <f>IF($K167="","",M167-X167)</f>
       </c>
-      <c r="AC167" s="3">
-        <f>IF($K167="","",Y167-AB167)</f>
-      </c>
-    </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG167" s="3">
+        <f>IF($K167="","",Y167-AF167)</f>
+      </c>
+    </row>
+    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="D168" s="2"/>
       <c r="J168" s="3"/>
@@ -9329,16 +9353,16 @@
         <f>IF($K168="","",L168-M168-R168-S168-T168-U168-V168-W168)</f>
       </c>
       <c r="Z168" s="3">
-        <f>IF($K168="","",(Y168-AB168)/J168*100)</f>
+        <f>IF($K168="","",(Y168-AF168)/J168*100)</f>
       </c>
       <c r="AA168" s="3">
         <f>IF($K168="","",M168-X168)</f>
       </c>
-      <c r="AC168" s="3">
-        <f>IF($K168="","",Y168-AB168)</f>
-      </c>
-    </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG168" s="3">
+        <f>IF($K168="","",Y168-AF168)</f>
+      </c>
+    </row>
+    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="D169" s="2"/>
       <c r="J169" s="3"/>
@@ -9380,16 +9404,16 @@
         <f>IF($K169="","",L169-M169-R169-S169-T169-U169-V169-W169)</f>
       </c>
       <c r="Z169" s="3">
-        <f>IF($K169="","",(Y169-AB169)/J169*100)</f>
+        <f>IF($K169="","",(Y169-AF169)/J169*100)</f>
       </c>
       <c r="AA169" s="3">
         <f>IF($K169="","",M169-X169)</f>
       </c>
-      <c r="AC169" s="3">
-        <f>IF($K169="","",Y169-AB169)</f>
-      </c>
-    </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG169" s="3">
+        <f>IF($K169="","",Y169-AF169)</f>
+      </c>
+    </row>
+    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="D170" s="2"/>
       <c r="J170" s="3"/>
@@ -9431,16 +9455,16 @@
         <f>IF($K170="","",L170-M170-R170-S170-T170-U170-V170-W170)</f>
       </c>
       <c r="Z170" s="3">
-        <f>IF($K170="","",(Y170-AB170)/J170*100)</f>
+        <f>IF($K170="","",(Y170-AF170)/J170*100)</f>
       </c>
       <c r="AA170" s="3">
         <f>IF($K170="","",M170-X170)</f>
       </c>
-      <c r="AC170" s="3">
-        <f>IF($K170="","",Y170-AB170)</f>
-      </c>
-    </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG170" s="3">
+        <f>IF($K170="","",Y170-AF170)</f>
+      </c>
+    </row>
+    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="D171" s="2"/>
       <c r="J171" s="3"/>
@@ -9482,16 +9506,16 @@
         <f>IF($K171="","",L171-M171-R171-S171-T171-U171-V171-W171)</f>
       </c>
       <c r="Z171" s="3">
-        <f>IF($K171="","",(Y171-AB171)/J171*100)</f>
+        <f>IF($K171="","",(Y171-AF171)/J171*100)</f>
       </c>
       <c r="AA171" s="3">
         <f>IF($K171="","",M171-X171)</f>
       </c>
-      <c r="AC171" s="3">
-        <f>IF($K171="","",Y171-AB171)</f>
-      </c>
-    </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG171" s="3">
+        <f>IF($K171="","",Y171-AF171)</f>
+      </c>
+    </row>
+    <row r="172" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="D172" s="2"/>
       <c r="J172" s="3"/>
@@ -9533,16 +9557,16 @@
         <f>IF($K172="","",L172-M172-R172-S172-T172-U172-V172-W172)</f>
       </c>
       <c r="Z172" s="3">
-        <f>IF($K172="","",(Y172-AB172)/J172*100)</f>
+        <f>IF($K172="","",(Y172-AF172)/J172*100)</f>
       </c>
       <c r="AA172" s="3">
         <f>IF($K172="","",M172-X172)</f>
       </c>
-      <c r="AC172" s="3">
-        <f>IF($K172="","",Y172-AB172)</f>
-      </c>
-    </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG172" s="3">
+        <f>IF($K172="","",Y172-AF172)</f>
+      </c>
+    </row>
+    <row r="173" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="D173" s="2"/>
       <c r="J173" s="3"/>
@@ -9584,16 +9608,16 @@
         <f>IF($K173="","",L173-M173-R173-S173-T173-U173-V173-W173)</f>
       </c>
       <c r="Z173" s="3">
-        <f>IF($K173="","",(Y173-AB173)/J173*100)</f>
+        <f>IF($K173="","",(Y173-AF173)/J173*100)</f>
       </c>
       <c r="AA173" s="3">
         <f>IF($K173="","",M173-X173)</f>
       </c>
-      <c r="AC173" s="3">
-        <f>IF($K173="","",Y173-AB173)</f>
-      </c>
-    </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG173" s="3">
+        <f>IF($K173="","",Y173-AF173)</f>
+      </c>
+    </row>
+    <row r="174" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="D174" s="2"/>
       <c r="J174" s="3"/>
@@ -9635,16 +9659,16 @@
         <f>IF($K174="","",L174-M174-R174-S174-T174-U174-V174-W174)</f>
       </c>
       <c r="Z174" s="3">
-        <f>IF($K174="","",(Y174-AB174)/J174*100)</f>
+        <f>IF($K174="","",(Y174-AF174)/J174*100)</f>
       </c>
       <c r="AA174" s="3">
         <f>IF($K174="","",M174-X174)</f>
       </c>
-      <c r="AC174" s="3">
-        <f>IF($K174="","",Y174-AB174)</f>
-      </c>
-    </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG174" s="3">
+        <f>IF($K174="","",Y174-AF174)</f>
+      </c>
+    </row>
+    <row r="175" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="D175" s="2"/>
       <c r="J175" s="3"/>
@@ -9686,16 +9710,16 @@
         <f>IF($K175="","",L175-M175-R175-S175-T175-U175-V175-W175)</f>
       </c>
       <c r="Z175" s="3">
-        <f>IF($K175="","",(Y175-AB175)/J175*100)</f>
+        <f>IF($K175="","",(Y175-AF175)/J175*100)</f>
       </c>
       <c r="AA175" s="3">
         <f>IF($K175="","",M175-X175)</f>
       </c>
-      <c r="AC175" s="3">
-        <f>IF($K175="","",Y175-AB175)</f>
-      </c>
-    </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG175" s="3">
+        <f>IF($K175="","",Y175-AF175)</f>
+      </c>
+    </row>
+    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="D176" s="2"/>
       <c r="J176" s="3"/>
@@ -9737,16 +9761,16 @@
         <f>IF($K176="","",L176-M176-R176-S176-T176-U176-V176-W176)</f>
       </c>
       <c r="Z176" s="3">
-        <f>IF($K176="","",(Y176-AB176)/J176*100)</f>
+        <f>IF($K176="","",(Y176-AF176)/J176*100)</f>
       </c>
       <c r="AA176" s="3">
         <f>IF($K176="","",M176-X176)</f>
       </c>
-      <c r="AC176" s="3">
-        <f>IF($K176="","",Y176-AB176)</f>
-      </c>
-    </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG176" s="3">
+        <f>IF($K176="","",Y176-AF176)</f>
+      </c>
+    </row>
+    <row r="177" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="D177" s="2"/>
       <c r="J177" s="3"/>
@@ -9788,16 +9812,16 @@
         <f>IF($K177="","",L177-M177-R177-S177-T177-U177-V177-W177)</f>
       </c>
       <c r="Z177" s="3">
-        <f>IF($K177="","",(Y177-AB177)/J177*100)</f>
+        <f>IF($K177="","",(Y177-AF177)/J177*100)</f>
       </c>
       <c r="AA177" s="3">
         <f>IF($K177="","",M177-X177)</f>
       </c>
-      <c r="AC177" s="3">
-        <f>IF($K177="","",Y177-AB177)</f>
-      </c>
-    </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG177" s="3">
+        <f>IF($K177="","",Y177-AF177)</f>
+      </c>
+    </row>
+    <row r="178" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="D178" s="2"/>
       <c r="J178" s="3"/>
@@ -9839,16 +9863,16 @@
         <f>IF($K178="","",L178-M178-R178-S178-T178-U178-V178-W178)</f>
       </c>
       <c r="Z178" s="3">
-        <f>IF($K178="","",(Y178-AB178)/J178*100)</f>
+        <f>IF($K178="","",(Y178-AF178)/J178*100)</f>
       </c>
       <c r="AA178" s="3">
         <f>IF($K178="","",M178-X178)</f>
       </c>
-      <c r="AC178" s="3">
-        <f>IF($K178="","",Y178-AB178)</f>
-      </c>
-    </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG178" s="3">
+        <f>IF($K178="","",Y178-AF178)</f>
+      </c>
+    </row>
+    <row r="179" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="D179" s="2"/>
       <c r="J179" s="3"/>
@@ -9890,16 +9914,16 @@
         <f>IF($K179="","",L179-M179-R179-S179-T179-U179-V179-W179)</f>
       </c>
       <c r="Z179" s="3">
-        <f>IF($K179="","",(Y179-AB179)/J179*100)</f>
+        <f>IF($K179="","",(Y179-AF179)/J179*100)</f>
       </c>
       <c r="AA179" s="3">
         <f>IF($K179="","",M179-X179)</f>
       </c>
-      <c r="AC179" s="3">
-        <f>IF($K179="","",Y179-AB179)</f>
-      </c>
-    </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG179" s="3">
+        <f>IF($K179="","",Y179-AF179)</f>
+      </c>
+    </row>
+    <row r="180" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="D180" s="2"/>
       <c r="J180" s="3"/>
@@ -9941,16 +9965,16 @@
         <f>IF($K180="","",L180-M180-R180-S180-T180-U180-V180-W180)</f>
       </c>
       <c r="Z180" s="3">
-        <f>IF($K180="","",(Y180-AB180)/J180*100)</f>
+        <f>IF($K180="","",(Y180-AF180)/J180*100)</f>
       </c>
       <c r="AA180" s="3">
         <f>IF($K180="","",M180-X180)</f>
       </c>
-      <c r="AC180" s="3">
-        <f>IF($K180="","",Y180-AB180)</f>
-      </c>
-    </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG180" s="3">
+        <f>IF($K180="","",Y180-AF180)</f>
+      </c>
+    </row>
+    <row r="181" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="D181" s="2"/>
       <c r="J181" s="3"/>
@@ -9992,16 +10016,16 @@
         <f>IF($K181="","",L181-M181-R181-S181-T181-U181-V181-W181)</f>
       </c>
       <c r="Z181" s="3">
-        <f>IF($K181="","",(Y181-AB181)/J181*100)</f>
+        <f>IF($K181="","",(Y181-AF181)/J181*100)</f>
       </c>
       <c r="AA181" s="3">
         <f>IF($K181="","",M181-X181)</f>
       </c>
-      <c r="AC181" s="3">
-        <f>IF($K181="","",Y181-AB181)</f>
-      </c>
-    </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG181" s="3">
+        <f>IF($K181="","",Y181-AF181)</f>
+      </c>
+    </row>
+    <row r="182" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="D182" s="2"/>
       <c r="J182" s="3"/>
@@ -10043,16 +10067,16 @@
         <f>IF($K182="","",L182-M182-R182-S182-T182-U182-V182-W182)</f>
       </c>
       <c r="Z182" s="3">
-        <f>IF($K182="","",(Y182-AB182)/J182*100)</f>
+        <f>IF($K182="","",(Y182-AF182)/J182*100)</f>
       </c>
       <c r="AA182" s="3">
         <f>IF($K182="","",M182-X182)</f>
       </c>
-      <c r="AC182" s="3">
-        <f>IF($K182="","",Y182-AB182)</f>
-      </c>
-    </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG182" s="3">
+        <f>IF($K182="","",Y182-AF182)</f>
+      </c>
+    </row>
+    <row r="183" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="D183" s="2"/>
       <c r="J183" s="3"/>
@@ -10094,16 +10118,16 @@
         <f>IF($K183="","",L183-M183-R183-S183-T183-U183-V183-W183)</f>
       </c>
       <c r="Z183" s="3">
-        <f>IF($K183="","",(Y183-AB183)/J183*100)</f>
+        <f>IF($K183="","",(Y183-AF183)/J183*100)</f>
       </c>
       <c r="AA183" s="3">
         <f>IF($K183="","",M183-X183)</f>
       </c>
-      <c r="AC183" s="3">
-        <f>IF($K183="","",Y183-AB183)</f>
-      </c>
-    </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG183" s="3">
+        <f>IF($K183="","",Y183-AF183)</f>
+      </c>
+    </row>
+    <row r="184" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="D184" s="2"/>
       <c r="J184" s="3"/>
@@ -10145,16 +10169,16 @@
         <f>IF($K184="","",L184-M184-R184-S184-T184-U184-V184-W184)</f>
       </c>
       <c r="Z184" s="3">
-        <f>IF($K184="","",(Y184-AB184)/J184*100)</f>
+        <f>IF($K184="","",(Y184-AF184)/J184*100)</f>
       </c>
       <c r="AA184" s="3">
         <f>IF($K184="","",M184-X184)</f>
       </c>
-      <c r="AC184" s="3">
-        <f>IF($K184="","",Y184-AB184)</f>
-      </c>
-    </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG184" s="3">
+        <f>IF($K184="","",Y184-AF184)</f>
+      </c>
+    </row>
+    <row r="185" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="D185" s="2"/>
       <c r="J185" s="3"/>
@@ -10196,16 +10220,16 @@
         <f>IF($K185="","",L185-M185-R185-S185-T185-U185-V185-W185)</f>
       </c>
       <c r="Z185" s="3">
-        <f>IF($K185="","",(Y185-AB185)/J185*100)</f>
+        <f>IF($K185="","",(Y185-AF185)/J185*100)</f>
       </c>
       <c r="AA185" s="3">
         <f>IF($K185="","",M185-X185)</f>
       </c>
-      <c r="AC185" s="3">
-        <f>IF($K185="","",Y185-AB185)</f>
-      </c>
-    </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG185" s="3">
+        <f>IF($K185="","",Y185-AF185)</f>
+      </c>
+    </row>
+    <row r="186" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="D186" s="2"/>
       <c r="J186" s="3"/>
@@ -10247,16 +10271,16 @@
         <f>IF($K186="","",L186-M186-R186-S186-T186-U186-V186-W186)</f>
       </c>
       <c r="Z186" s="3">
-        <f>IF($K186="","",(Y186-AB186)/J186*100)</f>
+        <f>IF($K186="","",(Y186-AF186)/J186*100)</f>
       </c>
       <c r="AA186" s="3">
         <f>IF($K186="","",M186-X186)</f>
       </c>
-      <c r="AC186" s="3">
-        <f>IF($K186="","",Y186-AB186)</f>
-      </c>
-    </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG186" s="3">
+        <f>IF($K186="","",Y186-AF186)</f>
+      </c>
+    </row>
+    <row r="187" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="D187" s="2"/>
       <c r="J187" s="3"/>
@@ -10298,16 +10322,16 @@
         <f>IF($K187="","",L187-M187-R187-S187-T187-U187-V187-W187)</f>
       </c>
       <c r="Z187" s="3">
-        <f>IF($K187="","",(Y187-AB187)/J187*100)</f>
+        <f>IF($K187="","",(Y187-AF187)/J187*100)</f>
       </c>
       <c r="AA187" s="3">
         <f>IF($K187="","",M187-X187)</f>
       </c>
-      <c r="AC187" s="3">
-        <f>IF($K187="","",Y187-AB187)</f>
-      </c>
-    </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG187" s="3">
+        <f>IF($K187="","",Y187-AF187)</f>
+      </c>
+    </row>
+    <row r="188" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="D188" s="2"/>
       <c r="J188" s="3"/>
@@ -10349,16 +10373,16 @@
         <f>IF($K188="","",L188-M188-R188-S188-T188-U188-V188-W188)</f>
       </c>
       <c r="Z188" s="3">
-        <f>IF($K188="","",(Y188-AB188)/J188*100)</f>
+        <f>IF($K188="","",(Y188-AF188)/J188*100)</f>
       </c>
       <c r="AA188" s="3">
         <f>IF($K188="","",M188-X188)</f>
       </c>
-      <c r="AC188" s="3">
-        <f>IF($K188="","",Y188-AB188)</f>
-      </c>
-    </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG188" s="3">
+        <f>IF($K188="","",Y188-AF188)</f>
+      </c>
+    </row>
+    <row r="189" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="D189" s="2"/>
       <c r="J189" s="3"/>
@@ -10400,16 +10424,16 @@
         <f>IF($K189="","",L189-M189-R189-S189-T189-U189-V189-W189)</f>
       </c>
       <c r="Z189" s="3">
-        <f>IF($K189="","",(Y189-AB189)/J189*100)</f>
+        <f>IF($K189="","",(Y189-AF189)/J189*100)</f>
       </c>
       <c r="AA189" s="3">
         <f>IF($K189="","",M189-X189)</f>
       </c>
-      <c r="AC189" s="3">
-        <f>IF($K189="","",Y189-AB189)</f>
-      </c>
-    </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG189" s="3">
+        <f>IF($K189="","",Y189-AF189)</f>
+      </c>
+    </row>
+    <row r="190" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="D190" s="2"/>
       <c r="J190" s="3"/>
@@ -10451,16 +10475,16 @@
         <f>IF($K190="","",L190-M190-R190-S190-T190-U190-V190-W190)</f>
       </c>
       <c r="Z190" s="3">
-        <f>IF($K190="","",(Y190-AB190)/J190*100)</f>
+        <f>IF($K190="","",(Y190-AF190)/J190*100)</f>
       </c>
       <c r="AA190" s="3">
         <f>IF($K190="","",M190-X190)</f>
       </c>
-      <c r="AC190" s="3">
-        <f>IF($K190="","",Y190-AB190)</f>
-      </c>
-    </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG190" s="3">
+        <f>IF($K190="","",Y190-AF190)</f>
+      </c>
+    </row>
+    <row r="191" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="D191" s="2"/>
       <c r="J191" s="3"/>
@@ -10502,16 +10526,16 @@
         <f>IF($K191="","",L191-M191-R191-S191-T191-U191-V191-W191)</f>
       </c>
       <c r="Z191" s="3">
-        <f>IF($K191="","",(Y191-AB191)/J191*100)</f>
+        <f>IF($K191="","",(Y191-AF191)/J191*100)</f>
       </c>
       <c r="AA191" s="3">
         <f>IF($K191="","",M191-X191)</f>
       </c>
-      <c r="AC191" s="3">
-        <f>IF($K191="","",Y191-AB191)</f>
-      </c>
-    </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG191" s="3">
+        <f>IF($K191="","",Y191-AF191)</f>
+      </c>
+    </row>
+    <row r="192" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="D192" s="2"/>
       <c r="J192" s="3"/>
@@ -10553,16 +10577,16 @@
         <f>IF($K192="","",L192-M192-R192-S192-T192-U192-V192-W192)</f>
       </c>
       <c r="Z192" s="3">
-        <f>IF($K192="","",(Y192-AB192)/J192*100)</f>
+        <f>IF($K192="","",(Y192-AF192)/J192*100)</f>
       </c>
       <c r="AA192" s="3">
         <f>IF($K192="","",M192-X192)</f>
       </c>
-      <c r="AC192" s="3">
-        <f>IF($K192="","",Y192-AB192)</f>
-      </c>
-    </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG192" s="3">
+        <f>IF($K192="","",Y192-AF192)</f>
+      </c>
+    </row>
+    <row r="193" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="D193" s="2"/>
       <c r="J193" s="3"/>
@@ -10604,16 +10628,16 @@
         <f>IF($K193="","",L193-M193-R193-S193-T193-U193-V193-W193)</f>
       </c>
       <c r="Z193" s="3">
-        <f>IF($K193="","",(Y193-AB193)/J193*100)</f>
+        <f>IF($K193="","",(Y193-AF193)/J193*100)</f>
       </c>
       <c r="AA193" s="3">
         <f>IF($K193="","",M193-X193)</f>
       </c>
-      <c r="AC193" s="3">
-        <f>IF($K193="","",Y193-AB193)</f>
-      </c>
-    </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG193" s="3">
+        <f>IF($K193="","",Y193-AF193)</f>
+      </c>
+    </row>
+    <row r="194" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="D194" s="2"/>
       <c r="J194" s="3"/>
@@ -10655,16 +10679,16 @@
         <f>IF($K194="","",L194-M194-R194-S194-T194-U194-V194-W194)</f>
       </c>
       <c r="Z194" s="3">
-        <f>IF($K194="","",(Y194-AB194)/J194*100)</f>
+        <f>IF($K194="","",(Y194-AF194)/J194*100)</f>
       </c>
       <c r="AA194" s="3">
         <f>IF($K194="","",M194-X194)</f>
       </c>
-      <c r="AC194" s="3">
-        <f>IF($K194="","",Y194-AB194)</f>
-      </c>
-    </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG194" s="3">
+        <f>IF($K194="","",Y194-AF194)</f>
+      </c>
+    </row>
+    <row r="195" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="D195" s="2"/>
       <c r="J195" s="3"/>
@@ -10706,16 +10730,16 @@
         <f>IF($K195="","",L195-M195-R195-S195-T195-U195-V195-W195)</f>
       </c>
       <c r="Z195" s="3">
-        <f>IF($K195="","",(Y195-AB195)/J195*100)</f>
+        <f>IF($K195="","",(Y195-AF195)/J195*100)</f>
       </c>
       <c r="AA195" s="3">
         <f>IF($K195="","",M195-X195)</f>
       </c>
-      <c r="AC195" s="3">
-        <f>IF($K195="","",Y195-AB195)</f>
-      </c>
-    </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG195" s="3">
+        <f>IF($K195="","",Y195-AF195)</f>
+      </c>
+    </row>
+    <row r="196" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="D196" s="2"/>
       <c r="J196" s="3"/>
@@ -10757,16 +10781,16 @@
         <f>IF($K196="","",L196-M196-R196-S196-T196-U196-V196-W196)</f>
       </c>
       <c r="Z196" s="3">
-        <f>IF($K196="","",(Y196-AB196)/J196*100)</f>
+        <f>IF($K196="","",(Y196-AF196)/J196*100)</f>
       </c>
       <c r="AA196" s="3">
         <f>IF($K196="","",M196-X196)</f>
       </c>
-      <c r="AC196" s="3">
-        <f>IF($K196="","",Y196-AB196)</f>
-      </c>
-    </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG196" s="3">
+        <f>IF($K196="","",Y196-AF196)</f>
+      </c>
+    </row>
+    <row r="197" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="D197" s="2"/>
       <c r="J197" s="3"/>
@@ -10808,16 +10832,16 @@
         <f>IF($K197="","",L197-M197-R197-S197-T197-U197-V197-W197)</f>
       </c>
       <c r="Z197" s="3">
-        <f>IF($K197="","",(Y197-AB197)/J197*100)</f>
+        <f>IF($K197="","",(Y197-AF197)/J197*100)</f>
       </c>
       <c r="AA197" s="3">
         <f>IF($K197="","",M197-X197)</f>
       </c>
-      <c r="AC197" s="3">
-        <f>IF($K197="","",Y197-AB197)</f>
-      </c>
-    </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG197" s="3">
+        <f>IF($K197="","",Y197-AF197)</f>
+      </c>
+    </row>
+    <row r="198" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="D198" s="2"/>
       <c r="J198" s="3"/>
@@ -10859,16 +10883,16 @@
         <f>IF($K198="","",L198-M198-R198-S198-T198-U198-V198-W198)</f>
       </c>
       <c r="Z198" s="3">
-        <f>IF($K198="","",(Y198-AB198)/J198*100)</f>
+        <f>IF($K198="","",(Y198-AF198)/J198*100)</f>
       </c>
       <c r="AA198" s="3">
         <f>IF($K198="","",M198-X198)</f>
       </c>
-      <c r="AC198" s="3">
-        <f>IF($K198="","",Y198-AB198)</f>
-      </c>
-    </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG198" s="3">
+        <f>IF($K198="","",Y198-AF198)</f>
+      </c>
+    </row>
+    <row r="199" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="D199" s="2"/>
       <c r="J199" s="3"/>
@@ -10910,16 +10934,16 @@
         <f>IF($K199="","",L199-M199-R199-S199-T199-U199-V199-W199)</f>
       </c>
       <c r="Z199" s="3">
-        <f>IF($K199="","",(Y199-AB199)/J199*100)</f>
+        <f>IF($K199="","",(Y199-AF199)/J199*100)</f>
       </c>
       <c r="AA199" s="3">
         <f>IF($K199="","",M199-X199)</f>
       </c>
-      <c r="AC199" s="3">
-        <f>IF($K199="","",Y199-AB199)</f>
-      </c>
-    </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG199" s="3">
+        <f>IF($K199="","",Y199-AF199)</f>
+      </c>
+    </row>
+    <row r="200" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="D200" s="2"/>
       <c r="J200" s="3"/>
@@ -10961,16 +10985,16 @@
         <f>IF($K200="","",L200-M200-R200-S200-T200-U200-V200-W200)</f>
       </c>
       <c r="Z200" s="3">
-        <f>IF($K200="","",(Y200-AB200)/J200*100)</f>
+        <f>IF($K200="","",(Y200-AF200)/J200*100)</f>
       </c>
       <c r="AA200" s="3">
         <f>IF($K200="","",M200-X200)</f>
       </c>
-      <c r="AC200" s="3">
-        <f>IF($K200="","",Y200-AB200)</f>
-      </c>
-    </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG200" s="3">
+        <f>IF($K200="","",Y200-AF200)</f>
+      </c>
+    </row>
+    <row r="201" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="D201" s="2"/>
       <c r="J201" s="3"/>
@@ -11012,16 +11036,16 @@
         <f>IF($K201="","",L201-M201-R201-S201-T201-U201-V201-W201)</f>
       </c>
       <c r="Z201" s="3">
-        <f>IF($K201="","",(Y201-AB201)/J201*100)</f>
+        <f>IF($K201="","",(Y201-AF201)/J201*100)</f>
       </c>
       <c r="AA201" s="3">
         <f>IF($K201="","",M201-X201)</f>
       </c>
-      <c r="AC201" s="3">
-        <f>IF($K201="","",Y201-AB201)</f>
-      </c>
-    </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AG201" s="3">
+        <f>IF($K201="","",Y201-AF201)</f>
+      </c>
+    </row>
+    <row r="202" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="D202" s="2"/>
       <c r="J202" s="3"/>
@@ -11063,18 +11087,18 @@
         <f>IF($K202="","",L202-M202-R202-S202-T202-U202-V202-W202)</f>
       </c>
       <c r="Z202" s="3">
-        <f>IF($K202="","",(Y202-AB202)/J202*100)</f>
+        <f>IF($K202="","",(Y202-AF202)/J202*100)</f>
       </c>
       <c r="AA202" s="3">
         <f>IF($K202="","",M202-X202)</f>
       </c>
-      <c r="AC202" s="3">
-        <f>IF($K202="","",Y202-AB202)</f>
-      </c>
-    </row>
-    <row r="203" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG202" s="3">
+        <f>IF($K202="","",Y202-AF202)</f>
+      </c>
+    </row>
+    <row r="203" spans="1:38" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -11135,7 +11159,7 @@
         <f>SUM(Y2:Y202)</f>
       </c>
       <c r="Z203" s="6">
-        <f>IFERROR((Y203-AB203)/K203*100,0)</f>
+        <f>IFERROR((Y203-AF203)/K203*100,0)</f>
       </c>
       <c r="AA203" s="6">
         <f>SUM(AA2:AA202)</f>
@@ -11146,11 +11170,23 @@
       <c r="AC203" s="6">
         <f>SUM(AC2:AC202)</f>
       </c>
-      <c r="AD203" s="4"/>
-      <c r="AE203" s="4"/>
-      <c r="AF203" s="4"/>
-      <c r="AG203" s="4"/>
+      <c r="AD203" s="6">
+        <f>SUM(AD2:AD202)</f>
+      </c>
+      <c r="AE203" s="6">
+        <f>SUM(AE2:AE202)</f>
+      </c>
+      <c r="AF203" s="6">
+        <f>SUM(AF2:AF202)</f>
+      </c>
+      <c r="AG203" s="6">
+        <f>SUM(AG2:AG202)</f>
+      </c>
       <c r="AH203" s="4"/>
+      <c r="AI203" s="4"/>
+      <c r="AJ203" s="4"/>
+      <c r="AK203" s="4"/>
+      <c r="AL203" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
